--- a/OIC DOCS/dummy.xlsx
+++ b/OIC DOCS/dummy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jadav\Coding\Automation\UIIC\uiic_automation\OIC DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5326ED0-966D-43F8-9EA0-DA4F750134E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7E54A8-0A55-492C-B48E-CD41D68BDD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{0249C969-0BD7-4CC8-B38D-D9EE02361E7A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="236">
   <si>
     <t>Type of Body</t>
   </si>
@@ -331,9 +331,6 @@
     <t>Type of Licence</t>
   </si>
   <si>
-    <t>LMV-MCWG</t>
-  </si>
-  <si>
     <t>initial loss assessment</t>
   </si>
   <si>
@@ -697,9 +694,6 @@
     <t>AGRA</t>
   </si>
   <si>
-    <t>Panchkula, Haryana</t>
-  </si>
-  <si>
     <t xml:space="preserve">pin code </t>
   </si>
   <si>
@@ -722,6 +716,36 @@
   </si>
   <si>
     <t>CBZL12533</t>
+  </si>
+  <si>
+    <t>RTO NAME</t>
+  </si>
+  <si>
+    <t>gaya</t>
+  </si>
+  <si>
+    <t>workshop date</t>
+  </si>
+  <si>
+    <t>HPV</t>
+  </si>
+  <si>
+    <t>registered_owner_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">workshop estimate date </t>
+  </si>
+  <si>
+    <t xml:space="preserve">expiry date </t>
+  </si>
+  <si>
+    <t>license_number</t>
+  </si>
+  <si>
+    <t>SLA/200019</t>
+  </si>
+  <si>
+    <t>assam, bajali</t>
   </si>
 </sst>
 </file>
@@ -729,11 +753,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="m/d/yyyy;@"/>
-    <numFmt numFmtId="165" formatCode="[$-409]mmmmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]mmmmm\-yy;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -788,6 +812,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFD7BA7D"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1075,7 +1105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1089,10 +1119,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1153,7 +1183,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1293,45 +1323,47 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="justify"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="justify"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1360,16 +1392,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>1524</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>597408</xdr:colOff>
           <xdr:row>194</xdr:row>
-          <xdr:rowOff>158496</xdr:rowOff>
+          <xdr:rowOff>173736</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>291084</xdr:colOff>
+          <xdr:colOff>179832</xdr:colOff>
           <xdr:row>196</xdr:row>
-          <xdr:rowOff>67056</xdr:rowOff>
+          <xdr:rowOff>82296</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1710,12 +1742,14 @@
   <dimension ref="A2:AE294"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="8.77734375" style="1"/>
+    <col min="1" max="3" width="8.77734375" style="1"/>
+    <col min="4" max="4" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.5546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.77734375" style="1"/>
     <col min="7" max="7" width="26.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.77734375" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.77734375" style="1"/>
+    <col min="9" max="9" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="8.77734375" style="1"/>
     <col min="14" max="14" width="25.109375" style="1" customWidth="1"/>
     <col min="15" max="15" width="32" style="1" customWidth="1"/>
     <col min="16" max="16384" width="8.77734375" style="1"/>
@@ -2077,18 +2111,18 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="129" t="s">
+      <c r="B12" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -2623,7 +2657,7 @@
         <v>19</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="4"/>
@@ -2664,7 +2698,7 @@
         <v>19</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2739,14 +2773,14 @@
       <c r="D29" s="19"/>
       <c r="E29" s="20"/>
       <c r="F29" s="21"/>
-      <c r="G29" s="134" t="s">
+      <c r="G29" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="133"/>
-      <c r="I29" s="136" t="s">
+      <c r="H29" s="127"/>
+      <c r="I29" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="133"/>
+      <c r="J29" s="127"/>
       <c r="K29" s="22" t="s">
         <v>43</v>
       </c>
@@ -2784,15 +2818,15 @@
       <c r="F30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="137" t="s">
-        <v>226</v>
-      </c>
-      <c r="H30" s="126"/>
-      <c r="I30" s="136" t="str">
+      <c r="G30" s="133" t="s">
+        <v>224</v>
+      </c>
+      <c r="H30" s="134"/>
+      <c r="I30" s="132" t="str">
         <f>G30</f>
         <v>MEXC19606KT080595</v>
       </c>
-      <c r="J30" s="133"/>
+      <c r="J30" s="127"/>
       <c r="K30" s="22" t="str">
         <f>G30</f>
         <v>MEXC19606KT080595</v>
@@ -2831,15 +2865,15 @@
       <c r="F31" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="134" t="s">
-        <v>227</v>
-      </c>
-      <c r="H31" s="133"/>
-      <c r="I31" s="135" t="str">
+      <c r="G31" s="126" t="s">
+        <v>225</v>
+      </c>
+      <c r="H31" s="127"/>
+      <c r="I31" s="128" t="str">
         <f>G31</f>
         <v>CBZL12533</v>
       </c>
-      <c r="J31" s="128"/>
+      <c r="J31" s="129"/>
       <c r="K31" s="27" t="str">
         <f>G31</f>
         <v>CBZL12533</v>
@@ -2879,7 +2913,7 @@
         <v>19</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -3283,8 +3317,12 @@
       <c r="G42" s="2">
         <v>54</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="H42" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -3533,8 +3571,12 @@
       <c r="G48" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
+      <c r="H48" s="139" t="s">
+        <v>230</v>
+      </c>
+      <c r="I48" s="125" t="s">
+        <v>81</v>
+      </c>
       <c r="J48" s="8" t="s">
         <v>82</v>
       </c>
@@ -3615,7 +3657,7 @@
         <v>19</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -3826,7 +3868,7 @@
         <v>19</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -3868,7 +3910,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O56" s="2">
         <v>50000</v>
@@ -3896,7 +3938,7 @@
         <v>4</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="32"/>
@@ -3909,10 +3951,10 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O57" s="122" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
@@ -3937,7 +3979,7 @@
         <v>17</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="13"/>
@@ -3978,7 +4020,7 @@
         <v>23</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="13"/>
@@ -3986,7 +4028,7 @@
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -4028,7 +4070,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O60" s="123">
         <v>0.42708333333333331</v>
@@ -4056,7 +4098,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="32"/>
@@ -4069,7 +4111,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
       <c r="N61" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O61" s="2">
         <v>987</v>
@@ -4095,7 +4137,7 @@
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="13"/>
@@ -4112,7 +4154,7 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O62" s="2">
         <v>781371</v>
@@ -4138,7 +4180,7 @@
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="13"/>
@@ -4146,10 +4188,10 @@
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4157,10 +4199,10 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="O63" s="122" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
@@ -4183,7 +4225,7 @@
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="32"/>
@@ -4191,7 +4233,7 @@
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -4222,7 +4264,7 @@
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="13"/>
@@ -4230,7 +4272,7 @@
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -4329,7 +4371,7 @@
         <v>6</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="4"/>
@@ -4364,7 +4406,7 @@
       <c r="A69" s="2"/>
       <c r="B69" s="14"/>
       <c r="C69" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="4"/>
@@ -4372,10 +4414,14 @@
         <v>19</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I69" s="124">
+        <v>46149</v>
+      </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
@@ -4411,7 +4457,7 @@
         <v>19</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -4442,7 +4488,7 @@
       <c r="A71" s="2"/>
       <c r="B71" s="14"/>
       <c r="C71" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="4"/>
@@ -4450,7 +4496,7 @@
         <v>19</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -4480,8 +4526,12 @@
     <row r="72" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
+      <c r="C72" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D72" s="124">
+        <v>46152</v>
+      </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -4516,7 +4566,7 @@
         <v>7</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="13"/>
@@ -4524,7 +4574,7 @@
         <v>19</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -4590,7 +4640,7 @@
         <v>8</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="13"/>
@@ -4598,7 +4648,7 @@
         <v>19</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -4664,7 +4714,7 @@
         <v>9</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="32"/>
@@ -4699,7 +4749,7 @@
       <c r="A78" s="2"/>
       <c r="B78" s="14"/>
       <c r="C78" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="32"/>
@@ -4733,17 +4783,17 @@
     <row r="79" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A79" s="2"/>
       <c r="B79" s="14"/>
-      <c r="C79" s="129" t="s">
+      <c r="C79" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="130"/>
-      <c r="E79" s="130"/>
-      <c r="F79" s="130"/>
-      <c r="G79" s="130"/>
-      <c r="H79" s="130"/>
-      <c r="I79" s="130"/>
-      <c r="J79" s="130"/>
-      <c r="K79" s="130"/>
+      <c r="D79" s="131"/>
+      <c r="E79" s="131"/>
+      <c r="F79" s="131"/>
+      <c r="G79" s="131"/>
+      <c r="H79" s="131"/>
+      <c r="I79" s="131"/>
+      <c r="J79" s="131"/>
+      <c r="K79" s="131"/>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -4773,8 +4823,12 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
+      <c r="H80" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I80" s="124">
+        <v>46169</v>
+      </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
@@ -4804,14 +4858,18 @@
         <v>10</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
+      <c r="H81" s="125" t="s">
+        <v>233</v>
+      </c>
+      <c r="I81" s="125" t="s">
+        <v>234</v>
+      </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
@@ -4838,17 +4896,17 @@
     <row r="82" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="14"/>
-      <c r="C82" s="129" t="s">
-        <v>124</v>
-      </c>
-      <c r="D82" s="130"/>
-      <c r="E82" s="130"/>
-      <c r="F82" s="130"/>
-      <c r="G82" s="130"/>
-      <c r="H82" s="130"/>
-      <c r="I82" s="130"/>
-      <c r="J82" s="130"/>
-      <c r="K82" s="130"/>
+      <c r="C82" s="130" t="s">
+        <v>123</v>
+      </c>
+      <c r="D82" s="131"/>
+      <c r="E82" s="131"/>
+      <c r="F82" s="131"/>
+      <c r="G82" s="131"/>
+      <c r="H82" s="131"/>
+      <c r="I82" s="131"/>
+      <c r="J82" s="131"/>
+      <c r="K82" s="131"/>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -4909,7 +4967,7 @@
         <v>11</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
@@ -4944,7 +5002,7 @@
       <c r="A85" s="2"/>
       <c r="B85" s="14"/>
       <c r="C85" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
@@ -5014,7 +5072,7 @@
         <v>12</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
@@ -5088,7 +5146,7 @@
         <v>2</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
@@ -5125,7 +5183,7 @@
         <v>3</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -5162,7 +5220,7 @@
         <v>4</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
@@ -5232,7 +5290,7 @@
         <v>13</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
@@ -5301,7 +5359,7 @@
       <c r="B95" s="18"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E95" s="19"/>
       <c r="F95" s="35"/>
@@ -5336,7 +5394,7 @@
     <row r="96" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="B96" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -5346,7 +5404,7 @@
         <v>-119.88888888888889</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
@@ -5379,7 +5437,7 @@
     <row r="97" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="B97" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
@@ -5388,7 +5446,7 @@
         <v>18</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H97" s="19"/>
       <c r="I97" s="19"/>
@@ -5458,13 +5516,13 @@
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
       <c r="G99" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
@@ -5492,30 +5550,30 @@
     <row r="100" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A100" s="2"/>
       <c r="B100" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C100" s="30" t="s">
         <v>138</v>
-      </c>
-      <c r="C100" s="30" t="s">
-        <v>139</v>
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="31"/>
       <c r="F100" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="G100" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="G100" s="42" t="s">
+      <c r="H100" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="H100" s="42" t="s">
+      <c r="I100" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="I100" s="43" t="s">
+      <c r="J100" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="J100" s="8" t="s">
+      <c r="K100" s="44" t="s">
         <v>144</v>
-      </c>
-      <c r="K100" s="44" t="s">
-        <v>145</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -5544,7 +5602,7 @@
         <v>1</v>
       </c>
       <c r="C101" s="45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="38"/>
@@ -5587,7 +5645,7 @@
         <v>2</v>
       </c>
       <c r="C102" s="47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="38"/>
@@ -5630,7 +5688,7 @@
         <v>3</v>
       </c>
       <c r="C103" s="47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="38"/>
@@ -5638,7 +5696,7 @@
         <v>8570</v>
       </c>
       <c r="G103" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H103" s="46">
         <v>500</v>
@@ -5673,7 +5731,7 @@
         <v>4</v>
       </c>
       <c r="C104" s="47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="38"/>
@@ -5681,7 +5739,7 @@
         <v>8861</v>
       </c>
       <c r="G104" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H104" s="46">
         <v>5</v>
@@ -5716,7 +5774,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="38"/>
@@ -5724,7 +5782,7 @@
         <v>9110</v>
       </c>
       <c r="G105" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H105" s="46">
         <v>5</v>
@@ -5759,7 +5817,7 @@
         <v>6</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="38"/>
@@ -5767,7 +5825,7 @@
         <v>3030</v>
       </c>
       <c r="G106" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H106" s="46">
         <v>4</v>
@@ -5802,7 +5860,7 @@
         <v>7</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="38"/>
@@ -5810,7 +5868,7 @@
         <v>1560</v>
       </c>
       <c r="G107" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H107" s="46"/>
       <c r="I107" s="46">
@@ -5845,7 +5903,7 @@
         <v>8</v>
       </c>
       <c r="C108" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="38"/>
@@ -5853,7 +5911,7 @@
         <v>8570</v>
       </c>
       <c r="G108" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H108" s="46">
         <v>4</v>
@@ -5888,7 +5946,7 @@
         <v>9</v>
       </c>
       <c r="C109" s="47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="38"/>
@@ -5896,7 +5954,7 @@
         <v>9110</v>
       </c>
       <c r="G109" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H109" s="46">
         <v>4</v>
@@ -5931,7 +5989,7 @@
         <v>10</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="38"/>
@@ -5939,7 +5997,7 @@
         <v>8861</v>
       </c>
       <c r="G110" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H110" s="46"/>
       <c r="I110" s="46">
@@ -5974,7 +6032,7 @@
         <v>11</v>
       </c>
       <c r="C111" s="47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" s="38"/>
@@ -5982,7 +6040,7 @@
         <v>2270</v>
       </c>
       <c r="G111" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H111" s="46"/>
       <c r="I111" s="46">
@@ -6017,7 +6075,7 @@
         <v>12</v>
       </c>
       <c r="C112" s="47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" s="38"/>
@@ -6025,7 +6083,7 @@
         <v>2270</v>
       </c>
       <c r="G112" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H112" s="46">
         <v>5</v>
@@ -6060,7 +6118,7 @@
         <v>13</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" s="38"/>
@@ -6068,7 +6126,7 @@
         <v>302</v>
       </c>
       <c r="G113" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H113" s="46">
         <v>4</v>
@@ -6103,7 +6161,7 @@
         <v>14</v>
       </c>
       <c r="C114" s="47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" s="38"/>
@@ -6111,7 +6169,7 @@
         <v>3560</v>
       </c>
       <c r="G114" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H114" s="46"/>
       <c r="I114" s="46">
@@ -6146,7 +6204,7 @@
         <v>15</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" s="38"/>
@@ -6154,7 +6212,7 @@
         <v>70000</v>
       </c>
       <c r="G115" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H115" s="46">
         <v>4</v>
@@ -6189,7 +6247,7 @@
         <v>16</v>
       </c>
       <c r="C116" s="47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" s="38"/>
@@ -6234,7 +6292,7 @@
         <v>17</v>
       </c>
       <c r="C117" s="47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" s="38"/>
@@ -6872,7 +6930,7 @@
     <row r="136" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A136" s="2"/>
       <c r="B136" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -6925,7 +6983,7 @@
         <v>18</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="31"/>
@@ -6971,7 +7029,7 @@
     <row r="138" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A138" s="2"/>
       <c r="B138" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -7018,7 +7076,7 @@
     <row r="139" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A139" s="2"/>
       <c r="B139" s="61" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -7057,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="31"/>
@@ -7099,7 +7157,7 @@
     <row r="141" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2"/>
       <c r="B141" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C141" s="19"/>
       <c r="D141" s="19"/>
@@ -7146,7 +7204,7 @@
     <row r="142" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2"/>
       <c r="B142" s="30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="19"/>
@@ -7220,7 +7278,7 @@
     <row r="144" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A144" s="2"/>
       <c r="B144" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -7522,7 +7580,7 @@
     <row r="153" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A153" s="2"/>
       <c r="B153" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -7590,7 +7648,7 @@
     <row r="155" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A155" s="2"/>
       <c r="B155" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C155" s="19"/>
       <c r="D155" s="19"/>
@@ -7625,24 +7683,24 @@
     <row r="156" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A156" s="2"/>
       <c r="B156" s="73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C156" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D156" s="19"/>
       <c r="E156" s="36"/>
       <c r="F156" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="G156" s="76" t="s">
         <v>174</v>
       </c>
-      <c r="G156" s="76" t="s">
+      <c r="H156" s="77" t="s">
         <v>175</v>
       </c>
-      <c r="H156" s="77" t="s">
+      <c r="I156" s="78" t="s">
         <v>176</v>
-      </c>
-      <c r="I156" s="78" t="s">
-        <v>177</v>
       </c>
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
@@ -7673,7 +7731,7 @@
         <v>1</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
@@ -7712,7 +7770,7 @@
         <v>2</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
@@ -7751,7 +7809,7 @@
         <v>3</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
@@ -7853,7 +7911,7 @@
     <row r="162" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A162" s="2"/>
       <c r="B162" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C162" s="41"/>
       <c r="D162" s="41"/>
@@ -7933,7 +7991,7 @@
     <row r="164" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="38"/>
       <c r="B164" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C164" s="19"/>
       <c r="D164" s="19"/>
@@ -7982,7 +8040,7 @@
       <c r="B165" s="30"/>
       <c r="C165" s="5"/>
       <c r="D165" s="49" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E165" s="5"/>
       <c r="F165" s="86"/>
@@ -8051,7 +8109,7 @@
     <row r="167" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A167" s="2"/>
       <c r="B167" s="70" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C167" s="19"/>
       <c r="D167" s="19"/>
@@ -8059,10 +8117,10 @@
       <c r="F167" s="92"/>
       <c r="G167" s="92"/>
       <c r="H167" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I167" s="93" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
@@ -8133,7 +8191,7 @@
         <v>18</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
@@ -8173,7 +8231,7 @@
     <row r="170" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2"/>
       <c r="B170" s="70" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C170" s="19"/>
       <c r="D170" s="19"/>
@@ -8247,7 +8305,7 @@
     <row r="172" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A172" s="2"/>
       <c r="B172" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -8318,16 +8376,16 @@
     <row r="174" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A174" s="2"/>
       <c r="B174" s="30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C174" s="5"/>
       <c r="D174" s="5"/>
       <c r="E174" s="31"/>
       <c r="F174" s="42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G174" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
@@ -8357,7 +8415,7 @@
     <row r="175" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A175" s="2"/>
       <c r="B175" s="97" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C175" s="41"/>
       <c r="D175" s="41"/>
@@ -8398,7 +8456,7 @@
     <row r="176" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A176" s="2"/>
       <c r="B176" s="24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
@@ -8439,7 +8497,7 @@
     <row r="177" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A177" s="2"/>
       <c r="B177" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -8480,7 +8538,7 @@
     <row r="178" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
       <c r="B178" s="24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
@@ -8518,7 +8576,7 @@
     <row r="179" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2"/>
       <c r="B179" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C179" s="5"/>
       <c r="D179" s="19"/>
@@ -8592,7 +8650,7 @@
     <row r="181" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A181" s="2"/>
       <c r="B181" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -8629,7 +8687,7 @@
     <row r="182" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A182" s="2"/>
       <c r="B182" s="70" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C182" s="19"/>
       <c r="D182" s="19"/>
@@ -8699,18 +8757,18 @@
     </row>
     <row r="184" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A184" s="33"/>
-      <c r="B184" s="131" t="s">
-        <v>190</v>
-      </c>
-      <c r="C184" s="130"/>
-      <c r="D184" s="130"/>
-      <c r="E184" s="130"/>
-      <c r="F184" s="130"/>
-      <c r="G184" s="130"/>
-      <c r="H184" s="130"/>
-      <c r="I184" s="130"/>
-      <c r="J184" s="130"/>
-      <c r="K184" s="130"/>
+      <c r="B184" s="137" t="s">
+        <v>189</v>
+      </c>
+      <c r="C184" s="131"/>
+      <c r="D184" s="131"/>
+      <c r="E184" s="131"/>
+      <c r="F184" s="131"/>
+      <c r="G184" s="131"/>
+      <c r="H184" s="131"/>
+      <c r="I184" s="131"/>
+      <c r="J184" s="131"/>
+      <c r="K184" s="131"/>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
@@ -8768,7 +8826,7 @@
     <row r="186" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A186" s="2"/>
       <c r="B186" s="100" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -8839,7 +8897,7 @@
         <v>1</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" s="4" t="s">
@@ -8914,7 +8972,7 @@
         <v>2</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" s="4" t="s">
@@ -8987,7 +9045,7 @@
       <c r="A192" s="2"/>
       <c r="B192" s="4"/>
       <c r="C192" s="97" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D192" s="41"/>
       <c r="E192" s="41"/>
@@ -8996,7 +9054,7 @@
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
       <c r="J192" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
@@ -9057,7 +9115,7 @@
       <c r="A194" s="2"/>
       <c r="B194" s="4"/>
       <c r="C194" s="102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="5"/>
@@ -9191,13 +9249,13 @@
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E198" s="121" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F198" s="120">
         <v>3.5010231260389999E+19</v>
@@ -9211,7 +9269,7 @@
       <c r="K198" s="2"/>
       <c r="L198" s="2"/>
       <c r="M198" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -9279,27 +9337,27 @@
       <c r="K200" s="2"/>
       <c r="L200" s="2"/>
       <c r="M200" s="78" t="s">
+        <v>197</v>
+      </c>
+      <c r="N200" s="103" t="s">
         <v>198</v>
       </c>
-      <c r="N200" s="103" t="s">
+      <c r="O200" s="138" t="s">
         <v>199</v>
       </c>
-      <c r="O200" s="132" t="s">
+      <c r="P200" s="127"/>
+      <c r="Q200" s="138" t="s">
         <v>200</v>
       </c>
-      <c r="P200" s="133"/>
-      <c r="Q200" s="132" t="s">
+      <c r="R200" s="127"/>
+      <c r="S200" s="138" t="s">
         <v>201</v>
       </c>
-      <c r="R200" s="133"/>
-      <c r="S200" s="132" t="s">
+      <c r="T200" s="127"/>
+      <c r="U200" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="T200" s="133"/>
-      <c r="U200" s="125" t="s">
-        <v>203</v>
-      </c>
-      <c r="V200" s="126"/>
+      <c r="V200" s="134"/>
       <c r="W200" s="2"/>
       <c r="X200" s="2"/>
       <c r="Y200" s="2"/>
@@ -9326,25 +9384,25 @@
       <c r="M201" s="104"/>
       <c r="N201" s="31"/>
       <c r="O201" s="77" t="s">
+        <v>203</v>
+      </c>
+      <c r="P201" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="P201" s="76" t="s">
-        <v>205</v>
-      </c>
       <c r="Q201" s="105" t="s">
+        <v>203</v>
+      </c>
+      <c r="R201" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="R201" s="76" t="s">
-        <v>205</v>
-      </c>
       <c r="S201" s="105" t="s">
+        <v>203</v>
+      </c>
+      <c r="T201" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="T201" s="76" t="s">
-        <v>205</v>
-      </c>
-      <c r="U201" s="127"/>
-      <c r="V201" s="128"/>
+      <c r="U201" s="136"/>
+      <c r="V201" s="129"/>
       <c r="W201" s="2"/>
       <c r="X201" s="2"/>
       <c r="Y201" s="2"/>
@@ -9359,10 +9417,10 @@
       <c r="A202" s="2"/>
       <c r="B202" s="4"/>
       <c r="C202" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D202" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
@@ -9562,7 +9620,7 @@
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E206" s="2">
         <v>2500</v>
@@ -9575,7 +9633,7 @@
       <c r="K206" s="2"/>
       <c r="L206" s="2"/>
       <c r="M206" s="70" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N206" s="74"/>
       <c r="O206" s="74"/>
@@ -11319,7 +11377,7 @@
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" s="117">
@@ -11356,7 +11414,7 @@
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" s="117"/>
@@ -12442,6 +12500,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="U200:V201"/>
+    <mergeCell ref="C79:K79"/>
+    <mergeCell ref="C82:K82"/>
+    <mergeCell ref="B184:K184"/>
+    <mergeCell ref="O200:P200"/>
+    <mergeCell ref="Q200:R200"/>
+    <mergeCell ref="S200:T200"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="B12:K12"/>
@@ -12449,13 +12514,6 @@
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="U200:V201"/>
-    <mergeCell ref="C79:K79"/>
-    <mergeCell ref="C82:K82"/>
-    <mergeCell ref="B184:K184"/>
-    <mergeCell ref="O200:P200"/>
-    <mergeCell ref="Q200:R200"/>
-    <mergeCell ref="S200:T200"/>
   </mergeCells>
   <conditionalFormatting sqref="E262:F262">
     <cfRule type="expression" priority="1" stopIfTrue="1">
@@ -12472,16 +12530,16 @@
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>594360</xdr:colOff>
                 <xdr:row>194</xdr:row>
-                <xdr:rowOff>160020</xdr:rowOff>
+                <xdr:rowOff>175260</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>289560</xdr:colOff>
+                <xdr:colOff>175260</xdr:colOff>
                 <xdr:row>196</xdr:row>
-                <xdr:rowOff>68580</xdr:rowOff>
+                <xdr:rowOff>83820</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>

--- a/OIC DOCS/dummy.xlsx
+++ b/OIC DOCS/dummy.xlsx
@@ -1,20 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jadav\Coding\Automation\UIIC\uiic_automation\OIC DOCS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CCF3AC-7552-4B09-9068-3DAB8BDE64E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="257">
   <si>
     <t>Er. SUNIL KUMAR</t>
   </si>
@@ -738,14 +758,62 @@
   </si>
   <si>
     <t>Date of Registration/isurance</t>
+  </si>
+  <si>
+    <t>traveling_expenses</t>
+  </si>
+  <si>
+    <t>photocharges</t>
+  </si>
+  <si>
+    <t>DAILY_ALLOWANCE</t>
+  </si>
+  <si>
+    <t>professional_fee</t>
+  </si>
+  <si>
+    <t>other_expenses</t>
+  </si>
+  <si>
+    <t>salvage_amount</t>
+  </si>
+  <si>
+    <t>Estimate Date</t>
+  </si>
+  <si>
+    <t>Registered Owner Name</t>
+  </si>
+  <si>
+    <t>fitness valid upto</t>
+  </si>
+  <si>
+    <t>permit valid upto</t>
+  </si>
+  <si>
+    <t>validity of auth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auth number </t>
+  </si>
+  <si>
+    <t xml:space="preserve">qualification </t>
+  </si>
+  <si>
+    <t>10/10/2025</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>charges filed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmmmm-yy"/>
+    <numFmt numFmtId="164" formatCode="mmmmm\-yy"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -791,7 +859,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FFd7ba7d"/>
+      <color rgb="FFD7BA7D"/>
       <name val="Consolas"/>
       <family val="2"/>
     </font>
@@ -804,7 +872,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -818,7 +886,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7f7f7f"/>
+        <fgColor rgb="FF7F7F7F"/>
       </patternFill>
     </fill>
   </fills>
@@ -1072,7 +1140,7 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
@@ -1084,7 +1152,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -1129,518 +1197,532 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="177">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="14" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="20" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="16" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="16" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="16" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="17" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="17" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="17" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="18" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="19" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="20" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="21" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="14" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="16" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="22" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="23" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="16" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="24" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="14" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="25" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="14" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="13" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="17" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1651,10 +1733,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1692,71 +1774,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1784,7 +1866,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1807,11 +1889,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1820,13 +1902,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1836,7 +1918,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1845,7 +1927,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1854,7 +1936,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1862,10 +1944,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1930,47 +2012,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE294"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="164" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="165" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="164" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="166" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="167" width="26.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="165" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="165" width="26.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="167" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="167" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="167" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="165" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="164" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="165" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="167" width="25.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="165" width="32.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="167" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="165" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="167" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="167" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="164" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="8.6640625" style="151" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="152" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="151" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="153" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" style="154" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="152" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.33203125" style="152" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="154" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="154" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="154" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="152" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="151" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="152" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.109375" style="154" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32" style="152" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" style="154" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5546875" style="152" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" style="154" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.5546875" style="151" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5546875" style="154" bestFit="1" customWidth="1"/>
+    <col min="22" max="31" width="13.5546875" style="151" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -2003,7 +2075,7 @@
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="5"/>
@@ -2036,7 +2108,7 @@
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="9" t="s">
         <v>0</v>
@@ -2073,7 +2145,7 @@
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
         <v>2</v>
@@ -2110,7 +2182,7 @@
       <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
         <v>4</v>
@@ -2147,7 +2219,7 @@
       <c r="AD5" s="5"/>
       <c r="AE5" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="12" t="s">
         <v>6</v>
@@ -2184,7 +2256,7 @@
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
@@ -2217,7 +2289,7 @@
       <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="5"/>
@@ -2250,7 +2322,7 @@
       <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="20" t="s">
         <v>8</v>
@@ -2289,7 +2361,7 @@
       <c r="AD9" s="5"/>
       <c r="AE9" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="20"/>
       <c r="C10" s="5"/>
@@ -2322,7 +2394,7 @@
       <c r="AD10" s="5"/>
       <c r="AE10" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="23" t="s">
         <v>11</v>
@@ -2357,20 +2429,20 @@
       <c r="AD11" s="5"/>
       <c r="AE11" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="6"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="157"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="159"/>
+      <c r="H12" s="158"/>
+      <c r="I12" s="158"/>
+      <c r="J12" s="158"/>
+      <c r="K12" s="159"/>
       <c r="L12" s="5"/>
       <c r="M12" s="6"/>
       <c r="N12" s="8"/>
@@ -2392,7 +2464,7 @@
       <c r="AD12" s="5"/>
       <c r="AE12" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6">
         <v>1</v>
@@ -2427,7 +2499,7 @@
       <c r="AD13" s="5"/>
       <c r="AE13" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="20" t="s">
         <v>13</v>
@@ -2472,7 +2544,7 @@
       <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5" t="s">
@@ -2509,7 +2581,7 @@
       <c r="AD15" s="5"/>
       <c r="AE15" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
@@ -2542,7 +2614,7 @@
       <c r="AD16" s="5"/>
       <c r="AE16" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
         <v>19</v>
@@ -2591,7 +2663,7 @@
       <c r="AD17" s="5"/>
       <c r="AE17" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
@@ -2624,7 +2696,7 @@
       <c r="AD18" s="5"/>
       <c r="AE18" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="20" t="s">
         <v>24</v>
@@ -2665,7 +2737,7 @@
       <c r="AD19" s="5"/>
       <c r="AE19" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="6"/>
       <c r="C20" s="5" t="s">
@@ -2704,7 +2776,7 @@
       <c r="AD20" s="5"/>
       <c r="AE20" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="6"/>
       <c r="C21" s="5" t="s">
@@ -2743,7 +2815,7 @@
       <c r="AD21" s="5"/>
       <c r="AE21" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="20"/>
       <c r="C22" s="5"/>
@@ -2780,7 +2852,7 @@
       <c r="AD22" s="5"/>
       <c r="AE22" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="20" t="s">
         <v>30</v>
@@ -2821,7 +2893,7 @@
       <c r="AD23" s="5"/>
       <c r="AE23" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="20"/>
       <c r="C24" s="5"/>
@@ -2854,7 +2926,7 @@
       <c r="AD24" s="5"/>
       <c r="AE24" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="20">
         <v>2</v>
@@ -2895,7 +2967,7 @@
       <c r="AD25" s="5"/>
       <c r="AE25" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
         <v>13</v>
@@ -2936,7 +3008,7 @@
       <c r="AD26" s="5"/>
       <c r="AE26" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
         <v>19</v>
@@ -2977,7 +3049,7 @@
       <c r="AD27" s="5"/>
       <c r="AE27" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
         <v>24</v>
@@ -3018,22 +3090,22 @@
       <c r="AD28" s="5"/>
       <c r="AE28" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="28"/>
       <c r="D29" s="29"/>
       <c r="E29" s="30"/>
       <c r="F29" s="31"/>
-      <c r="G29" s="32" t="s">
+      <c r="G29" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="33"/>
-      <c r="I29" s="34" t="s">
+      <c r="H29" s="161"/>
+      <c r="I29" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="33"/>
-      <c r="K29" s="35" t="s">
+      <c r="J29" s="161"/>
+      <c r="K29" s="32" t="s">
         <v>43</v>
       </c>
       <c r="L29" s="5"/>
@@ -3057,12 +3129,12 @@
       <c r="AD29" s="5"/>
       <c r="AE29" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="33" t="s">
         <v>44</v>
       </c>
       <c r="D30" s="7"/>
@@ -3070,16 +3142,18 @@
       <c r="F30" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="37" t="s">
+      <c r="G30" s="163" t="s">
         <v>45</v>
       </c>
-      <c r="H30" s="38"/>
-      <c r="I30" s="34">
+      <c r="H30" s="164"/>
+      <c r="I30" s="162" t="str">
         <f>G30</f>
-      </c>
-      <c r="J30" s="33"/>
-      <c r="K30" s="35">
+        <v>MEXC19606KT080595</v>
+      </c>
+      <c r="J30" s="161"/>
+      <c r="K30" s="32" t="str">
         <f>G30</f>
+        <v>MEXC19606KT080595</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="6"/>
@@ -3102,29 +3176,31 @@
       <c r="AD30" s="5"/>
       <c r="AE30" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="35" t="s">
         <v>47</v>
       </c>
       <c r="D31" s="14"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="41" t="s">
+      <c r="E31" s="36"/>
+      <c r="F31" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="32" t="s">
+      <c r="G31" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="33"/>
-      <c r="I31" s="42">
+      <c r="H31" s="161"/>
+      <c r="I31" s="165" t="str">
         <f>G31</f>
-      </c>
-      <c r="J31" s="43"/>
-      <c r="K31" s="44">
+        <v>CBZL12533</v>
+      </c>
+      <c r="J31" s="166"/>
+      <c r="K31" s="38" t="str">
         <f>G31</f>
+        <v>CBZL12533</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="6"/>
@@ -3147,7 +3223,7 @@
       <c r="AD31" s="5"/>
       <c r="AE31" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="6" t="s">
         <v>49</v>
@@ -3188,7 +3264,7 @@
       <c r="AD32" s="5"/>
       <c r="AE32" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="6" t="s">
         <v>52</v>
@@ -3205,9 +3281,13 @@
         <v>54</v>
       </c>
       <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
+      <c r="I33" s="8" t="s">
+        <v>248</v>
+      </c>
       <c r="J33" s="8"/>
-      <c r="K33" s="6"/>
+      <c r="K33" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="L33" s="5"/>
       <c r="M33" s="6"/>
       <c r="N33" s="8"/>
@@ -3229,7 +3309,7 @@
       <c r="AD33" s="5"/>
       <c r="AE33" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="6" t="s">
         <v>55</v>
@@ -3246,8 +3326,12 @@
         <v>57</v>
       </c>
       <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
+      <c r="I34" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="J34" s="176" t="s">
+        <v>254</v>
+      </c>
       <c r="K34" s="6"/>
       <c r="L34" s="5"/>
       <c r="M34" s="6"/>
@@ -3270,7 +3354,7 @@
       <c r="AD34" s="5"/>
       <c r="AE34" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="6" t="s">
         <v>58</v>
@@ -3287,13 +3371,21 @@
         <v>60</v>
       </c>
       <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
+      <c r="I35" s="8" t="s">
+        <v>241</v>
+      </c>
       <c r="J35" s="8"/>
-      <c r="K35" s="6"/>
+      <c r="K35" s="6">
+        <v>1000</v>
+      </c>
       <c r="L35" s="5"/>
       <c r="M35" s="6"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="6"/>
+      <c r="N35" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="O35" s="176" t="s">
+        <v>254</v>
+      </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="6"/>
       <c r="R35" s="8"/>
@@ -3311,7 +3403,7 @@
       <c r="AD35" s="5"/>
       <c r="AE35" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="6" t="s">
         <v>61</v>
@@ -3328,13 +3420,21 @@
         <v>990</v>
       </c>
       <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
+      <c r="I36" s="8" t="s">
+        <v>242</v>
+      </c>
       <c r="J36" s="8"/>
-      <c r="K36" s="6"/>
+      <c r="K36" s="6">
+        <v>1000</v>
+      </c>
       <c r="L36" s="5"/>
       <c r="M36" s="6"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="6"/>
+      <c r="N36" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="O36" s="176" t="s">
+        <v>254</v>
+      </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="6"/>
       <c r="R36" s="8"/>
@@ -3352,7 +3452,7 @@
       <c r="AD36" s="5"/>
       <c r="AE36" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="6" t="s">
         <v>63</v>
@@ -3369,13 +3469,21 @@
         <v>9800</v>
       </c>
       <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
+      <c r="I37" s="8" t="s">
+        <v>243</v>
+      </c>
       <c r="J37" s="8"/>
-      <c r="K37" s="6"/>
+      <c r="K37" s="6">
+        <v>1000</v>
+      </c>
       <c r="L37" s="5"/>
       <c r="M37" s="6"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="6"/>
+      <c r="N37" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="O37" s="6">
+        <v>5454</v>
+      </c>
       <c r="P37" s="8"/>
       <c r="Q37" s="6"/>
       <c r="R37" s="8"/>
@@ -3393,7 +3501,7 @@
       <c r="AD37" s="5"/>
       <c r="AE37" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
         <v>65</v>
@@ -3410,13 +3518,21 @@
         <v>40</v>
       </c>
       <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
+      <c r="I38" s="8" t="s">
+        <v>244</v>
+      </c>
       <c r="J38" s="8"/>
-      <c r="K38" s="6"/>
+      <c r="K38" s="6">
+        <v>1000</v>
+      </c>
       <c r="L38" s="5"/>
       <c r="M38" s="6"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="6"/>
+      <c r="N38" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="O38" s="6">
+        <v>1515</v>
+      </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="6"/>
       <c r="R38" s="8"/>
@@ -3434,7 +3550,7 @@
       <c r="AD38" s="5"/>
       <c r="AE38" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="6"/>
       <c r="C39" s="5" t="s">
@@ -3449,9 +3565,13 @@
         <v>16</v>
       </c>
       <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
+      <c r="I39" s="8" t="s">
+        <v>245</v>
+      </c>
       <c r="J39" s="8"/>
-      <c r="K39" s="6"/>
+      <c r="K39" s="6">
+        <v>1000</v>
+      </c>
       <c r="L39" s="5"/>
       <c r="M39" s="6"/>
       <c r="N39" s="8"/>
@@ -3473,7 +3593,7 @@
       <c r="AD39" s="5"/>
       <c r="AE39" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="6"/>
       <c r="C40" s="5" t="s">
@@ -3488,13 +3608,21 @@
         <v>16</v>
       </c>
       <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
+      <c r="I40" s="8" t="s">
+        <v>246</v>
+      </c>
       <c r="J40" s="8"/>
-      <c r="K40" s="6"/>
+      <c r="K40" s="6">
+        <v>1000</v>
+      </c>
       <c r="L40" s="5"/>
       <c r="M40" s="6"/>
-      <c r="N40" s="8"/>
-      <c r="O40" s="6"/>
+      <c r="N40" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>255</v>
+      </c>
       <c r="P40" s="8"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="8"/>
@@ -3512,7 +3640,7 @@
       <c r="AD40" s="5"/>
       <c r="AE40" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="6"/>
       <c r="C41" s="5" t="s">
@@ -3532,8 +3660,12 @@
       <c r="K41" s="6"/>
       <c r="L41" s="5"/>
       <c r="M41" s="6"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="6"/>
+      <c r="N41" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>255</v>
+      </c>
       <c r="P41" s="8"/>
       <c r="Q41" s="6"/>
       <c r="R41" s="8"/>
@@ -3551,7 +3683,7 @@
       <c r="AD41" s="5"/>
       <c r="AE41" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="6"/>
       <c r="C42" s="5" t="s">
@@ -3562,7 +3694,7 @@
       <c r="F42" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G42" s="45">
+      <c r="G42" s="39">
         <v>54</v>
       </c>
       <c r="H42" s="8" t="s">
@@ -3594,7 +3726,7 @@
       <c r="AD42" s="5"/>
       <c r="AE42" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="6" t="s">
         <v>73</v>
@@ -3635,7 +3767,7 @@
       <c r="AD43" s="5"/>
       <c r="AE43" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="6" t="s">
         <v>75</v>
@@ -3653,10 +3785,10 @@
       </c>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
-      <c r="J44" s="46" t="s">
+      <c r="J44" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="K44" s="47"/>
+      <c r="K44" s="41"/>
       <c r="L44" s="5"/>
       <c r="M44" s="6"/>
       <c r="N44" s="8"/>
@@ -3678,7 +3810,7 @@
       <c r="AD44" s="5"/>
       <c r="AE44" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="6" t="s">
         <v>79</v>
@@ -3696,10 +3828,10 @@
       </c>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="48" t="s">
+      <c r="J45" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="K45" s="49" t="s">
+      <c r="K45" s="43" t="s">
         <v>83</v>
       </c>
       <c r="L45" s="5"/>
@@ -3723,7 +3855,7 @@
       <c r="AD45" s="5"/>
       <c r="AE45" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="6" t="s">
         <v>84</v>
@@ -3732,8 +3864,8 @@
         <v>85</v>
       </c>
       <c r="D46" s="7"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="51"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="45"/>
       <c r="G46" s="6">
         <v>1199</v>
       </c>
@@ -3762,7 +3894,7 @@
       <c r="AD46" s="5"/>
       <c r="AE46" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="20">
         <v>3</v>
@@ -3803,7 +3935,7 @@
       <c r="AD47" s="5"/>
       <c r="AE47" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row r="48" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="6" t="s">
         <v>13</v>
@@ -3819,7 +3951,7 @@
       <c r="G48" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H48" s="52" t="s">
+      <c r="H48" s="46" t="s">
         <v>90</v>
       </c>
       <c r="I48" s="8" t="s">
@@ -3852,7 +3984,7 @@
       <c r="AD48" s="5"/>
       <c r="AE48" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row r="49" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="6"/>
       <c r="C49" s="5" t="s">
@@ -3891,7 +4023,7 @@
       <c r="AD49" s="5"/>
       <c r="AE49" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="6"/>
       <c r="C50" s="5" t="s">
@@ -3930,7 +4062,7 @@
       <c r="AD50" s="5"/>
       <c r="AE50" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row r="51" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="6" t="s">
         <v>19</v>
@@ -3973,7 +4105,7 @@
       <c r="AD51" s="5"/>
       <c r="AE51" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row r="52" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="6" t="s">
         <v>24</v>
@@ -4014,7 +4146,7 @@
       <c r="AD52" s="5"/>
       <c r="AE52" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row r="53" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="6" t="s">
         <v>30</v>
@@ -4055,7 +4187,7 @@
       <c r="AD53" s="5"/>
       <c r="AE53" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row r="54" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="6" t="s">
         <v>46</v>
@@ -4100,7 +4232,7 @@
       <c r="AD54" s="5"/>
       <c r="AE54" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row r="55" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="6" t="s">
         <v>49</v>
@@ -4141,12 +4273,12 @@
       <c r="AD55" s="5"/>
       <c r="AE55" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row r="56" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="6"/>
       <c r="C56" s="5"/>
       <c r="D56" s="7"/>
-      <c r="E56" s="50"/>
+      <c r="E56" s="44"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="8"/>
@@ -4158,7 +4290,7 @@
       <c r="N56" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="O56" s="45">
+      <c r="O56" s="39">
         <v>50000</v>
       </c>
       <c r="P56" s="8"/>
@@ -4178,7 +4310,7 @@
       <c r="AD56" s="5"/>
       <c r="AE56" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row r="57" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="20">
         <v>4</v>
@@ -4187,8 +4319,8 @@
         <v>109</v>
       </c>
       <c r="D57" s="7"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="51"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="45"/>
       <c r="G57" s="6"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -4219,7 +4351,7 @@
       <c r="AD57" s="5"/>
       <c r="AE57" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row r="58" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="6" t="s">
         <v>13</v>
@@ -4260,7 +4392,7 @@
       <c r="AD58" s="5"/>
       <c r="AE58" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row r="59" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="6" t="s">
         <v>19</v>
@@ -4301,7 +4433,7 @@
       <c r="AD59" s="5"/>
       <c r="AE59" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row r="60" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="6"/>
       <c r="C60" s="5"/>
@@ -4318,7 +4450,7 @@
       <c r="N60" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="O60" s="53">
+      <c r="O60" s="47">
         <v>1.4269675925925926</v>
       </c>
       <c r="P60" s="8"/>
@@ -4338,7 +4470,7 @@
       <c r="AD60" s="5"/>
       <c r="AE60" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row r="61" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="20">
         <v>5</v>
@@ -4347,8 +4479,8 @@
         <v>116</v>
       </c>
       <c r="D61" s="7"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="45"/>
       <c r="G61" s="6"/>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -4359,7 +4491,7 @@
       <c r="N61" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="O61" s="45">
+      <c r="O61" s="39">
         <v>987</v>
       </c>
       <c r="P61" s="8"/>
@@ -4379,7 +4511,7 @@
       <c r="AD61" s="5"/>
       <c r="AE61" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row r="62" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="6"/>
       <c r="C62" s="5" t="s">
@@ -4402,7 +4534,7 @@
       <c r="N62" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="O62" s="45">
+      <c r="O62" s="39">
         <v>781371</v>
       </c>
       <c r="P62" s="8"/>
@@ -4422,7 +4554,7 @@
       <c r="AD62" s="5"/>
       <c r="AE62" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row r="63" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="6"/>
       <c r="C63" s="5" t="s">
@@ -4467,14 +4599,14 @@
       <c r="AD63" s="5"/>
       <c r="AE63" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row r="64" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="6"/>
       <c r="C64" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D64" s="7"/>
-      <c r="E64" s="50"/>
+      <c r="E64" s="44"/>
       <c r="F64" s="20" t="s">
         <v>15</v>
       </c>
@@ -4506,7 +4638,7 @@
       <c r="AD64" s="5"/>
       <c r="AE64" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row r="65" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="6"/>
       <c r="C65" s="5" t="s">
@@ -4545,7 +4677,7 @@
       <c r="AD65" s="5"/>
       <c r="AE65" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row r="66" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="6"/>
       <c r="C66" s="5"/>
@@ -4578,7 +4710,7 @@
       <c r="AD66" s="5"/>
       <c r="AE66" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row r="67" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="6"/>
       <c r="C67" s="5"/>
@@ -4611,7 +4743,7 @@
       <c r="AD67" s="5"/>
       <c r="AE67" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row r="68" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="20">
         <v>6</v>
@@ -4648,7 +4780,7 @@
       <c r="AD68" s="5"/>
       <c r="AE68" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row r="69" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="20"/>
       <c r="C69" s="5" t="s">
@@ -4691,7 +4823,7 @@
       <c r="AD69" s="5"/>
       <c r="AE69" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row r="70" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="20"/>
       <c r="C70" s="5" t="s">
@@ -4730,7 +4862,7 @@
       <c r="AD70" s="5"/>
       <c r="AE70" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row r="71" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="20"/>
       <c r="C71" s="5" t="s">
@@ -4769,7 +4901,7 @@
       <c r="AD71" s="5"/>
       <c r="AE71" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row r="72" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="6"/>
       <c r="C72" s="5" t="s">
@@ -4806,7 +4938,7 @@
       <c r="AD72" s="5"/>
       <c r="AE72" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row r="73" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="20">
         <v>7</v>
@@ -4847,7 +4979,7 @@
       <c r="AD73" s="5"/>
       <c r="AE73" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row r="74" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="20"/>
       <c r="C74" s="10"/>
@@ -4880,7 +5012,7 @@
       <c r="AD74" s="5"/>
       <c r="AE74" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row r="75" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="20">
         <v>8</v>
@@ -4921,7 +5053,7 @@
       <c r="AD75" s="5"/>
       <c r="AE75" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row r="76" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="6"/>
       <c r="C76" s="5"/>
@@ -4954,7 +5086,7 @@
       <c r="AD76" s="5"/>
       <c r="AE76" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row r="77" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="20">
         <v>9</v>
@@ -4963,8 +5095,8 @@
         <v>140</v>
       </c>
       <c r="D77" s="7"/>
-      <c r="E77" s="50"/>
-      <c r="F77" s="51"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="45"/>
       <c r="G77" s="6"/>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -4991,15 +5123,15 @@
       <c r="AD77" s="5"/>
       <c r="AE77" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row r="78" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="20"/>
       <c r="C78" s="5" t="s">
         <v>141</v>
       </c>
       <c r="D78" s="7"/>
-      <c r="E78" s="50"/>
-      <c r="F78" s="51"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="45"/>
       <c r="G78" s="6"/>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
@@ -5026,20 +5158,20 @@
       <c r="AD78" s="5"/>
       <c r="AE78" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row r="79" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="20"/>
-      <c r="C79" s="54" t="s">
+      <c r="C79" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="D79" s="7"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="6"/>
+      <c r="D79" s="157"/>
+      <c r="E79" s="158"/>
+      <c r="F79" s="159"/>
+      <c r="G79" s="159"/>
+      <c r="H79" s="158"/>
+      <c r="I79" s="158"/>
+      <c r="J79" s="158"/>
+      <c r="K79" s="159"/>
       <c r="L79" s="5"/>
       <c r="M79" s="6"/>
       <c r="N79" s="8"/>
@@ -5061,7 +5193,7 @@
       <c r="AD79" s="5"/>
       <c r="AE79" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row r="80" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="6"/>
       <c r="C80" s="5"/>
@@ -5098,7 +5230,7 @@
       <c r="AD80" s="5"/>
       <c r="AE80" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row r="81" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="20">
         <v>10</v>
@@ -5139,20 +5271,20 @@
       <c r="AD81" s="5"/>
       <c r="AE81" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row r="82" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
       <c r="B82" s="20"/>
-      <c r="C82" s="54" t="s">
+      <c r="C82" s="167" t="s">
         <v>147</v>
       </c>
-      <c r="D82" s="7"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="6"/>
+      <c r="D82" s="157"/>
+      <c r="E82" s="158"/>
+      <c r="F82" s="159"/>
+      <c r="G82" s="159"/>
+      <c r="H82" s="158"/>
+      <c r="I82" s="158"/>
+      <c r="J82" s="158"/>
+      <c r="K82" s="159"/>
       <c r="L82" s="5"/>
       <c r="M82" s="6"/>
       <c r="N82" s="8"/>
@@ -5174,8 +5306,8 @@
       <c r="AD82" s="5"/>
       <c r="AE82" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="55"/>
+    <row r="83" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="49"/>
       <c r="B83" s="6"/>
       <c r="C83" s="5"/>
       <c r="D83" s="7"/>
@@ -5207,7 +5339,7 @@
       <c r="AD83" s="5"/>
       <c r="AE83" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row r="84" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
       <c r="B84" s="20">
         <v>11</v>
@@ -5244,7 +5376,7 @@
       <c r="AD84" s="5"/>
       <c r="AE84" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row r="85" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
       <c r="B85" s="20"/>
       <c r="C85" s="5" t="s">
@@ -5279,7 +5411,7 @@
       <c r="AD85" s="5"/>
       <c r="AE85" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row r="86" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
       <c r="B86" s="20"/>
       <c r="C86" s="5"/>
@@ -5312,7 +5444,7 @@
       <c r="AD86" s="5"/>
       <c r="AE86" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row r="87" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
       <c r="B87" s="20">
         <v>12</v>
@@ -5349,9 +5481,9 @@
       <c r="AD87" s="5"/>
       <c r="AE87" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row r="88" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
-      <c r="B88" s="45">
+      <c r="B88" s="39">
         <v>1</v>
       </c>
       <c r="C88" s="5" t="s">
@@ -5386,9 +5518,9 @@
       <c r="AD88" s="5"/>
       <c r="AE88" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row r="89" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
-      <c r="B89" s="45">
+      <c r="B89" s="39">
         <v>2</v>
       </c>
       <c r="C89" s="5" t="s">
@@ -5427,9 +5559,9 @@
       <c r="AD89" s="5"/>
       <c r="AE89" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row r="90" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
-      <c r="B90" s="45">
+      <c r="B90" s="39">
         <v>3</v>
       </c>
       <c r="C90" s="5" t="s">
@@ -5468,9 +5600,9 @@
       <c r="AD90" s="5"/>
       <c r="AE90" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row r="91" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
-      <c r="B91" s="45">
+      <c r="B91" s="39">
         <v>4</v>
       </c>
       <c r="C91" s="10" t="s">
@@ -5509,9 +5641,9 @@
       <c r="AD91" s="5"/>
       <c r="AE91" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row r="92" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
-      <c r="B92" s="45"/>
+      <c r="B92" s="39"/>
       <c r="C92" s="10"/>
       <c r="D92" s="7"/>
       <c r="E92" s="8"/>
@@ -5542,7 +5674,7 @@
       <c r="AD92" s="5"/>
       <c r="AE92" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row r="93" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="20">
         <v>13</v>
@@ -5579,7 +5711,7 @@
       <c r="AD93" s="5"/>
       <c r="AE93" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row r="94" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="20"/>
       <c r="C94" s="5"/>
@@ -5612,19 +5744,19 @@
       <c r="AD94" s="5"/>
       <c r="AE94" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+    <row r="95" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
-      <c r="B95" s="56"/>
-      <c r="C95" s="57"/>
+      <c r="B95" s="50"/>
+      <c r="C95" s="51"/>
       <c r="D95" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="E95" s="58"/>
-      <c r="F95" s="59"/>
-      <c r="G95" s="60"/>
-      <c r="H95" s="58"/>
-      <c r="I95" s="58"/>
-      <c r="J95" s="61">
+      <c r="E95" s="52"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="52"/>
+      <c r="I95" s="52"/>
+      <c r="J95" s="55">
         <v>500</v>
       </c>
       <c r="K95" s="6"/>
@@ -5649,24 +5781,26 @@
       <c r="AD95" s="5"/>
       <c r="AE95" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+    <row r="96" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
-      <c r="B96" s="62" t="s">
+      <c r="B96" s="56" t="s">
         <v>159</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="7"/>
       <c r="E96" s="15"/>
-      <c r="F96" s="63">
+      <c r="F96" s="57">
         <f>E262</f>
+        <v>-119.88888888888889</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>160</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
-      <c r="J96" s="64">
+      <c r="J96" s="58">
         <f>IF(F96&lt;0.5,0,IF(F96&lt;1,5,IF(F96&lt;2,10,IF(F96&lt;3,15,IF(F96&lt;4,25,IF(F96&lt;5,35,IF(F96&lt;10,40,50)))))))</f>
+        <v>0</v>
       </c>
       <c r="K96" s="6"/>
       <c r="L96" s="5"/>
@@ -5690,23 +5824,23 @@
       <c r="AD96" s="5"/>
       <c r="AE96" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+    <row r="97" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
-      <c r="B97" s="56" t="s">
+      <c r="B97" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="C97" s="57"/>
+      <c r="C97" s="51"/>
       <c r="D97" s="29"/>
       <c r="E97" s="8"/>
-      <c r="F97" s="65">
+      <c r="F97" s="59">
         <v>18</v>
       </c>
-      <c r="G97" s="60" t="s">
+      <c r="G97" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="H97" s="58"/>
-      <c r="I97" s="58"/>
-      <c r="J97" s="65">
+      <c r="H97" s="52"/>
+      <c r="I97" s="52"/>
+      <c r="J97" s="59">
         <v>18</v>
       </c>
       <c r="K97" s="6"/>
@@ -5731,14 +5865,14 @@
       <c r="AD97" s="5"/>
       <c r="AE97" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+    <row r="98" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
-      <c r="B98" s="66"/>
-      <c r="C98" s="67"/>
-      <c r="D98" s="68"/>
-      <c r="E98" s="69"/>
-      <c r="F98" s="66"/>
-      <c r="G98" s="66"/>
+      <c r="B98" s="60"/>
+      <c r="C98" s="61"/>
+      <c r="D98" s="62"/>
+      <c r="E98" s="63"/>
+      <c r="F98" s="60"/>
+      <c r="G98" s="60"/>
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
@@ -5764,7 +5898,7 @@
       <c r="AD98" s="5"/>
       <c r="AE98" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+    <row r="99" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
       <c r="B99" s="12"/>
       <c r="C99" s="13"/>
@@ -5803,32 +5937,32 @@
       <c r="AD99" s="5"/>
       <c r="AE99" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+    <row r="100" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
-      <c r="B100" s="70" t="s">
+      <c r="B100" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="C100" s="71" t="s">
+      <c r="C100" s="65" t="s">
         <v>165</v>
       </c>
       <c r="D100" s="14"/>
-      <c r="E100" s="72"/>
-      <c r="F100" s="73" t="s">
+      <c r="E100" s="66"/>
+      <c r="F100" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="G100" s="73" t="s">
+      <c r="G100" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="H100" s="74" t="s">
+      <c r="H100" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="I100" s="75" t="s">
+      <c r="I100" s="69" t="s">
         <v>169</v>
       </c>
       <c r="J100" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="K100" s="76" t="s">
+      <c r="K100" s="70" t="s">
         <v>171</v>
       </c>
       <c r="L100" s="5"/>
@@ -5852,26 +5986,26 @@
       <c r="AD100" s="5"/>
       <c r="AE100" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+    <row r="101" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
-      <c r="B101" s="37">
+      <c r="B101" s="34">
         <v>1</v>
       </c>
-      <c r="C101" s="77" t="s">
+      <c r="C101" s="71" t="s">
         <v>172</v>
       </c>
       <c r="D101" s="7"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="79">
+      <c r="E101" s="72"/>
+      <c r="F101" s="73">
         <v>1560</v>
       </c>
-      <c r="G101" s="79">
+      <c r="G101" s="73">
         <v>1210.93</v>
       </c>
-      <c r="H101" s="79"/>
-      <c r="I101" s="79"/>
+      <c r="H101" s="73"/>
+      <c r="I101" s="73"/>
       <c r="J101" s="8"/>
-      <c r="K101" s="45">
+      <c r="K101" s="39">
         <v>1</v>
       </c>
       <c r="L101" s="5"/>
@@ -5895,26 +6029,26 @@
       <c r="AD101" s="5"/>
       <c r="AE101" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+    <row r="102" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
-      <c r="B102" s="80">
+      <c r="B102" s="74">
         <v>2</v>
       </c>
-      <c r="C102" s="81" t="s">
+      <c r="C102" s="75" t="s">
         <v>173</v>
       </c>
       <c r="D102" s="7"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="79">
+      <c r="E102" s="72"/>
+      <c r="F102" s="73">
         <v>1480</v>
       </c>
-      <c r="G102" s="79">
+      <c r="G102" s="73">
         <v>992.18</v>
       </c>
-      <c r="H102" s="79"/>
-      <c r="I102" s="79"/>
+      <c r="H102" s="73"/>
+      <c r="I102" s="73"/>
       <c r="J102" s="8"/>
-      <c r="K102" s="45">
+      <c r="K102" s="39">
         <v>2</v>
       </c>
       <c r="L102" s="5"/>
@@ -5938,26 +6072,26 @@
       <c r="AD102" s="5"/>
       <c r="AE102" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+    <row r="103" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
-      <c r="B103" s="80">
+      <c r="B103" s="74">
         <v>3</v>
       </c>
-      <c r="C103" s="81" t="s">
+      <c r="C103" s="75" t="s">
         <v>174</v>
       </c>
       <c r="D103" s="7"/>
-      <c r="E103" s="78"/>
-      <c r="F103" s="79">
+      <c r="E103" s="72"/>
+      <c r="F103" s="73">
         <v>8570</v>
       </c>
-      <c r="G103" s="82" t="s">
+      <c r="G103" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H103" s="79">
+      <c r="H103" s="73">
         <v>500</v>
       </c>
-      <c r="I103" s="79"/>
+      <c r="I103" s="73"/>
       <c r="J103" s="8"/>
       <c r="K103" s="6"/>
       <c r="L103" s="5"/>
@@ -5981,26 +6115,26 @@
       <c r="AD103" s="5"/>
       <c r="AE103" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+    <row r="104" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
-      <c r="B104" s="80">
+      <c r="B104" s="74">
         <v>4</v>
       </c>
-      <c r="C104" s="81" t="s">
+      <c r="C104" s="75" t="s">
         <v>176</v>
       </c>
       <c r="D104" s="7"/>
-      <c r="E104" s="78"/>
-      <c r="F104" s="79">
+      <c r="E104" s="72"/>
+      <c r="F104" s="73">
         <v>8861</v>
       </c>
-      <c r="G104" s="82" t="s">
+      <c r="G104" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H104" s="79">
+      <c r="H104" s="73">
         <v>5</v>
       </c>
-      <c r="I104" s="79"/>
+      <c r="I104" s="73"/>
       <c r="J104" s="8"/>
       <c r="K104" s="6"/>
       <c r="L104" s="5"/>
@@ -6024,26 +6158,26 @@
       <c r="AD104" s="5"/>
       <c r="AE104" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+    <row r="105" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
-      <c r="B105" s="80">
+      <c r="B105" s="74">
         <v>5</v>
       </c>
-      <c r="C105" s="81" t="s">
+      <c r="C105" s="75" t="s">
         <v>177</v>
       </c>
       <c r="D105" s="7"/>
-      <c r="E105" s="78"/>
-      <c r="F105" s="79">
+      <c r="E105" s="72"/>
+      <c r="F105" s="73">
         <v>9110</v>
       </c>
-      <c r="G105" s="82" t="s">
+      <c r="G105" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H105" s="79">
+      <c r="H105" s="73">
         <v>5</v>
       </c>
-      <c r="I105" s="79"/>
+      <c r="I105" s="73"/>
       <c r="J105" s="8"/>
       <c r="K105" s="6"/>
       <c r="L105" s="5"/>
@@ -6067,26 +6201,26 @@
       <c r="AD105" s="5"/>
       <c r="AE105" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+    <row r="106" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
-      <c r="B106" s="80">
+      <c r="B106" s="74">
         <v>6</v>
       </c>
-      <c r="C106" s="81" t="s">
+      <c r="C106" s="75" t="s">
         <v>178</v>
       </c>
       <c r="D106" s="7"/>
-      <c r="E106" s="78"/>
-      <c r="F106" s="79">
+      <c r="E106" s="72"/>
+      <c r="F106" s="73">
         <v>3030</v>
       </c>
-      <c r="G106" s="82" t="s">
+      <c r="G106" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H106" s="79">
+      <c r="H106" s="73">
         <v>4</v>
       </c>
-      <c r="I106" s="79"/>
+      <c r="I106" s="73"/>
       <c r="J106" s="8"/>
       <c r="K106" s="6"/>
       <c r="L106" s="5"/>
@@ -6110,24 +6244,24 @@
       <c r="AD106" s="5"/>
       <c r="AE106" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+    <row r="107" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
-      <c r="B107" s="80">
+      <c r="B107" s="74">
         <v>7</v>
       </c>
-      <c r="C107" s="81" t="s">
+      <c r="C107" s="75" t="s">
         <v>179</v>
       </c>
       <c r="D107" s="7"/>
-      <c r="E107" s="78"/>
-      <c r="F107" s="79">
+      <c r="E107" s="72"/>
+      <c r="F107" s="73">
         <v>1560</v>
       </c>
-      <c r="G107" s="82" t="s">
+      <c r="G107" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H107" s="79"/>
-      <c r="I107" s="79">
+      <c r="H107" s="73"/>
+      <c r="I107" s="73">
         <v>5</v>
       </c>
       <c r="J107" s="8"/>
@@ -6153,26 +6287,26 @@
       <c r="AD107" s="5"/>
       <c r="AE107" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+    <row r="108" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
-      <c r="B108" s="80">
+      <c r="B108" s="74">
         <v>8</v>
       </c>
-      <c r="C108" s="81" t="s">
+      <c r="C108" s="75" t="s">
         <v>180</v>
       </c>
       <c r="D108" s="7"/>
-      <c r="E108" s="78"/>
-      <c r="F108" s="79">
+      <c r="E108" s="72"/>
+      <c r="F108" s="73">
         <v>8570</v>
       </c>
-      <c r="G108" s="82" t="s">
+      <c r="G108" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H108" s="79">
+      <c r="H108" s="73">
         <v>4</v>
       </c>
-      <c r="I108" s="79"/>
+      <c r="I108" s="73"/>
       <c r="J108" s="8"/>
       <c r="K108" s="6"/>
       <c r="L108" s="5"/>
@@ -6196,26 +6330,26 @@
       <c r="AD108" s="5"/>
       <c r="AE108" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+    <row r="109" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
-      <c r="B109" s="80">
+      <c r="B109" s="74">
         <v>9</v>
       </c>
-      <c r="C109" s="81" t="s">
+      <c r="C109" s="75" t="s">
         <v>181</v>
       </c>
       <c r="D109" s="7"/>
-      <c r="E109" s="78"/>
-      <c r="F109" s="79">
+      <c r="E109" s="72"/>
+      <c r="F109" s="73">
         <v>9110</v>
       </c>
-      <c r="G109" s="82" t="s">
+      <c r="G109" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H109" s="79">
+      <c r="H109" s="73">
         <v>4</v>
       </c>
-      <c r="I109" s="79"/>
+      <c r="I109" s="73"/>
       <c r="J109" s="8"/>
       <c r="K109" s="6"/>
       <c r="L109" s="5"/>
@@ -6239,24 +6373,24 @@
       <c r="AD109" s="5"/>
       <c r="AE109" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
+    <row r="110" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
-      <c r="B110" s="80">
+      <c r="B110" s="74">
         <v>10</v>
       </c>
-      <c r="C110" s="81" t="s">
+      <c r="C110" s="75" t="s">
         <v>182</v>
       </c>
       <c r="D110" s="7"/>
-      <c r="E110" s="78"/>
-      <c r="F110" s="79">
+      <c r="E110" s="72"/>
+      <c r="F110" s="73">
         <v>8861</v>
       </c>
-      <c r="G110" s="82" t="s">
+      <c r="G110" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H110" s="79"/>
-      <c r="I110" s="79">
+      <c r="H110" s="73"/>
+      <c r="I110" s="73">
         <v>5</v>
       </c>
       <c r="J110" s="8"/>
@@ -6282,24 +6416,24 @@
       <c r="AD110" s="5"/>
       <c r="AE110" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+    <row r="111" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
-      <c r="B111" s="80">
+      <c r="B111" s="74">
         <v>11</v>
       </c>
-      <c r="C111" s="81" t="s">
+      <c r="C111" s="75" t="s">
         <v>183</v>
       </c>
       <c r="D111" s="7"/>
-      <c r="E111" s="78"/>
-      <c r="F111" s="79">
+      <c r="E111" s="72"/>
+      <c r="F111" s="73">
         <v>2270</v>
       </c>
-      <c r="G111" s="82" t="s">
+      <c r="G111" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H111" s="79"/>
-      <c r="I111" s="79">
+      <c r="H111" s="73"/>
+      <c r="I111" s="73">
         <v>4</v>
       </c>
       <c r="J111" s="8"/>
@@ -6325,26 +6459,26 @@
       <c r="AD111" s="5"/>
       <c r="AE111" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
+    <row r="112" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
-      <c r="B112" s="80">
+      <c r="B112" s="74">
         <v>12</v>
       </c>
-      <c r="C112" s="81" t="s">
+      <c r="C112" s="75" t="s">
         <v>184</v>
       </c>
       <c r="D112" s="7"/>
-      <c r="E112" s="78"/>
-      <c r="F112" s="79">
+      <c r="E112" s="72"/>
+      <c r="F112" s="73">
         <v>2270</v>
       </c>
-      <c r="G112" s="82" t="s">
+      <c r="G112" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H112" s="79">
+      <c r="H112" s="73">
         <v>5</v>
       </c>
-      <c r="I112" s="79"/>
+      <c r="I112" s="73"/>
       <c r="J112" s="8"/>
       <c r="K112" s="6"/>
       <c r="L112" s="5"/>
@@ -6368,26 +6502,26 @@
       <c r="AD112" s="5"/>
       <c r="AE112" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+    <row r="113" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
-      <c r="B113" s="80">
+      <c r="B113" s="74">
         <v>13</v>
       </c>
-      <c r="C113" s="81" t="s">
+      <c r="C113" s="75" t="s">
         <v>185</v>
       </c>
       <c r="D113" s="7"/>
-      <c r="E113" s="78"/>
-      <c r="F113" s="79">
+      <c r="E113" s="72"/>
+      <c r="F113" s="73">
         <v>302</v>
       </c>
-      <c r="G113" s="82" t="s">
+      <c r="G113" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H113" s="79">
+      <c r="H113" s="73">
         <v>4</v>
       </c>
-      <c r="I113" s="79"/>
+      <c r="I113" s="73"/>
       <c r="J113" s="8"/>
       <c r="K113" s="6"/>
       <c r="L113" s="5"/>
@@ -6411,24 +6545,24 @@
       <c r="AD113" s="5"/>
       <c r="AE113" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+    <row r="114" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
-      <c r="B114" s="80">
+      <c r="B114" s="74">
         <v>14</v>
       </c>
-      <c r="C114" s="81" t="s">
+      <c r="C114" s="75" t="s">
         <v>186</v>
       </c>
       <c r="D114" s="7"/>
-      <c r="E114" s="78"/>
-      <c r="F114" s="79">
+      <c r="E114" s="72"/>
+      <c r="F114" s="73">
         <v>3560</v>
       </c>
-      <c r="G114" s="82" t="s">
+      <c r="G114" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H114" s="79"/>
-      <c r="I114" s="79">
+      <c r="H114" s="73"/>
+      <c r="I114" s="73">
         <v>5</v>
       </c>
       <c r="J114" s="8"/>
@@ -6454,26 +6588,26 @@
       <c r="AD114" s="5"/>
       <c r="AE114" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+    <row r="115" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
-      <c r="B115" s="80">
+      <c r="B115" s="74">
         <v>15</v>
       </c>
-      <c r="C115" s="81" t="s">
+      <c r="C115" s="75" t="s">
         <v>187</v>
       </c>
       <c r="D115" s="7"/>
-      <c r="E115" s="78"/>
-      <c r="F115" s="79">
+      <c r="E115" s="72"/>
+      <c r="F115" s="73">
         <v>70000</v>
       </c>
-      <c r="G115" s="82" t="s">
+      <c r="G115" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="H115" s="79">
+      <c r="H115" s="73">
         <v>4</v>
       </c>
-      <c r="I115" s="79"/>
+      <c r="I115" s="73"/>
       <c r="J115" s="8"/>
       <c r="K115" s="6"/>
       <c r="L115" s="5"/>
@@ -6497,28 +6631,28 @@
       <c r="AD115" s="5"/>
       <c r="AE115" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+    <row r="116" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
-      <c r="B116" s="80">
+      <c r="B116" s="74">
         <v>16</v>
       </c>
-      <c r="C116" s="81" t="s">
+      <c r="C116" s="75" t="s">
         <v>188</v>
       </c>
       <c r="D116" s="7"/>
-      <c r="E116" s="78"/>
-      <c r="F116" s="79">
+      <c r="E116" s="72"/>
+      <c r="F116" s="73">
         <v>100</v>
       </c>
-      <c r="G116" s="79"/>
-      <c r="H116" s="79">
+      <c r="G116" s="73"/>
+      <c r="H116" s="73">
         <v>4</v>
       </c>
-      <c r="I116" s="79"/>
-      <c r="J116" s="83">
+      <c r="I116" s="73"/>
+      <c r="J116" s="77">
         <v>1771.18</v>
       </c>
-      <c r="K116" s="45">
+      <c r="K116" s="39">
         <v>3</v>
       </c>
       <c r="L116" s="5"/>
@@ -6542,28 +6676,28 @@
       <c r="AD116" s="5"/>
       <c r="AE116" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
+    <row r="117" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
-      <c r="B117" s="80">
+      <c r="B117" s="74">
         <v>17</v>
       </c>
-      <c r="C117" s="81" t="s">
+      <c r="C117" s="75" t="s">
         <v>189</v>
       </c>
       <c r="D117" s="7"/>
-      <c r="E117" s="78"/>
-      <c r="F117" s="79">
+      <c r="E117" s="72"/>
+      <c r="F117" s="73">
         <v>12</v>
       </c>
-      <c r="G117" s="79"/>
-      <c r="H117" s="79"/>
-      <c r="I117" s="79">
+      <c r="G117" s="73"/>
+      <c r="H117" s="73"/>
+      <c r="I117" s="73">
         <v>4</v>
       </c>
-      <c r="J117" s="76">
+      <c r="J117" s="70">
         <v>20000</v>
       </c>
-      <c r="K117" s="45">
+      <c r="K117" s="39">
         <v>4</v>
       </c>
       <c r="L117" s="5"/>
@@ -6587,16 +6721,16 @@
       <c r="AD117" s="5"/>
       <c r="AE117" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
+    <row r="118" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
-      <c r="B118" s="80"/>
+      <c r="B118" s="74"/>
       <c r="C118" s="5"/>
       <c r="D118" s="7"/>
-      <c r="E118" s="78"/>
-      <c r="F118" s="79"/>
-      <c r="G118" s="79"/>
-      <c r="H118" s="79"/>
-      <c r="I118" s="79"/>
+      <c r="E118" s="72"/>
+      <c r="F118" s="73"/>
+      <c r="G118" s="73"/>
+      <c r="H118" s="73"/>
+      <c r="I118" s="73"/>
       <c r="J118" s="8"/>
       <c r="K118" s="6"/>
       <c r="L118" s="5"/>
@@ -6620,16 +6754,16 @@
       <c r="AD118" s="5"/>
       <c r="AE118" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
+    <row r="119" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
-      <c r="B119" s="80"/>
+      <c r="B119" s="74"/>
       <c r="C119" s="5"/>
       <c r="D119" s="7"/>
-      <c r="E119" s="78"/>
-      <c r="F119" s="79"/>
-      <c r="G119" s="79"/>
-      <c r="H119" s="79"/>
-      <c r="I119" s="79"/>
+      <c r="E119" s="72"/>
+      <c r="F119" s="73"/>
+      <c r="G119" s="73"/>
+      <c r="H119" s="73"/>
+      <c r="I119" s="73"/>
       <c r="J119" s="8"/>
       <c r="K119" s="6"/>
       <c r="L119" s="5"/>
@@ -6653,16 +6787,16 @@
       <c r="AD119" s="5"/>
       <c r="AE119" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+    <row r="120" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
-      <c r="B120" s="80"/>
+      <c r="B120" s="74"/>
       <c r="C120" s="5"/>
       <c r="D120" s="7"/>
-      <c r="E120" s="78"/>
-      <c r="F120" s="79"/>
-      <c r="G120" s="79"/>
-      <c r="H120" s="79"/>
-      <c r="I120" s="79"/>
+      <c r="E120" s="72"/>
+      <c r="F120" s="73"/>
+      <c r="G120" s="73"/>
+      <c r="H120" s="73"/>
+      <c r="I120" s="73"/>
       <c r="J120" s="8"/>
       <c r="K120" s="6"/>
       <c r="L120" s="5"/>
@@ -6686,16 +6820,16 @@
       <c r="AD120" s="5"/>
       <c r="AE120" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
+    <row r="121" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
-      <c r="B121" s="80"/>
+      <c r="B121" s="74"/>
       <c r="C121" s="5"/>
       <c r="D121" s="7"/>
-      <c r="E121" s="78"/>
-      <c r="F121" s="79"/>
-      <c r="G121" s="79"/>
-      <c r="H121" s="79"/>
-      <c r="I121" s="79"/>
+      <c r="E121" s="72"/>
+      <c r="F121" s="73"/>
+      <c r="G121" s="73"/>
+      <c r="H121" s="73"/>
+      <c r="I121" s="73"/>
       <c r="J121" s="8"/>
       <c r="K121" s="6"/>
       <c r="L121" s="5"/>
@@ -6719,16 +6853,16 @@
       <c r="AD121" s="5"/>
       <c r="AE121" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
+    <row r="122" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
-      <c r="B122" s="80"/>
+      <c r="B122" s="74"/>
       <c r="C122" s="5"/>
       <c r="D122" s="7"/>
-      <c r="E122" s="78"/>
-      <c r="F122" s="79"/>
-      <c r="G122" s="79"/>
-      <c r="H122" s="79"/>
-      <c r="I122" s="79"/>
+      <c r="E122" s="72"/>
+      <c r="F122" s="73"/>
+      <c r="G122" s="73"/>
+      <c r="H122" s="73"/>
+      <c r="I122" s="73"/>
       <c r="J122" s="8"/>
       <c r="K122" s="6"/>
       <c r="L122" s="5"/>
@@ -6752,16 +6886,16 @@
       <c r="AD122" s="5"/>
       <c r="AE122" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
+    <row r="123" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
-      <c r="B123" s="80"/>
+      <c r="B123" s="74"/>
       <c r="C123" s="5"/>
       <c r="D123" s="7"/>
-      <c r="E123" s="78"/>
-      <c r="F123" s="79"/>
-      <c r="G123" s="79"/>
-      <c r="H123" s="79"/>
-      <c r="I123" s="79"/>
+      <c r="E123" s="72"/>
+      <c r="F123" s="73"/>
+      <c r="G123" s="73"/>
+      <c r="H123" s="73"/>
+      <c r="I123" s="73"/>
       <c r="J123" s="8"/>
       <c r="K123" s="6"/>
       <c r="L123" s="5"/>
@@ -6785,16 +6919,16 @@
       <c r="AD123" s="5"/>
       <c r="AE123" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
+    <row r="124" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
-      <c r="B124" s="80"/>
+      <c r="B124" s="74"/>
       <c r="C124" s="5"/>
       <c r="D124" s="7"/>
-      <c r="E124" s="78"/>
-      <c r="F124" s="79"/>
-      <c r="G124" s="79"/>
-      <c r="H124" s="79"/>
-      <c r="I124" s="79"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="73"/>
+      <c r="G124" s="73"/>
+      <c r="H124" s="73"/>
+      <c r="I124" s="73"/>
       <c r="J124" s="8"/>
       <c r="K124" s="6"/>
       <c r="L124" s="5"/>
@@ -6818,16 +6952,16 @@
       <c r="AD124" s="5"/>
       <c r="AE124" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
+    <row r="125" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
-      <c r="B125" s="80"/>
+      <c r="B125" s="74"/>
       <c r="C125" s="5"/>
       <c r="D125" s="7"/>
-      <c r="E125" s="78"/>
-      <c r="F125" s="79"/>
-      <c r="G125" s="79"/>
-      <c r="H125" s="79"/>
-      <c r="I125" s="79"/>
+      <c r="E125" s="72"/>
+      <c r="F125" s="73"/>
+      <c r="G125" s="73"/>
+      <c r="H125" s="73"/>
+      <c r="I125" s="73"/>
       <c r="J125" s="8"/>
       <c r="K125" s="6"/>
       <c r="L125" s="5"/>
@@ -6851,16 +6985,16 @@
       <c r="AD125" s="5"/>
       <c r="AE125" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
+    <row r="126" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
-      <c r="B126" s="80"/>
+      <c r="B126" s="74"/>
       <c r="C126" s="5"/>
       <c r="D126" s="7"/>
-      <c r="E126" s="78"/>
-      <c r="F126" s="79"/>
-      <c r="G126" s="79"/>
-      <c r="H126" s="79"/>
-      <c r="I126" s="79"/>
+      <c r="E126" s="72"/>
+      <c r="F126" s="73"/>
+      <c r="G126" s="73"/>
+      <c r="H126" s="73"/>
+      <c r="I126" s="73"/>
       <c r="J126" s="8"/>
       <c r="K126" s="6"/>
       <c r="L126" s="5"/>
@@ -6884,16 +7018,16 @@
       <c r="AD126" s="5"/>
       <c r="AE126" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
+    <row r="127" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
-      <c r="B127" s="80"/>
+      <c r="B127" s="74"/>
       <c r="C127" s="5"/>
       <c r="D127" s="7"/>
-      <c r="E127" s="78"/>
-      <c r="F127" s="79"/>
-      <c r="G127" s="79"/>
-      <c r="H127" s="79"/>
-      <c r="I127" s="79"/>
+      <c r="E127" s="72"/>
+      <c r="F127" s="73"/>
+      <c r="G127" s="73"/>
+      <c r="H127" s="73"/>
+      <c r="I127" s="73"/>
       <c r="J127" s="8"/>
       <c r="K127" s="6"/>
       <c r="L127" s="5"/>
@@ -6917,16 +7051,16 @@
       <c r="AD127" s="5"/>
       <c r="AE127" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
+    <row r="128" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
-      <c r="B128" s="80"/>
+      <c r="B128" s="74"/>
       <c r="C128" s="5"/>
       <c r="D128" s="7"/>
-      <c r="E128" s="78"/>
-      <c r="F128" s="79"/>
-      <c r="G128" s="79"/>
-      <c r="H128" s="79"/>
-      <c r="I128" s="79"/>
+      <c r="E128" s="72"/>
+      <c r="F128" s="73"/>
+      <c r="G128" s="73"/>
+      <c r="H128" s="73"/>
+      <c r="I128" s="73"/>
       <c r="J128" s="8"/>
       <c r="K128" s="6"/>
       <c r="L128" s="5"/>
@@ -6950,16 +7084,16 @@
       <c r="AD128" s="5"/>
       <c r="AE128" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
+    <row r="129" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
-      <c r="B129" s="80"/>
+      <c r="B129" s="74"/>
       <c r="C129" s="5"/>
       <c r="D129" s="7"/>
-      <c r="E129" s="78"/>
-      <c r="F129" s="79"/>
-      <c r="G129" s="79"/>
-      <c r="H129" s="79"/>
-      <c r="I129" s="79"/>
+      <c r="E129" s="72"/>
+      <c r="F129" s="73"/>
+      <c r="G129" s="73"/>
+      <c r="H129" s="73"/>
+      <c r="I129" s="73"/>
       <c r="J129" s="8"/>
       <c r="K129" s="6"/>
       <c r="L129" s="5"/>
@@ -6983,16 +7117,16 @@
       <c r="AD129" s="5"/>
       <c r="AE129" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
+    <row r="130" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
-      <c r="B130" s="80"/>
+      <c r="B130" s="74"/>
       <c r="C130" s="5"/>
       <c r="D130" s="7"/>
-      <c r="E130" s="78"/>
-      <c r="F130" s="79"/>
-      <c r="G130" s="79"/>
-      <c r="H130" s="79"/>
-      <c r="I130" s="79"/>
+      <c r="E130" s="72"/>
+      <c r="F130" s="73"/>
+      <c r="G130" s="73"/>
+      <c r="H130" s="73"/>
+      <c r="I130" s="73"/>
       <c r="J130" s="8"/>
       <c r="K130" s="6"/>
       <c r="L130" s="5"/>
@@ -7016,16 +7150,16 @@
       <c r="AD130" s="5"/>
       <c r="AE130" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
+    <row r="131" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
-      <c r="B131" s="80"/>
+      <c r="B131" s="74"/>
       <c r="C131" s="5"/>
       <c r="D131" s="7"/>
-      <c r="E131" s="78"/>
-      <c r="F131" s="79"/>
-      <c r="G131" s="79"/>
-      <c r="H131" s="79"/>
-      <c r="I131" s="79"/>
+      <c r="E131" s="72"/>
+      <c r="F131" s="73"/>
+      <c r="G131" s="73"/>
+      <c r="H131" s="73"/>
+      <c r="I131" s="73"/>
       <c r="J131" s="8"/>
       <c r="K131" s="6"/>
       <c r="L131" s="5"/>
@@ -7049,16 +7183,16 @@
       <c r="AD131" s="5"/>
       <c r="AE131" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
+    <row r="132" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
-      <c r="B132" s="80"/>
+      <c r="B132" s="74"/>
       <c r="C132" s="5"/>
       <c r="D132" s="7"/>
-      <c r="E132" s="78"/>
-      <c r="F132" s="79"/>
-      <c r="G132" s="79"/>
-      <c r="H132" s="79"/>
-      <c r="I132" s="79"/>
+      <c r="E132" s="72"/>
+      <c r="F132" s="73"/>
+      <c r="G132" s="73"/>
+      <c r="H132" s="73"/>
+      <c r="I132" s="73"/>
       <c r="J132" s="8"/>
       <c r="K132" s="6"/>
       <c r="L132" s="5"/>
@@ -7082,16 +7216,16 @@
       <c r="AD132" s="5"/>
       <c r="AE132" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
+    <row r="133" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
-      <c r="B133" s="80"/>
+      <c r="B133" s="74"/>
       <c r="C133" s="5"/>
       <c r="D133" s="7"/>
-      <c r="E133" s="78"/>
-      <c r="F133" s="79"/>
-      <c r="G133" s="79"/>
-      <c r="H133" s="79"/>
-      <c r="I133" s="79"/>
+      <c r="E133" s="72"/>
+      <c r="F133" s="73"/>
+      <c r="G133" s="73"/>
+      <c r="H133" s="73"/>
+      <c r="I133" s="73"/>
       <c r="J133" s="8"/>
       <c r="K133" s="6"/>
       <c r="L133" s="5"/>
@@ -7115,16 +7249,16 @@
       <c r="AD133" s="5"/>
       <c r="AE133" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
+    <row r="134" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
-      <c r="B134" s="80"/>
+      <c r="B134" s="74"/>
       <c r="C134" s="5"/>
       <c r="D134" s="7"/>
-      <c r="E134" s="78"/>
-      <c r="F134" s="79"/>
-      <c r="G134" s="79"/>
-      <c r="H134" s="79"/>
-      <c r="I134" s="79"/>
+      <c r="E134" s="72"/>
+      <c r="F134" s="73"/>
+      <c r="G134" s="73"/>
+      <c r="H134" s="73"/>
+      <c r="I134" s="73"/>
       <c r="J134" s="8"/>
       <c r="K134" s="6"/>
       <c r="L134" s="5"/>
@@ -7148,16 +7282,16 @@
       <c r="AD134" s="5"/>
       <c r="AE134" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
+    <row r="135" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
-      <c r="B135" s="84"/>
-      <c r="C135" s="85"/>
-      <c r="D135" s="86"/>
-      <c r="E135" s="87"/>
-      <c r="F135" s="88"/>
-      <c r="G135" s="74"/>
-      <c r="H135" s="89"/>
-      <c r="I135" s="74">
+      <c r="B135" s="78"/>
+      <c r="C135" s="79"/>
+      <c r="D135" s="80"/>
+      <c r="E135" s="81"/>
+      <c r="F135" s="82"/>
+      <c r="G135" s="68"/>
+      <c r="H135" s="83"/>
+      <c r="I135" s="68">
         <v>1000</v>
       </c>
       <c r="J135" s="21"/>
@@ -7183,32 +7317,37 @@
       <c r="AD135" s="5"/>
       <c r="AE135" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
+    <row r="136" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
-      <c r="B136" s="62" t="s">
+      <c r="B136" s="56" t="s">
         <v>190</v>
       </c>
       <c r="C136" s="5"/>
       <c r="D136" s="7"/>
-      <c r="E136" s="78"/>
-      <c r="F136" s="79">
+      <c r="E136" s="72"/>
+      <c r="F136" s="73">
         <f>SUM(F101:F135)</f>
-      </c>
-      <c r="G136" s="90">
+        <v>139226</v>
+      </c>
+      <c r="G136" s="84">
         <f>SUM(G101:G135)</f>
-      </c>
-      <c r="H136" s="91">
+        <v>2203.11</v>
+      </c>
+      <c r="H136" s="85">
         <f>SUM(H101:H135)</f>
-      </c>
-      <c r="I136" s="91">
+        <v>539</v>
+      </c>
+      <c r="I136" s="85">
         <f>SUM(I101:I135)</f>
-      </c>
-      <c r="J136" s="63">
+        <v>1023</v>
+      </c>
+      <c r="J136" s="57">
         <f>SUM(J101:J135)</f>
+        <v>21771.18</v>
       </c>
       <c r="K136" s="6"/>
       <c r="L136" s="5"/>
-      <c r="M136" s="63"/>
+      <c r="M136" s="57"/>
       <c r="N136" s="8"/>
       <c r="O136" s="6"/>
       <c r="P136" s="8"/>
@@ -7228,32 +7367,36 @@
       <c r="AD136" s="5"/>
       <c r="AE136" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
-      <c r="A137" s="92"/>
-      <c r="B137" s="93">
+    <row r="137" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="86"/>
+      <c r="B137" s="87">
         <v>18</v>
       </c>
       <c r="C137" s="13" t="s">
         <v>191</v>
       </c>
       <c r="D137" s="14"/>
-      <c r="E137" s="72"/>
-      <c r="F137" s="94">
+      <c r="E137" s="66"/>
+      <c r="F137" s="88">
         <f>B137*F136/100</f>
-      </c>
-      <c r="G137" s="94">
+        <v>25060.68</v>
+      </c>
+      <c r="G137" s="88">
         <f>B137*G136/100</f>
-      </c>
-      <c r="H137" s="94">
+        <v>396.55980000000005</v>
+      </c>
+      <c r="H137" s="88">
         <f>B137*H136/100</f>
-      </c>
-      <c r="I137" s="94">
+        <v>97.02</v>
+      </c>
+      <c r="I137" s="88">
         <f>18*I136/100</f>
-      </c>
-      <c r="J137" s="63"/>
+        <v>184.14</v>
+      </c>
+      <c r="J137" s="57"/>
       <c r="K137" s="6"/>
       <c r="L137" s="5"/>
-      <c r="M137" s="63"/>
+      <c r="M137" s="57"/>
       <c r="N137" s="8"/>
       <c r="O137" s="6"/>
       <c r="P137" s="8"/>
@@ -7273,27 +7416,31 @@
       <c r="AD137" s="5"/>
       <c r="AE137" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
+    <row r="138" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
-      <c r="B138" s="62" t="s">
+      <c r="B138" s="56" t="s">
         <v>190</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="7"/>
       <c r="E138" s="8"/>
-      <c r="F138" s="90">
+      <c r="F138" s="84">
         <f>SUM(F136:F137)</f>
-      </c>
-      <c r="G138" s="90">
+        <v>164286.68</v>
+      </c>
+      <c r="G138" s="84">
         <f>SUM(G136:G137)</f>
-      </c>
-      <c r="H138" s="90">
+        <v>2599.6698000000001</v>
+      </c>
+      <c r="H138" s="84">
         <f>SUM(H136:H137)</f>
-      </c>
-      <c r="I138" s="91">
+        <v>636.02</v>
+      </c>
+      <c r="I138" s="85">
         <f>SUM(I136:I137)</f>
-      </c>
-      <c r="J138" s="63"/>
+        <v>1207.1399999999999</v>
+      </c>
+      <c r="J138" s="57"/>
       <c r="K138" s="6"/>
       <c r="L138" s="5"/>
       <c r="M138" s="6"/>
@@ -7316,18 +7463,18 @@
       <c r="AD138" s="5"/>
       <c r="AE138" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
+    <row r="139" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
-      <c r="B139" s="95" t="s">
+      <c r="B139" s="89" t="s">
         <v>192</v>
       </c>
       <c r="C139" s="5"/>
       <c r="D139" s="7"/>
       <c r="E139" s="8"/>
-      <c r="F139" s="90"/>
-      <c r="G139" s="90"/>
-      <c r="H139" s="90"/>
-      <c r="I139" s="91"/>
+      <c r="F139" s="84"/>
+      <c r="G139" s="84"/>
+      <c r="H139" s="84"/>
+      <c r="I139" s="85"/>
       <c r="J139" s="8"/>
       <c r="K139" s="6"/>
       <c r="L139" s="5"/>
@@ -7351,27 +7498,30 @@
       <c r="AD139" s="5"/>
       <c r="AE139" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
+    <row r="140" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
-      <c r="B140" s="96">
+      <c r="B140" s="90">
         <f>J96</f>
+        <v>0</v>
       </c>
       <c r="C140" s="13" t="s">
         <v>193</v>
       </c>
       <c r="D140" s="14"/>
-      <c r="E140" s="72"/>
-      <c r="F140" s="97"/>
-      <c r="G140" s="97">
+      <c r="E140" s="66"/>
+      <c r="F140" s="91"/>
+      <c r="G140" s="91">
         <f>B140*G138/100</f>
-      </c>
-      <c r="H140" s="97">
+        <v>0</v>
+      </c>
+      <c r="H140" s="91">
         <f>H138/2</f>
-      </c>
-      <c r="I140" s="91">
+        <v>318.01</v>
+      </c>
+      <c r="I140" s="85">
         <v>0</v>
       </c>
-      <c r="J140" s="63"/>
+      <c r="J140" s="57"/>
       <c r="K140" s="6"/>
       <c r="L140" s="5"/>
       <c r="M140" s="6"/>
@@ -7394,27 +7544,31 @@
       <c r="AD140" s="5"/>
       <c r="AE140" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
+    <row r="141" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
-      <c r="B141" s="56" t="s">
+      <c r="B141" s="50" t="s">
         <v>194</v>
       </c>
-      <c r="C141" s="57"/>
+      <c r="C141" s="51"/>
       <c r="D141" s="29"/>
-      <c r="E141" s="98"/>
-      <c r="F141" s="99">
+      <c r="E141" s="92"/>
+      <c r="F141" s="93">
         <f>F138</f>
-      </c>
-      <c r="G141" s="100">
+        <v>164286.68</v>
+      </c>
+      <c r="G141" s="94">
         <f>G138-G140</f>
-      </c>
-      <c r="H141" s="99">
+        <v>2599.6698000000001</v>
+      </c>
+      <c r="H141" s="93">
         <f>H138-H140</f>
-      </c>
-      <c r="I141" s="100">
+        <v>318.01</v>
+      </c>
+      <c r="I141" s="94">
         <f>I138-I140</f>
-      </c>
-      <c r="J141" s="63"/>
+        <v>1207.1399999999999</v>
+      </c>
+      <c r="J141" s="57"/>
       <c r="K141" s="6"/>
       <c r="L141" s="5"/>
       <c r="M141" s="6"/>
@@ -7437,22 +7591,24 @@
       <c r="AD141" s="5"/>
       <c r="AE141" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
+    <row r="142" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
-      <c r="B142" s="70" t="s">
+      <c r="B142" s="64" t="s">
         <v>195</v>
       </c>
       <c r="C142" s="13"/>
       <c r="D142" s="29"/>
-      <c r="E142" s="101"/>
-      <c r="F142" s="102">
+      <c r="E142" s="95"/>
+      <c r="F142" s="96">
         <f>F141</f>
-      </c>
-      <c r="G142" s="103">
+        <v>164286.68</v>
+      </c>
+      <c r="G142" s="97">
         <f>G141+H141+I141+J141</f>
-      </c>
-      <c r="H142" s="104"/>
-      <c r="I142" s="98"/>
+        <v>4124.8197999999993</v>
+      </c>
+      <c r="H142" s="98"/>
+      <c r="I142" s="92"/>
       <c r="J142" s="8"/>
       <c r="K142" s="6"/>
       <c r="L142" s="5"/>
@@ -7476,7 +7632,7 @@
       <c r="AD142" s="5"/>
       <c r="AE142" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
+    <row r="143" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
       <c r="B143" s="20"/>
       <c r="C143" s="5"/>
@@ -7509,7 +7665,7 @@
       <c r="AD143" s="5"/>
       <c r="AE143" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
+    <row r="144" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
       <c r="B144" s="20" t="s">
         <v>196</v>
@@ -7520,6 +7676,7 @@
       <c r="F144" s="6"/>
       <c r="G144" s="21">
         <f>G140+H140+J140+I140</f>
+        <v>318.01</v>
       </c>
       <c r="H144" s="8"/>
       <c r="I144" s="8"/>
@@ -7546,7 +7703,7 @@
       <c r="AD144" s="5"/>
       <c r="AE144" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
+    <row r="145" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
       <c r="B145" s="6"/>
       <c r="C145" s="5"/>
@@ -7579,7 +7736,7 @@
       <c r="AD145" s="5"/>
       <c r="AE145" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
+    <row r="146" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="6"/>
       <c r="C146" s="5"/>
@@ -7612,7 +7769,7 @@
       <c r="AD146" s="5"/>
       <c r="AE146" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
+    <row r="147" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="6"/>
       <c r="C147" s="5"/>
@@ -7645,7 +7802,7 @@
       <c r="AD147" s="5"/>
       <c r="AE147" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
+    <row r="148" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="6"/>
       <c r="C148" s="5"/>
@@ -7678,7 +7835,7 @@
       <c r="AD148" s="5"/>
       <c r="AE148" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
+    <row r="149" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="6"/>
       <c r="C149" s="5"/>
@@ -7711,7 +7868,7 @@
       <c r="AD149" s="5"/>
       <c r="AE149" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
+    <row r="150" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="6"/>
       <c r="C150" s="5"/>
@@ -7744,7 +7901,7 @@
       <c r="AD150" s="5"/>
       <c r="AE150" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
+    <row r="151" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="6"/>
       <c r="C151" s="5"/>
@@ -7777,7 +7934,7 @@
       <c r="AD151" s="5"/>
       <c r="AE151" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
+    <row r="152" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="6"/>
       <c r="C152" s="5"/>
@@ -7810,7 +7967,7 @@
       <c r="AD152" s="5"/>
       <c r="AE152" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
+    <row r="153" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="23" t="s">
         <v>197</v>
@@ -7845,7 +8002,7 @@
       <c r="AD153" s="5"/>
       <c r="AE153" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
+    <row r="154" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="6"/>
       <c r="C154" s="5"/>
@@ -7878,18 +8035,18 @@
       <c r="AD154" s="5"/>
       <c r="AE154" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
+    <row r="155" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
-      <c r="B155" s="105" t="s">
+      <c r="B155" s="99" t="s">
         <v>198</v>
       </c>
-      <c r="C155" s="57"/>
+      <c r="C155" s="51"/>
       <c r="D155" s="29"/>
-      <c r="E155" s="58"/>
-      <c r="F155" s="60"/>
-      <c r="G155" s="106"/>
-      <c r="H155" s="58"/>
-      <c r="I155" s="75"/>
+      <c r="E155" s="52"/>
+      <c r="F155" s="54"/>
+      <c r="G155" s="100"/>
+      <c r="H155" s="52"/>
+      <c r="I155" s="69"/>
       <c r="J155" s="8"/>
       <c r="K155" s="6"/>
       <c r="L155" s="5"/>
@@ -7913,26 +8070,26 @@
       <c r="AD155" s="5"/>
       <c r="AE155" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
+    <row r="156" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
-      <c r="B156" s="107" t="s">
+      <c r="B156" s="101" t="s">
         <v>164</v>
       </c>
-      <c r="C156" s="108" t="s">
+      <c r="C156" s="102" t="s">
         <v>199</v>
       </c>
       <c r="D156" s="29"/>
-      <c r="E156" s="98"/>
-      <c r="F156" s="109" t="s">
+      <c r="E156" s="92"/>
+      <c r="F156" s="103" t="s">
         <v>200</v>
       </c>
-      <c r="G156" s="110" t="s">
+      <c r="G156" s="104" t="s">
         <v>201</v>
       </c>
-      <c r="H156" s="111" t="s">
+      <c r="H156" s="105" t="s">
         <v>202</v>
       </c>
-      <c r="I156" s="112" t="s">
+      <c r="I156" s="106" t="s">
         <v>203</v>
       </c>
       <c r="J156" s="8"/>
@@ -7958,9 +8115,9 @@
       <c r="AD156" s="5"/>
       <c r="AE156" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
+    <row r="157" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
-      <c r="B157" s="80">
+      <c r="B157" s="74">
         <v>1</v>
       </c>
       <c r="C157" s="5" t="s">
@@ -7968,12 +8125,12 @@
       </c>
       <c r="D157" s="7"/>
       <c r="E157" s="8"/>
-      <c r="F157" s="113">
+      <c r="F157" s="107">
         <v>5</v>
       </c>
-      <c r="G157" s="79"/>
-      <c r="H157" s="90"/>
-      <c r="I157" s="113"/>
+      <c r="G157" s="73"/>
+      <c r="H157" s="84"/>
+      <c r="I157" s="107"/>
       <c r="J157" s="8"/>
       <c r="K157" s="6"/>
       <c r="L157" s="5"/>
@@ -7997,9 +8154,9 @@
       <c r="AD157" s="5"/>
       <c r="AE157" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
+    <row r="158" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
-      <c r="B158" s="80">
+      <c r="B158" s="74">
         <v>2</v>
       </c>
       <c r="C158" s="5" t="s">
@@ -8007,12 +8164,12 @@
       </c>
       <c r="D158" s="7"/>
       <c r="E158" s="8"/>
-      <c r="F158" s="91"/>
-      <c r="G158" s="79">
+      <c r="F158" s="85"/>
+      <c r="G158" s="73">
         <v>5</v>
       </c>
-      <c r="H158" s="90"/>
-      <c r="I158" s="91"/>
+      <c r="H158" s="84"/>
+      <c r="I158" s="85"/>
       <c r="J158" s="8"/>
       <c r="K158" s="6"/>
       <c r="L158" s="5"/>
@@ -8036,9 +8193,9 @@
       <c r="AD158" s="5"/>
       <c r="AE158" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
+    <row r="159" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
-      <c r="B159" s="80">
+      <c r="B159" s="74">
         <v>3</v>
       </c>
       <c r="C159" s="5" t="s">
@@ -8046,12 +8203,12 @@
       </c>
       <c r="D159" s="7"/>
       <c r="E159" s="8"/>
-      <c r="F159" s="91"/>
-      <c r="G159" s="79"/>
-      <c r="H159" s="90">
+      <c r="F159" s="85"/>
+      <c r="G159" s="73"/>
+      <c r="H159" s="84">
         <v>5</v>
       </c>
-      <c r="I159" s="91"/>
+      <c r="I159" s="85"/>
       <c r="J159" s="8"/>
       <c r="K159" s="6"/>
       <c r="L159" s="5"/>
@@ -8075,16 +8232,16 @@
       <c r="AD159" s="5"/>
       <c r="AE159" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
+    <row r="160" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
-      <c r="B160" s="80"/>
+      <c r="B160" s="74"/>
       <c r="C160" s="5"/>
       <c r="D160" s="7"/>
       <c r="E160" s="8"/>
-      <c r="F160" s="91"/>
-      <c r="G160" s="79"/>
-      <c r="H160" s="90"/>
-      <c r="I160" s="91"/>
+      <c r="F160" s="85"/>
+      <c r="G160" s="73"/>
+      <c r="H160" s="84"/>
+      <c r="I160" s="85"/>
       <c r="J160" s="8"/>
       <c r="K160" s="6"/>
       <c r="L160" s="5"/>
@@ -8108,16 +8265,16 @@
       <c r="AD160" s="5"/>
       <c r="AE160" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
+    <row r="161" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
-      <c r="B161" s="80"/>
+      <c r="B161" s="74"/>
       <c r="C161" s="5"/>
       <c r="D161" s="7"/>
       <c r="E161" s="8"/>
-      <c r="F161" s="94"/>
-      <c r="G161" s="79"/>
-      <c r="H161" s="90"/>
-      <c r="I161" s="94"/>
+      <c r="F161" s="88"/>
+      <c r="G161" s="73"/>
+      <c r="H161" s="84"/>
+      <c r="I161" s="88"/>
       <c r="J161" s="8"/>
       <c r="K161" s="6"/>
       <c r="L161" s="5"/>
@@ -8141,25 +8298,29 @@
       <c r="AD161" s="5"/>
       <c r="AE161" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
+    <row r="162" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
-      <c r="B162" s="114" t="s">
+      <c r="B162" s="108" t="s">
         <v>190</v>
       </c>
-      <c r="C162" s="67"/>
-      <c r="D162" s="68"/>
-      <c r="E162" s="69"/>
-      <c r="F162" s="91">
+      <c r="C162" s="61"/>
+      <c r="D162" s="62"/>
+      <c r="E162" s="63"/>
+      <c r="F162" s="85">
         <f>SUM(F157:F161)</f>
-      </c>
-      <c r="G162" s="115">
+        <v>5</v>
+      </c>
+      <c r="G162" s="109">
         <f>SUM(G157:G161)</f>
-      </c>
-      <c r="H162" s="113">
+        <v>5</v>
+      </c>
+      <c r="H162" s="107">
         <f>SUM(H157:H161)</f>
-      </c>
-      <c r="I162" s="79">
+        <v>5</v>
+      </c>
+      <c r="I162" s="73">
         <f>SUM(I157:I161)</f>
+        <v>0</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="6"/>
@@ -8184,16 +8345,16 @@
       <c r="AD162" s="5"/>
       <c r="AE162" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
+    <row r="163" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
-      <c r="B163" s="116"/>
+      <c r="B163" s="110"/>
       <c r="C163" s="13"/>
       <c r="D163" s="14"/>
       <c r="E163" s="15"/>
-      <c r="F163" s="94"/>
-      <c r="G163" s="117"/>
-      <c r="H163" s="94"/>
-      <c r="I163" s="88"/>
+      <c r="F163" s="88"/>
+      <c r="G163" s="111"/>
+      <c r="H163" s="88"/>
+      <c r="I163" s="82"/>
       <c r="J163" s="8"/>
       <c r="K163" s="6"/>
       <c r="L163" s="5"/>
@@ -8217,25 +8378,29 @@
       <c r="AD163" s="5"/>
       <c r="AE163" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
-      <c r="A164" s="92"/>
-      <c r="B164" s="105" t="s">
+    <row r="164" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="86"/>
+      <c r="B164" s="99" t="s">
         <v>190</v>
       </c>
-      <c r="C164" s="57"/>
+      <c r="C164" s="51"/>
       <c r="D164" s="29"/>
-      <c r="E164" s="58"/>
-      <c r="F164" s="100">
+      <c r="E164" s="52"/>
+      <c r="F164" s="94">
         <f>F162</f>
-      </c>
-      <c r="G164" s="118">
+        <v>5</v>
+      </c>
+      <c r="G164" s="112">
         <f>G162</f>
-      </c>
-      <c r="H164" s="113">
+        <v>5</v>
+      </c>
+      <c r="H164" s="107">
         <f>H162</f>
-      </c>
-      <c r="I164" s="119">
+        <v>5</v>
+      </c>
+      <c r="I164" s="113">
         <f>I162-I163</f>
+        <v>0</v>
       </c>
       <c r="J164" s="8"/>
       <c r="K164" s="6"/>
@@ -8260,20 +8425,21 @@
       <c r="AD164" s="5"/>
       <c r="AE164" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
+    <row r="165" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
-      <c r="B165" s="70"/>
+      <c r="B165" s="64"/>
       <c r="C165" s="13"/>
-      <c r="D165" s="86" t="s">
+      <c r="D165" s="80" t="s">
         <v>207</v>
       </c>
       <c r="E165" s="15"/>
-      <c r="F165" s="117"/>
-      <c r="G165" s="117"/>
-      <c r="H165" s="120">
+      <c r="F165" s="111"/>
+      <c r="G165" s="111"/>
+      <c r="H165" s="114">
         <f>F164+G164+H164+I164</f>
-      </c>
-      <c r="I165" s="121"/>
+        <v>15</v>
+      </c>
+      <c r="I165" s="115"/>
       <c r="J165" s="8"/>
       <c r="K165" s="6"/>
       <c r="L165" s="5"/>
@@ -8297,16 +8463,16 @@
       <c r="AD165" s="5"/>
       <c r="AE165" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
+    <row r="166" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
-      <c r="B166" s="122"/>
-      <c r="C166" s="67"/>
-      <c r="D166" s="68"/>
-      <c r="E166" s="69"/>
-      <c r="F166" s="115"/>
-      <c r="G166" s="115"/>
-      <c r="H166" s="63"/>
-      <c r="I166" s="63"/>
+      <c r="B166" s="116"/>
+      <c r="C166" s="61"/>
+      <c r="D166" s="62"/>
+      <c r="E166" s="63"/>
+      <c r="F166" s="109"/>
+      <c r="G166" s="109"/>
+      <c r="H166" s="57"/>
+      <c r="I166" s="57"/>
       <c r="J166" s="8"/>
       <c r="K166" s="6"/>
       <c r="L166" s="5"/>
@@ -8330,20 +8496,20 @@
       <c r="AD166" s="5"/>
       <c r="AE166" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
+    <row r="167" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
-      <c r="B167" s="105" t="s">
+      <c r="B167" s="99" t="s">
         <v>208</v>
       </c>
-      <c r="C167" s="57"/>
+      <c r="C167" s="51"/>
       <c r="D167" s="29"/>
-      <c r="E167" s="58"/>
-      <c r="F167" s="123"/>
-      <c r="G167" s="123"/>
-      <c r="H167" s="124" t="s">
+      <c r="E167" s="52"/>
+      <c r="F167" s="117"/>
+      <c r="G167" s="117"/>
+      <c r="H167" s="118" t="s">
         <v>166</v>
       </c>
-      <c r="I167" s="124" t="s">
+      <c r="I167" s="118" t="s">
         <v>209</v>
       </c>
       <c r="J167" s="8"/>
@@ -8369,19 +8535,21 @@
       <c r="AD167" s="5"/>
       <c r="AE167" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
+    <row r="168" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
-      <c r="B168" s="95"/>
+      <c r="B168" s="89"/>
       <c r="C168" s="5"/>
       <c r="D168" s="7"/>
       <c r="E168" s="8"/>
-      <c r="F168" s="63"/>
-      <c r="G168" s="63"/>
-      <c r="H168" s="91">
+      <c r="F168" s="57"/>
+      <c r="G168" s="57"/>
+      <c r="H168" s="85">
         <f>I155</f>
-      </c>
-      <c r="I168" s="91">
+        <v>0</v>
+      </c>
+      <c r="I168" s="85">
         <f>H165</f>
+        <v>15</v>
       </c>
       <c r="J168" s="8"/>
       <c r="K168" s="6"/>
@@ -8406,23 +8574,26 @@
       <c r="AD168" s="5"/>
       <c r="AE168" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
+    <row r="169" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
-      <c r="B169" s="125">
+      <c r="B169" s="119">
         <f>J97</f>
+        <v>18</v>
       </c>
       <c r="C169" s="13" t="s">
         <v>191</v>
       </c>
       <c r="D169" s="7"/>
       <c r="E169" s="8"/>
-      <c r="F169" s="63"/>
-      <c r="G169" s="63"/>
-      <c r="H169" s="91">
+      <c r="F169" s="57"/>
+      <c r="G169" s="57"/>
+      <c r="H169" s="85">
         <f>B169*H168/100</f>
-      </c>
-      <c r="I169" s="91">
+        <v>0</v>
+      </c>
+      <c r="I169" s="85">
         <f>B169*I168/100</f>
+        <v>2.7</v>
       </c>
       <c r="J169" s="8"/>
       <c r="K169" s="6"/>
@@ -8447,21 +8618,23 @@
       <c r="AD169" s="5"/>
       <c r="AE169" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
+    <row r="170" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
-      <c r="B170" s="105" t="s">
+      <c r="B170" s="99" t="s">
         <v>210</v>
       </c>
-      <c r="C170" s="57"/>
+      <c r="C170" s="51"/>
       <c r="D170" s="29"/>
-      <c r="E170" s="58"/>
-      <c r="F170" s="106"/>
-      <c r="G170" s="106"/>
-      <c r="H170" s="126">
+      <c r="E170" s="52"/>
+      <c r="F170" s="100"/>
+      <c r="G170" s="100"/>
+      <c r="H170" s="120">
         <f>H168+H169</f>
-      </c>
-      <c r="I170" s="103">
+        <v>0</v>
+      </c>
+      <c r="I170" s="97">
         <f>I168+I169</f>
+        <v>17.7</v>
       </c>
       <c r="J170" s="8"/>
       <c r="K170" s="6"/>
@@ -8486,7 +8659,7 @@
       <c r="AD170" s="5"/>
       <c r="AE170" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
+    <row r="171" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="6"/>
       <c r="C171" s="5"/>
@@ -8519,7 +8692,7 @@
       <c r="AD171" s="5"/>
       <c r="AE171" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
+    <row r="172" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="20" t="s">
         <v>211</v>
@@ -8530,6 +8703,7 @@
       <c r="F172" s="6"/>
       <c r="G172" s="21">
         <f>I170</f>
+        <v>17.7</v>
       </c>
       <c r="H172" s="8"/>
       <c r="I172" s="8"/>
@@ -8556,7 +8730,7 @@
       <c r="AD172" s="5"/>
       <c r="AE172" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
+    <row r="173" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="12"/>
       <c r="C173" s="13"/>
@@ -8589,18 +8763,18 @@
       <c r="AD173" s="5"/>
       <c r="AE173" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
+    <row r="174" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
-      <c r="B174" s="70" t="s">
+      <c r="B174" s="64" t="s">
         <v>212</v>
       </c>
       <c r="C174" s="13"/>
       <c r="D174" s="14"/>
-      <c r="E174" s="72"/>
-      <c r="F174" s="73" t="s">
+      <c r="E174" s="66"/>
+      <c r="F174" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="G174" s="73" t="s">
+      <c r="G174" s="67" t="s">
         <v>209</v>
       </c>
       <c r="H174" s="8"/>
@@ -8628,19 +8802,21 @@
       <c r="AD174" s="5"/>
       <c r="AE174" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
+    <row r="175" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
-      <c r="B175" s="127" t="s">
+      <c r="B175" s="121" t="s">
         <v>213</v>
       </c>
-      <c r="C175" s="67"/>
-      <c r="D175" s="68"/>
-      <c r="E175" s="69"/>
-      <c r="F175" s="113">
+      <c r="C175" s="61"/>
+      <c r="D175" s="62"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="107">
         <f>F142</f>
-      </c>
-      <c r="G175" s="119">
+        <v>164286.68</v>
+      </c>
+      <c r="G175" s="113">
         <f>G142</f>
+        <v>4124.8197999999993</v>
       </c>
       <c r="H175" s="8"/>
       <c r="I175" s="8"/>
@@ -8667,19 +8843,21 @@
       <c r="AD175" s="5"/>
       <c r="AE175" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
+    <row r="176" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
-      <c r="B176" s="116" t="s">
+      <c r="B176" s="110" t="s">
         <v>214</v>
       </c>
       <c r="C176" s="13"/>
       <c r="D176" s="14"/>
       <c r="E176" s="15"/>
-      <c r="F176" s="94">
+      <c r="F176" s="88">
         <f>H170</f>
-      </c>
-      <c r="G176" s="88">
+        <v>0</v>
+      </c>
+      <c r="G176" s="82">
         <f>G172</f>
+        <v>17.7</v>
       </c>
       <c r="H176" s="8"/>
       <c r="I176" s="8"/>
@@ -8706,19 +8884,21 @@
       <c r="AD176" s="5"/>
       <c r="AE176" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
+    <row r="177" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
-      <c r="B177" s="62" t="s">
+      <c r="B177" s="56" t="s">
         <v>190</v>
       </c>
       <c r="C177" s="5"/>
       <c r="D177" s="7"/>
-      <c r="E177" s="78"/>
-      <c r="F177" s="79">
+      <c r="E177" s="72"/>
+      <c r="F177" s="73">
         <f>F175+F176</f>
-      </c>
-      <c r="G177" s="79">
+        <v>164286.68</v>
+      </c>
+      <c r="G177" s="73">
         <f>G175+G176</f>
+        <v>4142.5197999999991</v>
       </c>
       <c r="H177" s="8"/>
       <c r="I177" s="8"/>
@@ -8745,17 +8925,18 @@
       <c r="AD177" s="5"/>
       <c r="AE177" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
+    <row r="178" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
-      <c r="B178" s="116" t="s">
+      <c r="B178" s="110" t="s">
         <v>215</v>
       </c>
       <c r="C178" s="13"/>
       <c r="D178" s="14"/>
-      <c r="E178" s="72"/>
-      <c r="F178" s="82"/>
-      <c r="G178" s="79">
+      <c r="E178" s="66"/>
+      <c r="F178" s="76"/>
+      <c r="G178" s="73">
         <f>J95</f>
+        <v>500</v>
       </c>
       <c r="H178" s="8"/>
       <c r="I178" s="8"/>
@@ -8782,19 +8963,21 @@
       <c r="AD178" s="5"/>
       <c r="AE178" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
+    <row r="179" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
-      <c r="B179" s="70" t="s">
+      <c r="B179" s="64" t="s">
         <v>216</v>
       </c>
       <c r="C179" s="13"/>
       <c r="D179" s="29"/>
-      <c r="E179" s="101"/>
-      <c r="F179" s="126">
+      <c r="E179" s="95"/>
+      <c r="F179" s="120">
         <f>F177</f>
-      </c>
-      <c r="G179" s="128">
+        <v>164286.68</v>
+      </c>
+      <c r="G179" s="122">
         <f>G177-G178</f>
+        <v>3642.5197999999991</v>
       </c>
       <c r="H179" s="8"/>
       <c r="I179" s="8"/>
@@ -8821,7 +9004,7 @@
       <c r="AD179" s="5"/>
       <c r="AE179" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
+    <row r="180" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
       <c r="B180" s="6"/>
       <c r="C180" s="5"/>
@@ -8854,7 +9037,7 @@
       <c r="AD180" s="5"/>
       <c r="AE180" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75">
+    <row r="181" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
       <c r="B181" s="6" t="s">
         <v>217</v>
@@ -8863,7 +9046,7 @@
       <c r="D181" s="7"/>
       <c r="E181" s="8"/>
       <c r="F181" s="6"/>
-      <c r="G181" s="63">
+      <c r="G181" s="57">
         <v>0</v>
       </c>
       <c r="H181" s="8"/>
@@ -8891,20 +9074,21 @@
       <c r="AD181" s="5"/>
       <c r="AE181" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
+    <row r="182" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
-      <c r="B182" s="105" t="s">
+      <c r="B182" s="99" t="s">
         <v>218</v>
       </c>
-      <c r="C182" s="57"/>
+      <c r="C182" s="51"/>
       <c r="D182" s="29"/>
-      <c r="E182" s="58"/>
-      <c r="F182" s="60"/>
-      <c r="G182" s="75">
+      <c r="E182" s="52"/>
+      <c r="F182" s="54"/>
+      <c r="G182" s="69">
         <f>G179-G181</f>
+        <v>3642.5197999999991</v>
       </c>
       <c r="H182" s="8"/>
-      <c r="I182" s="63"/>
+      <c r="I182" s="57"/>
       <c r="J182" s="8"/>
       <c r="K182" s="6"/>
       <c r="L182" s="5"/>
@@ -8928,7 +9112,7 @@
       <c r="AD182" s="5"/>
       <c r="AE182" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
+    <row r="183" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
       <c r="B183" s="6"/>
       <c r="C183" s="5"/>
@@ -8961,20 +9145,20 @@
       <c r="AD183" s="5"/>
       <c r="AE183" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75">
+    <row r="184" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
-      <c r="B184" s="129" t="s">
+      <c r="B184" s="168" t="s">
         <v>219</v>
       </c>
-      <c r="C184" s="5"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="8"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="8"/>
-      <c r="I184" s="8"/>
-      <c r="J184" s="8"/>
-      <c r="K184" s="6"/>
+      <c r="C184" s="156"/>
+      <c r="D184" s="157"/>
+      <c r="E184" s="158"/>
+      <c r="F184" s="159"/>
+      <c r="G184" s="159"/>
+      <c r="H184" s="158"/>
+      <c r="I184" s="158"/>
+      <c r="J184" s="158"/>
+      <c r="K184" s="159"/>
       <c r="L184" s="5"/>
       <c r="M184" s="6"/>
       <c r="N184" s="8"/>
@@ -8996,19 +9180,19 @@
       <c r="AD184" s="5"/>
       <c r="AE184" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
+    <row r="185" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
       <c r="B185" s="24"/>
-      <c r="C185" s="54"/>
-      <c r="D185" s="130"/>
-      <c r="E185" s="131"/>
+      <c r="C185" s="48"/>
+      <c r="D185" s="123"/>
+      <c r="E185" s="124"/>
       <c r="F185" s="24"/>
       <c r="G185" s="24"/>
-      <c r="H185" s="131"/>
-      <c r="I185" s="131"/>
-      <c r="J185" s="131"/>
+      <c r="H185" s="124"/>
+      <c r="I185" s="124"/>
+      <c r="J185" s="124"/>
       <c r="K185" s="24"/>
-      <c r="L185" s="54"/>
+      <c r="L185" s="48"/>
       <c r="M185" s="6"/>
       <c r="N185" s="8"/>
       <c r="O185" s="6"/>
@@ -9029,9 +9213,9 @@
       <c r="AD185" s="5"/>
       <c r="AE185" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75">
+    <row r="186" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
-      <c r="B186" s="132" t="s">
+      <c r="B186" s="125" t="s">
         <v>220</v>
       </c>
       <c r="C186" s="5"/>
@@ -9064,7 +9248,7 @@
       <c r="AD186" s="5"/>
       <c r="AE186" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
+    <row r="187" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
       <c r="B187" s="20"/>
       <c r="C187" s="5"/>
@@ -9097,7 +9281,7 @@
       <c r="AD187" s="5"/>
       <c r="AE187" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75">
+    <row r="188" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
       <c r="B188" s="6">
         <v>1</v>
@@ -9109,8 +9293,9 @@
       <c r="E188" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F188" s="6">
+      <c r="F188" s="6" t="str">
         <f>G30</f>
+        <v>MEXC19606KT080595</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="8"/>
@@ -9138,7 +9323,7 @@
       <c r="AD188" s="5"/>
       <c r="AE188" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
+    <row r="189" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
       <c r="B189" s="6"/>
       <c r="C189" s="5"/>
@@ -9171,7 +9356,7 @@
       <c r="AD189" s="5"/>
       <c r="AE189" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75">
+    <row r="190" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
       <c r="B190" s="6">
         <v>2</v>
@@ -9183,8 +9368,9 @@
       <c r="E190" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F190" s="6">
+      <c r="F190" s="6" t="str">
         <f>G31</f>
+        <v>CBZL12533</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="8"/>
@@ -9212,7 +9398,7 @@
       <c r="AD190" s="5"/>
       <c r="AE190" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
+    <row r="191" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
       <c r="B191" s="20"/>
       <c r="C191" s="5"/>
@@ -9245,16 +9431,16 @@
       <c r="AD191" s="5"/>
       <c r="AE191" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75">
+    <row r="192" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
       <c r="B192" s="20"/>
-      <c r="C192" s="133" t="s">
+      <c r="C192" s="126" t="s">
         <v>223</v>
       </c>
-      <c r="D192" s="68"/>
-      <c r="E192" s="69"/>
-      <c r="F192" s="66"/>
-      <c r="G192" s="47"/>
+      <c r="D192" s="62"/>
+      <c r="E192" s="63"/>
+      <c r="F192" s="60"/>
+      <c r="G192" s="41"/>
       <c r="H192" s="8"/>
       <c r="I192" s="8"/>
       <c r="J192" s="11" t="s">
@@ -9282,14 +9468,14 @@
       <c r="AD192" s="5"/>
       <c r="AE192" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75">
+    <row r="193" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
       <c r="B193" s="6"/>
-      <c r="C193" s="36"/>
+      <c r="C193" s="33"/>
       <c r="D193" s="7"/>
       <c r="E193" s="8"/>
       <c r="F193" s="6"/>
-      <c r="G193" s="82"/>
+      <c r="G193" s="76"/>
       <c r="H193" s="8"/>
       <c r="I193" s="8"/>
       <c r="J193" s="8"/>
@@ -9315,16 +9501,16 @@
       <c r="AD193" s="5"/>
       <c r="AE193" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75">
+    <row r="194" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
       <c r="B194" s="20"/>
-      <c r="C194" s="134" t="s">
+      <c r="C194" s="127" t="s">
         <v>225</v>
       </c>
       <c r="D194" s="14"/>
       <c r="E194" s="15"/>
       <c r="F194" s="12"/>
-      <c r="G194" s="49"/>
+      <c r="G194" s="43"/>
       <c r="H194" s="8"/>
       <c r="I194" s="8"/>
       <c r="J194" s="8"/>
@@ -9350,7 +9536,7 @@
       <c r="AD194" s="5"/>
       <c r="AE194" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75">
+    <row r="195" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
       <c r="B195" s="20"/>
       <c r="C195" s="5"/>
@@ -9383,7 +9569,7 @@
       <c r="AD195" s="5"/>
       <c r="AE195" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75">
+    <row r="196" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
       <c r="B196" s="20"/>
       <c r="C196" s="5"/>
@@ -9416,7 +9602,7 @@
       <c r="AD196" s="5"/>
       <c r="AE196" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75">
+    <row r="197" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
       <c r="B197" s="20"/>
       <c r="C197" s="5"/>
@@ -9449,7 +9635,7 @@
       <c r="AD197" s="5"/>
       <c r="AE197" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75">
+    <row r="198" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
       <c r="B198" s="6"/>
       <c r="C198" s="5" t="s">
@@ -9458,14 +9644,14 @@
       <c r="D198" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E198" s="135" t="s">
+      <c r="E198" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="F198" s="136">
-        <v>35010231260390000000</v>
-      </c>
-      <c r="G198" s="136">
-        <v>35010231260390000000</v>
+      <c r="F198" s="129">
+        <v>3.5010231260389999E+19</v>
+      </c>
+      <c r="G198" s="129">
+        <v>3.5010231260389999E+19</v>
       </c>
       <c r="H198" s="8"/>
       <c r="I198" s="8"/>
@@ -9494,7 +9680,7 @@
       <c r="AD198" s="5"/>
       <c r="AE198" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75">
+    <row r="199" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
       <c r="B199" s="6"/>
       <c r="C199" s="5"/>
@@ -9527,7 +9713,7 @@
       <c r="AD199" s="5"/>
       <c r="AE199" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75">
+    <row r="200" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
       <c r="B200" s="6"/>
       <c r="C200" s="5"/>
@@ -9540,28 +9726,28 @@
       <c r="J200" s="8"/>
       <c r="K200" s="6"/>
       <c r="L200" s="5"/>
-      <c r="M200" s="137" t="s">
+      <c r="M200" s="130" t="s">
         <v>228</v>
       </c>
-      <c r="N200" s="138" t="s">
+      <c r="N200" s="131" t="s">
         <v>229</v>
       </c>
-      <c r="O200" s="139" t="s">
+      <c r="O200" s="169" t="s">
         <v>230</v>
       </c>
-      <c r="P200" s="33"/>
-      <c r="Q200" s="139" t="s">
+      <c r="P200" s="161"/>
+      <c r="Q200" s="169" t="s">
         <v>231</v>
       </c>
-      <c r="R200" s="33"/>
-      <c r="S200" s="140" t="s">
+      <c r="R200" s="161"/>
+      <c r="S200" s="170" t="s">
         <v>232</v>
       </c>
-      <c r="T200" s="141"/>
-      <c r="U200" s="142" t="s">
+      <c r="T200" s="171"/>
+      <c r="U200" s="172" t="s">
         <v>233</v>
       </c>
-      <c r="V200" s="143"/>
+      <c r="V200" s="173"/>
       <c r="W200" s="5"/>
       <c r="X200" s="5"/>
       <c r="Y200" s="5"/>
@@ -9572,7 +9758,7 @@
       <c r="AD200" s="5"/>
       <c r="AE200" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75">
+    <row r="201" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
       <c r="B201" s="6"/>
       <c r="C201" s="5"/>
@@ -9585,28 +9771,28 @@
       <c r="J201" s="8"/>
       <c r="K201" s="6"/>
       <c r="L201" s="5"/>
-      <c r="M201" s="144"/>
-      <c r="N201" s="72"/>
-      <c r="O201" s="139" t="s">
+      <c r="M201" s="133"/>
+      <c r="N201" s="66"/>
+      <c r="O201" s="132" t="s">
         <v>234</v>
       </c>
-      <c r="P201" s="145" t="s">
+      <c r="P201" s="134" t="s">
         <v>235</v>
       </c>
-      <c r="Q201" s="146" t="s">
+      <c r="Q201" s="135" t="s">
         <v>234</v>
       </c>
-      <c r="R201" s="145" t="s">
+      <c r="R201" s="134" t="s">
         <v>235</v>
       </c>
-      <c r="S201" s="147" t="s">
+      <c r="S201" s="136" t="s">
         <v>234</v>
       </c>
-      <c r="T201" s="148" t="s">
+      <c r="T201" s="137" t="s">
         <v>235</v>
       </c>
-      <c r="U201" s="149"/>
-      <c r="V201" s="150"/>
+      <c r="U201" s="174"/>
+      <c r="V201" s="175"/>
       <c r="W201" s="5"/>
       <c r="X201" s="5"/>
       <c r="Y201" s="5"/>
@@ -9617,7 +9803,7 @@
       <c r="AD201" s="5"/>
       <c r="AE201" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75">
+    <row r="202" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
       <c r="B202" s="20"/>
       <c r="C202" s="5" t="s">
@@ -9634,28 +9820,32 @@
       <c r="J202" s="8"/>
       <c r="K202" s="6"/>
       <c r="L202" s="5"/>
-      <c r="M202" s="151"/>
-      <c r="N202" s="50">
+      <c r="M202" s="138"/>
+      <c r="N202" s="44">
         <f>G136+H136</f>
-      </c>
-      <c r="O202" s="151">
+        <v>2742.11</v>
+      </c>
+      <c r="O202" s="138">
         <v>14</v>
       </c>
-      <c r="P202" s="152">
+      <c r="P202" s="139">
         <f>14*N202/100</f>
-      </c>
-      <c r="Q202" s="153">
+        <v>383.8954</v>
+      </c>
+      <c r="Q202" s="140">
         <v>14</v>
       </c>
-      <c r="R202" s="152">
+      <c r="R202" s="139">
         <f>P202</f>
-      </c>
-      <c r="S202" s="77"/>
-      <c r="T202" s="92"/>
-      <c r="U202" s="63">
+        <v>383.8954</v>
+      </c>
+      <c r="S202" s="71"/>
+      <c r="T202" s="86"/>
+      <c r="U202" s="57">
         <f>P202+R202</f>
-      </c>
-      <c r="V202" s="92"/>
+        <v>767.79079999999999</v>
+      </c>
+      <c r="V202" s="86"/>
       <c r="W202" s="5"/>
       <c r="X202" s="5"/>
       <c r="Y202" s="5"/>
@@ -9666,7 +9856,7 @@
       <c r="AD202" s="5"/>
       <c r="AE202" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75">
+    <row r="203" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
       <c r="B203" s="20"/>
       <c r="C203" s="5"/>
@@ -9679,28 +9869,32 @@
       <c r="J203" s="8"/>
       <c r="K203" s="6"/>
       <c r="L203" s="5"/>
-      <c r="M203" s="151"/>
-      <c r="N203" s="50">
+      <c r="M203" s="138"/>
+      <c r="N203" s="44">
         <f>I136</f>
-      </c>
-      <c r="O203" s="151">
+        <v>1023</v>
+      </c>
+      <c r="O203" s="138">
         <v>9</v>
       </c>
-      <c r="P203" s="152">
+      <c r="P203" s="139">
         <f>9*N203/100</f>
-      </c>
-      <c r="Q203" s="153">
+        <v>92.07</v>
+      </c>
+      <c r="Q203" s="140">
         <v>9</v>
       </c>
-      <c r="R203" s="152">
+      <c r="R203" s="139">
         <f>P203</f>
-      </c>
-      <c r="S203" s="81"/>
-      <c r="T203" s="92"/>
-      <c r="U203" s="63">
+        <v>92.07</v>
+      </c>
+      <c r="S203" s="75"/>
+      <c r="T203" s="86"/>
+      <c r="U203" s="57">
         <f>P203+R203</f>
-      </c>
-      <c r="V203" s="92"/>
+        <v>184.14</v>
+      </c>
+      <c r="V203" s="86"/>
       <c r="W203" s="5"/>
       <c r="X203" s="5"/>
       <c r="Y203" s="5"/>
@@ -9711,7 +9905,7 @@
       <c r="AD203" s="5"/>
       <c r="AE203" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75">
+    <row r="204" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
       <c r="B204" s="20"/>
       <c r="C204" s="5"/>
@@ -9724,28 +9918,32 @@
       <c r="J204" s="8"/>
       <c r="K204" s="6"/>
       <c r="L204" s="5"/>
-      <c r="M204" s="151"/>
-      <c r="N204" s="50">
+      <c r="M204" s="138"/>
+      <c r="N204" s="44">
         <f>J136</f>
-      </c>
-      <c r="O204" s="151">
+        <v>21771.18</v>
+      </c>
+      <c r="O204" s="138">
         <v>9</v>
       </c>
-      <c r="P204" s="152">
+      <c r="P204" s="139">
         <f>9*N204/100</f>
-      </c>
-      <c r="Q204" s="153">
+        <v>1959.4061999999999</v>
+      </c>
+      <c r="Q204" s="140">
         <v>9</v>
       </c>
-      <c r="R204" s="152">
+      <c r="R204" s="139">
         <f>P204</f>
-      </c>
-      <c r="S204" s="81"/>
-      <c r="T204" s="92"/>
-      <c r="U204" s="63">
+        <v>1959.4061999999999</v>
+      </c>
+      <c r="S204" s="75"/>
+      <c r="T204" s="86"/>
+      <c r="U204" s="57">
         <f>P204+R204</f>
-      </c>
-      <c r="V204" s="92"/>
+        <v>3918.8123999999998</v>
+      </c>
+      <c r="V204" s="86"/>
       <c r="W204" s="5"/>
       <c r="X204" s="5"/>
       <c r="Y204" s="5"/>
@@ -9756,7 +9954,7 @@
       <c r="AD204" s="5"/>
       <c r="AE204" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18.75">
+    <row r="205" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
       <c r="B205" s="20"/>
       <c r="C205" s="5"/>
@@ -9769,30 +9967,34 @@
       <c r="J205" s="8"/>
       <c r="K205" s="6"/>
       <c r="L205" s="5"/>
-      <c r="M205" s="44">
+      <c r="M205" s="38">
         <v>998729</v>
       </c>
-      <c r="N205" s="154">
+      <c r="N205" s="141">
         <f>I168</f>
-      </c>
-      <c r="O205" s="44">
+        <v>15</v>
+      </c>
+      <c r="O205" s="38">
         <v>9</v>
       </c>
-      <c r="P205" s="155">
+      <c r="P205" s="142">
         <f>9*N205/100</f>
-      </c>
-      <c r="Q205" s="156">
+        <v>1.35</v>
+      </c>
+      <c r="Q205" s="143">
         <v>9</v>
       </c>
-      <c r="R205" s="155">
+      <c r="R205" s="142">
         <f>P205</f>
-      </c>
-      <c r="S205" s="157"/>
-      <c r="T205" s="158"/>
-      <c r="U205" s="117">
+        <v>1.35</v>
+      </c>
+      <c r="S205" s="144"/>
+      <c r="T205" s="145"/>
+      <c r="U205" s="111">
         <f>P205+R205</f>
-      </c>
-      <c r="V205" s="158"/>
+        <v>2.7</v>
+      </c>
+      <c r="V205" s="145"/>
       <c r="W205" s="5"/>
       <c r="X205" s="5"/>
       <c r="Y205" s="5"/>
@@ -9803,14 +10005,14 @@
       <c r="AD205" s="5"/>
       <c r="AE205" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18.75">
+    <row r="206" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
       <c r="B206" s="6"/>
       <c r="C206" s="5"/>
       <c r="D206" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="E206" s="45">
+      <c r="E206" s="39">
         <v>2500</v>
       </c>
       <c r="F206" s="6"/>
@@ -9820,20 +10022,21 @@
       <c r="J206" s="8"/>
       <c r="K206" s="6"/>
       <c r="L206" s="5"/>
-      <c r="M206" s="105" t="s">
+      <c r="M206" s="99" t="s">
         <v>239</v>
       </c>
-      <c r="N206" s="159"/>
+      <c r="N206" s="146"/>
       <c r="O206" s="31"/>
-      <c r="P206" s="159"/>
-      <c r="Q206" s="160"/>
+      <c r="P206" s="146"/>
+      <c r="Q206" s="147"/>
       <c r="R206" s="30"/>
-      <c r="S206" s="108"/>
-      <c r="T206" s="108"/>
-      <c r="U206" s="106">
+      <c r="S206" s="102"/>
+      <c r="T206" s="102"/>
+      <c r="U206" s="100">
         <f>SUM(U202:U205)</f>
-      </c>
-      <c r="V206" s="161"/>
+        <v>4873.4431999999997</v>
+      </c>
+      <c r="V206" s="148"/>
       <c r="W206" s="5"/>
       <c r="X206" s="5"/>
       <c r="Y206" s="5"/>
@@ -9844,7 +10047,7 @@
       <c r="AD206" s="5"/>
       <c r="AE206" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18.75">
+    <row r="207" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
       <c r="B207" s="6"/>
       <c r="C207" s="5"/>
@@ -9877,7 +10080,7 @@
       <c r="AD207" s="5"/>
       <c r="AE207" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18.75">
+    <row r="208" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
       <c r="B208" s="6"/>
       <c r="C208" s="5"/>
@@ -9910,7 +10113,7 @@
       <c r="AD208" s="5"/>
       <c r="AE208" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18.75">
+    <row r="209" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
       <c r="B209" s="20"/>
       <c r="C209" s="5"/>
@@ -9943,7 +10146,7 @@
       <c r="AD209" s="5"/>
       <c r="AE209" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="18.75">
+    <row r="210" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
       <c r="B210" s="20"/>
       <c r="C210" s="5"/>
@@ -9976,7 +10179,7 @@
       <c r="AD210" s="5"/>
       <c r="AE210" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="18.75">
+    <row r="211" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
       <c r="B211" s="20"/>
       <c r="C211" s="5"/>
@@ -10009,7 +10212,7 @@
       <c r="AD211" s="5"/>
       <c r="AE211" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="18.75">
+    <row r="212" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
       <c r="B212" s="20"/>
       <c r="C212" s="5"/>
@@ -10042,7 +10245,7 @@
       <c r="AD212" s="5"/>
       <c r="AE212" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="18.75">
+    <row r="213" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
       <c r="B213" s="20"/>
       <c r="C213" s="5"/>
@@ -10075,7 +10278,7 @@
       <c r="AD213" s="5"/>
       <c r="AE213" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="18.75">
+    <row r="214" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
       <c r="B214" s="20"/>
       <c r="C214" s="5"/>
@@ -10108,7 +10311,7 @@
       <c r="AD214" s="5"/>
       <c r="AE214" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="18.75">
+    <row r="215" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
       <c r="B215" s="20"/>
       <c r="C215" s="5"/>
@@ -10141,7 +10344,7 @@
       <c r="AD215" s="5"/>
       <c r="AE215" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="18.75">
+    <row r="216" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
       <c r="B216" s="20"/>
       <c r="C216" s="5"/>
@@ -10174,7 +10377,7 @@
       <c r="AD216" s="5"/>
       <c r="AE216" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="18.75">
+    <row r="217" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
       <c r="B217" s="20"/>
       <c r="C217" s="5"/>
@@ -10207,7 +10410,7 @@
       <c r="AD217" s="5"/>
       <c r="AE217" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="18.75">
+    <row r="218" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
       <c r="B218" s="20"/>
       <c r="C218" s="5"/>
@@ -10240,7 +10443,7 @@
       <c r="AD218" s="5"/>
       <c r="AE218" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="18.75">
+    <row r="219" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
       <c r="B219" s="20"/>
       <c r="C219" s="5"/>
@@ -10273,7 +10476,7 @@
       <c r="AD219" s="5"/>
       <c r="AE219" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="18.75">
+    <row r="220" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
       <c r="B220" s="20"/>
       <c r="C220" s="5"/>
@@ -10306,7 +10509,7 @@
       <c r="AD220" s="5"/>
       <c r="AE220" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="18.75">
+    <row r="221" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
       <c r="B221" s="20"/>
       <c r="C221" s="5"/>
@@ -10339,7 +10542,7 @@
       <c r="AD221" s="5"/>
       <c r="AE221" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="18.75">
+    <row r="222" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
       <c r="B222" s="20"/>
       <c r="C222" s="5"/>
@@ -10372,7 +10575,7 @@
       <c r="AD222" s="5"/>
       <c r="AE222" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="18.75">
+    <row r="223" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
       <c r="B223" s="20"/>
       <c r="C223" s="5"/>
@@ -10405,7 +10608,7 @@
       <c r="AD223" s="5"/>
       <c r="AE223" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="18.75">
+    <row r="224" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
       <c r="B224" s="20"/>
       <c r="C224" s="5"/>
@@ -10438,7 +10641,7 @@
       <c r="AD224" s="5"/>
       <c r="AE224" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="18.75">
+    <row r="225" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
       <c r="B225" s="20"/>
       <c r="C225" s="5"/>
@@ -10471,7 +10674,7 @@
       <c r="AD225" s="5"/>
       <c r="AE225" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="18.75">
+    <row r="226" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
       <c r="B226" s="20"/>
       <c r="C226" s="5"/>
@@ -10504,7 +10707,7 @@
       <c r="AD226" s="5"/>
       <c r="AE226" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="18.75">
+    <row r="227" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
       <c r="B227" s="20"/>
       <c r="C227" s="5"/>
@@ -10537,7 +10740,7 @@
       <c r="AD227" s="5"/>
       <c r="AE227" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="18.75">
+    <row r="228" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
       <c r="B228" s="20"/>
       <c r="C228" s="5"/>
@@ -10570,7 +10773,7 @@
       <c r="AD228" s="5"/>
       <c r="AE228" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="18.75">
+    <row r="229" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
       <c r="B229" s="20"/>
       <c r="C229" s="5"/>
@@ -10603,7 +10806,7 @@
       <c r="AD229" s="5"/>
       <c r="AE229" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="18.75">
+    <row r="230" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
       <c r="B230" s="20"/>
       <c r="C230" s="5"/>
@@ -10636,7 +10839,7 @@
       <c r="AD230" s="5"/>
       <c r="AE230" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="18.75">
+    <row r="231" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
       <c r="B231" s="20"/>
       <c r="C231" s="5"/>
@@ -10669,7 +10872,7 @@
       <c r="AD231" s="5"/>
       <c r="AE231" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="18.75">
+    <row r="232" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
       <c r="B232" s="20"/>
       <c r="C232" s="5"/>
@@ -10702,7 +10905,7 @@
       <c r="AD232" s="5"/>
       <c r="AE232" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="18.75">
+    <row r="233" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
       <c r="B233" s="20"/>
       <c r="C233" s="5"/>
@@ -10735,7 +10938,7 @@
       <c r="AD233" s="5"/>
       <c r="AE233" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="18.75">
+    <row r="234" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
       <c r="B234" s="20"/>
       <c r="C234" s="5"/>
@@ -10768,7 +10971,7 @@
       <c r="AD234" s="5"/>
       <c r="AE234" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="18.75">
+    <row r="235" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
       <c r="B235" s="20"/>
       <c r="C235" s="5"/>
@@ -10801,7 +11004,7 @@
       <c r="AD235" s="5"/>
       <c r="AE235" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="18.75">
+    <row r="236" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
       <c r="B236" s="20"/>
       <c r="C236" s="5"/>
@@ -10834,7 +11037,7 @@
       <c r="AD236" s="5"/>
       <c r="AE236" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="18.75">
+    <row r="237" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
       <c r="B237" s="20"/>
       <c r="C237" s="5"/>
@@ -10867,7 +11070,7 @@
       <c r="AD237" s="5"/>
       <c r="AE237" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="18.75">
+    <row r="238" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
       <c r="B238" s="20"/>
       <c r="C238" s="5"/>
@@ -10900,7 +11103,7 @@
       <c r="AD238" s="5"/>
       <c r="AE238" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="18.75">
+    <row r="239" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
       <c r="B239" s="20"/>
       <c r="C239" s="5"/>
@@ -10933,7 +11136,7 @@
       <c r="AD239" s="5"/>
       <c r="AE239" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="18.75">
+    <row r="240" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
       <c r="B240" s="20"/>
       <c r="C240" s="5"/>
@@ -10966,7 +11169,7 @@
       <c r="AD240" s="5"/>
       <c r="AE240" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="18.75">
+    <row r="241" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
       <c r="B241" s="20"/>
       <c r="C241" s="5"/>
@@ -10999,7 +11202,7 @@
       <c r="AD241" s="5"/>
       <c r="AE241" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="18.75">
+    <row r="242" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
       <c r="B242" s="20"/>
       <c r="C242" s="5"/>
@@ -11032,7 +11235,7 @@
       <c r="AD242" s="5"/>
       <c r="AE242" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="18.75">
+    <row r="243" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
       <c r="B243" s="20"/>
       <c r="C243" s="5"/>
@@ -11065,7 +11268,7 @@
       <c r="AD243" s="5"/>
       <c r="AE243" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="18.75">
+    <row r="244" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
       <c r="B244" s="20"/>
       <c r="C244" s="5"/>
@@ -11098,7 +11301,7 @@
       <c r="AD244" s="5"/>
       <c r="AE244" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="18.75">
+    <row r="245" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
       <c r="B245" s="20"/>
       <c r="C245" s="5"/>
@@ -11131,7 +11334,7 @@
       <c r="AD245" s="5"/>
       <c r="AE245" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="18.75">
+    <row r="246" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
       <c r="B246" s="20"/>
       <c r="C246" s="5"/>
@@ -11164,7 +11367,7 @@
       <c r="AD246" s="5"/>
       <c r="AE246" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="18.75">
+    <row r="247" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
       <c r="B247" s="20"/>
       <c r="C247" s="5"/>
@@ -11197,7 +11400,7 @@
       <c r="AD247" s="5"/>
       <c r="AE247" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="18.75">
+    <row r="248" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
       <c r="B248" s="20"/>
       <c r="C248" s="5"/>
@@ -11230,7 +11433,7 @@
       <c r="AD248" s="5"/>
       <c r="AE248" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="18.75">
+    <row r="249" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
       <c r="B249" s="20"/>
       <c r="C249" s="5"/>
@@ -11263,7 +11466,7 @@
       <c r="AD249" s="5"/>
       <c r="AE249" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="18.75">
+    <row r="250" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
       <c r="B250" s="20"/>
       <c r="C250" s="5"/>
@@ -11296,7 +11499,7 @@
       <c r="AD250" s="5"/>
       <c r="AE250" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="18.75">
+    <row r="251" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
       <c r="B251" s="20"/>
       <c r="C251" s="5"/>
@@ -11329,7 +11532,7 @@
       <c r="AD251" s="5"/>
       <c r="AE251" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="18.75">
+    <row r="252" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
       <c r="B252" s="6"/>
       <c r="C252" s="5"/>
@@ -11362,7 +11565,7 @@
       <c r="AD252" s="5"/>
       <c r="AE252" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="18.75">
+    <row r="253" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
       <c r="B253" s="6"/>
       <c r="C253" s="5"/>
@@ -11395,7 +11598,7 @@
       <c r="AD253" s="5"/>
       <c r="AE253" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="18.75">
+    <row r="254" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
       <c r="B254" s="6"/>
       <c r="C254" s="5"/>
@@ -11428,7 +11631,7 @@
       <c r="AD254" s="5"/>
       <c r="AE254" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="18.75">
+    <row r="255" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
       <c r="B255" s="6"/>
       <c r="C255" s="5"/>
@@ -11461,7 +11664,7 @@
       <c r="AD255" s="5"/>
       <c r="AE255" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="18.75">
+    <row r="256" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
       <c r="B256" s="6"/>
       <c r="C256" s="5"/>
@@ -11494,7 +11697,7 @@
       <c r="AD256" s="5"/>
       <c r="AE256" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="18.75">
+    <row r="257" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
       <c r="B257" s="6"/>
       <c r="C257" s="5"/>
@@ -11527,7 +11730,7 @@
       <c r="AD257" s="5"/>
       <c r="AE257" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="18.75">
+    <row r="258" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
       <c r="B258" s="6"/>
       <c r="C258" s="5"/>
@@ -11560,17 +11763,17 @@
       <c r="AD258" s="5"/>
       <c r="AE258" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="18.75">
+    <row r="259" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
       <c r="B259" s="6"/>
       <c r="C259" s="5" t="s">
         <v>240</v>
       </c>
       <c r="D259" s="7"/>
-      <c r="E259" s="162">
+      <c r="E259" s="149">
         <v>43789</v>
       </c>
-      <c r="F259" s="162"/>
+      <c r="F259" s="149"/>
       <c r="G259" s="6"/>
       <c r="H259" s="8"/>
       <c r="I259" s="8"/>
@@ -11597,15 +11800,15 @@
       <c r="AD259" s="5"/>
       <c r="AE259" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="18.75">
+    <row r="260" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
       <c r="B260" s="6"/>
       <c r="C260" s="5" t="s">
         <v>112</v>
       </c>
       <c r="D260" s="7"/>
-      <c r="E260" s="162"/>
-      <c r="F260" s="162"/>
+      <c r="E260" s="149"/>
+      <c r="F260" s="149"/>
       <c r="G260" s="6"/>
       <c r="H260" s="8"/>
       <c r="I260" s="8"/>
@@ -11632,7 +11835,7 @@
       <c r="AD260" s="5"/>
       <c r="AE260" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="18.75">
+    <row r="261" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
       <c r="B261" s="6"/>
       <c r="C261" s="5"/>
@@ -11665,15 +11868,16 @@
       <c r="AD261" s="5"/>
       <c r="AE261" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="18.75">
+    <row r="262" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
       <c r="B262" s="6"/>
       <c r="C262" s="5"/>
       <c r="D262" s="7"/>
-      <c r="E262" s="63">
+      <c r="E262" s="57">
         <f>DAYS360(E259,E260,0)/360</f>
-      </c>
-      <c r="F262" s="63"/>
+        <v>-119.88888888888889</v>
+      </c>
+      <c r="F262" s="57"/>
       <c r="G262" s="6"/>
       <c r="H262" s="8"/>
       <c r="I262" s="8"/>
@@ -11700,7 +11904,7 @@
       <c r="AD262" s="5"/>
       <c r="AE262" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="18.75">
+    <row r="263" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
       <c r="B263" s="6"/>
       <c r="C263" s="5"/>
@@ -11733,7 +11937,7 @@
       <c r="AD263" s="5"/>
       <c r="AE263" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="18.75">
+    <row r="264" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
       <c r="B264" s="6"/>
       <c r="C264" s="5"/>
@@ -11766,7 +11970,7 @@
       <c r="AD264" s="5"/>
       <c r="AE264" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="18.75">
+    <row r="265" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
       <c r="B265" s="6"/>
       <c r="C265" s="5"/>
@@ -11799,7 +12003,7 @@
       <c r="AD265" s="5"/>
       <c r="AE265" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="18.75">
+    <row r="266" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
       <c r="B266" s="6"/>
       <c r="C266" s="5"/>
@@ -11832,7 +12036,7 @@
       <c r="AD266" s="5"/>
       <c r="AE266" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="18.75">
+    <row r="267" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
       <c r="B267" s="6"/>
       <c r="C267" s="5"/>
@@ -11865,7 +12069,7 @@
       <c r="AD267" s="5"/>
       <c r="AE267" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="18.75">
+    <row r="268" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
       <c r="B268" s="6"/>
       <c r="C268" s="5"/>
@@ -11874,7 +12078,7 @@
       <c r="F268" s="6"/>
       <c r="G268" s="6"/>
       <c r="H268" s="8"/>
-      <c r="I268" s="163"/>
+      <c r="I268" s="150"/>
       <c r="J268" s="8"/>
       <c r="K268" s="6"/>
       <c r="L268" s="5"/>
@@ -11898,7 +12102,7 @@
       <c r="AD268" s="5"/>
       <c r="AE268" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="18.75">
+    <row r="269" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
       <c r="B269" s="6"/>
       <c r="C269" s="5"/>
@@ -11931,7 +12135,7 @@
       <c r="AD269" s="5"/>
       <c r="AE269" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="18.75">
+    <row r="270" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
       <c r="B270" s="6"/>
       <c r="C270" s="5"/>
@@ -11964,7 +12168,7 @@
       <c r="AD270" s="5"/>
       <c r="AE270" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="18.75">
+    <row r="271" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1"/>
       <c r="B271" s="2"/>
       <c r="C271" s="1"/>
@@ -11997,7 +12201,7 @@
       <c r="AD271" s="5"/>
       <c r="AE271" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="18.75">
+    <row r="272" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1"/>
       <c r="B272" s="2"/>
       <c r="C272" s="1"/>
@@ -12030,7 +12234,7 @@
       <c r="AD272" s="5"/>
       <c r="AE272" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="18.75">
+    <row r="273" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1"/>
       <c r="B273" s="2"/>
       <c r="C273" s="1"/>
@@ -12063,7 +12267,7 @@
       <c r="AD273" s="5"/>
       <c r="AE273" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="18.75">
+    <row r="274" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1"/>
       <c r="B274" s="2"/>
       <c r="C274" s="1"/>
@@ -12096,7 +12300,7 @@
       <c r="AD274" s="5"/>
       <c r="AE274" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="18.75">
+    <row r="275" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1"/>
       <c r="B275" s="2"/>
       <c r="C275" s="1"/>
@@ -12129,7 +12333,7 @@
       <c r="AD275" s="5"/>
       <c r="AE275" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="18.75">
+    <row r="276" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1"/>
       <c r="B276" s="2"/>
       <c r="C276" s="1"/>
@@ -12162,7 +12366,7 @@
       <c r="AD276" s="5"/>
       <c r="AE276" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="18.75">
+    <row r="277" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1"/>
       <c r="B277" s="2"/>
       <c r="C277" s="1"/>
@@ -12195,7 +12399,7 @@
       <c r="AD277" s="5"/>
       <c r="AE277" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="18.75">
+    <row r="278" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1"/>
       <c r="B278" s="2"/>
       <c r="C278" s="1"/>
@@ -12228,7 +12432,7 @@
       <c r="AD278" s="5"/>
       <c r="AE278" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="18.75">
+    <row r="279" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1"/>
       <c r="B279" s="2"/>
       <c r="C279" s="1"/>
@@ -12261,7 +12465,7 @@
       <c r="AD279" s="5"/>
       <c r="AE279" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="18.75">
+    <row r="280" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1"/>
       <c r="B280" s="2"/>
       <c r="C280" s="1"/>
@@ -12294,7 +12498,7 @@
       <c r="AD280" s="5"/>
       <c r="AE280" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="18.75">
+    <row r="281" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1"/>
       <c r="B281" s="2"/>
       <c r="C281" s="1"/>
@@ -12327,7 +12531,7 @@
       <c r="AD281" s="5"/>
       <c r="AE281" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="18.75">
+    <row r="282" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1"/>
       <c r="B282" s="2"/>
       <c r="C282" s="1"/>
@@ -12360,7 +12564,7 @@
       <c r="AD282" s="5"/>
       <c r="AE282" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="18.75">
+    <row r="283" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1"/>
       <c r="B283" s="2"/>
       <c r="C283" s="1"/>
@@ -12393,7 +12597,7 @@
       <c r="AD283" s="5"/>
       <c r="AE283" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="18.75">
+    <row r="284" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1"/>
       <c r="B284" s="2"/>
       <c r="C284" s="1"/>
@@ -12426,7 +12630,7 @@
       <c r="AD284" s="5"/>
       <c r="AE284" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="18.75">
+    <row r="285" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1"/>
       <c r="B285" s="2"/>
       <c r="C285" s="1"/>
@@ -12459,7 +12663,7 @@
       <c r="AD285" s="5"/>
       <c r="AE285" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="18.75">
+    <row r="286" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1"/>
       <c r="B286" s="2"/>
       <c r="C286" s="1"/>
@@ -12492,7 +12696,7 @@
       <c r="AD286" s="5"/>
       <c r="AE286" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="18.75">
+    <row r="287" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1"/>
       <c r="B287" s="2"/>
       <c r="C287" s="1"/>
@@ -12525,7 +12729,7 @@
       <c r="AD287" s="5"/>
       <c r="AE287" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="18.75">
+    <row r="288" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1"/>
       <c r="B288" s="2"/>
       <c r="C288" s="1"/>
@@ -12558,7 +12762,7 @@
       <c r="AD288" s="5"/>
       <c r="AE288" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="18.75">
+    <row r="289" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1"/>
       <c r="B289" s="2"/>
       <c r="C289" s="1"/>
@@ -12591,7 +12795,7 @@
       <c r="AD289" s="5"/>
       <c r="AE289" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="18.75">
+    <row r="290" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1"/>
       <c r="B290" s="2"/>
       <c r="C290" s="1"/>
@@ -12624,7 +12828,7 @@
       <c r="AD290" s="5"/>
       <c r="AE290" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="18.75">
+    <row r="291" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1"/>
       <c r="B291" s="2"/>
       <c r="C291" s="1"/>
@@ -12657,7 +12861,7 @@
       <c r="AD291" s="5"/>
       <c r="AE291" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="18.75">
+    <row r="292" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1"/>
       <c r="B292" s="2"/>
       <c r="C292" s="1"/>
@@ -12690,7 +12894,7 @@
       <c r="AD292" s="5"/>
       <c r="AE292" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="18.75">
+    <row r="293" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1"/>
       <c r="B293" s="2"/>
       <c r="C293" s="1"/>
@@ -12723,7 +12927,7 @@
       <c r="AD293" s="5"/>
       <c r="AE293" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="18.75">
+    <row r="294" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1"/>
       <c r="B294" s="2"/>
       <c r="C294" s="1"/>
@@ -12758,20 +12962,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="O200:P200"/>
+    <mergeCell ref="Q200:R200"/>
+    <mergeCell ref="S200:T200"/>
+    <mergeCell ref="U200:V201"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="C79:K79"/>
+    <mergeCell ref="C82:K82"/>
+    <mergeCell ref="B184:K184"/>
     <mergeCell ref="B12:K12"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="C79:K79"/>
-    <mergeCell ref="C82:K82"/>
-    <mergeCell ref="B184:K184"/>
-    <mergeCell ref="O200:P200"/>
-    <mergeCell ref="Q200:R200"/>
-    <mergeCell ref="S200:T200"/>
-    <mergeCell ref="U200:V201"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/OIC DOCS/dummy.xlsx
+++ b/OIC DOCS/dummy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dev\Code\FastAPI\pc\uiic_automation\OIC DOCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jadav\Coding\Automation\UIIC\uiic_automation\OIC DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4F59EC-2CEC-43B5-B06D-7FAC66507F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E86E18-178E-485C-9405-7C1D21E7DE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="254">
   <si>
     <t>Er. SUNIL KUMAR</t>
   </si>
@@ -794,6 +794,9 @@
   </si>
   <si>
     <t>compulsory_excess</t>
+  </si>
+  <si>
+    <t>jumper</t>
   </si>
 </sst>
 </file>
@@ -1631,12 +1634,39 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1655,9 +1685,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1667,32 +1694,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2000,33 +2003,33 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE294"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.109375" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="31" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="31" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="4"/>
@@ -2059,7 +2062,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
     </row>
-    <row r="3" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="8" t="s">
         <v>0</v>
@@ -2096,7 +2099,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
     </row>
-    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
         <v>2</v>
@@ -2133,7 +2136,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
     </row>
-    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
         <v>4</v>
@@ -2170,7 +2173,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
     </row>
-    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="11" t="s">
         <v>6</v>
@@ -2207,7 +2210,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
     </row>
-    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="15"/>
       <c r="C7" s="16"/>
@@ -2240,7 +2243,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
     </row>
-    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="4"/>
@@ -2273,7 +2276,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
     </row>
-    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="19" t="s">
         <v>8</v>
@@ -2312,7 +2315,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
     </row>
-    <row r="10" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="19"/>
       <c r="C10" s="4"/>
@@ -2345,7 +2348,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
     </row>
-    <row r="11" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="22" t="s">
         <v>11</v>
@@ -2380,20 +2383,20 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
     </row>
-    <row r="12" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="168" t="s">
+      <c r="B12" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="167"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="165"/>
-      <c r="G12" s="165"/>
-      <c r="H12" s="164"/>
-      <c r="I12" s="164"/>
-      <c r="J12" s="164"/>
-      <c r="K12" s="165"/>
+      <c r="C12" s="152"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="154"/>
+      <c r="F12" s="155"/>
+      <c r="G12" s="155"/>
+      <c r="H12" s="154"/>
+      <c r="I12" s="154"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="155"/>
       <c r="L12" s="4"/>
       <c r="M12" s="5"/>
       <c r="N12" s="7"/>
@@ -2415,7 +2418,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
     </row>
-    <row r="13" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="5">
         <v>1</v>
@@ -2450,7 +2453,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
     </row>
-    <row r="14" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="19" t="s">
         <v>13</v>
@@ -2495,7 +2498,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
     </row>
-    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
       <c r="B15" s="5"/>
       <c r="C15" s="4" t="s">
@@ -2532,7 +2535,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
     </row>
-    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="4"/>
@@ -2565,7 +2568,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
     </row>
-    <row r="17" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="5" t="s">
         <v>19</v>
@@ -2614,7 +2617,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
     </row>
-    <row r="18" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="4"/>
@@ -2647,7 +2650,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
     </row>
-    <row r="19" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="19" t="s">
         <v>24</v>
@@ -2688,7 +2691,7 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
     </row>
-    <row r="20" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="5"/>
       <c r="C20" s="4" t="s">
@@ -2727,7 +2730,7 @@
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
     </row>
-    <row r="21" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="5"/>
       <c r="C21" s="4" t="s">
@@ -2766,7 +2769,7 @@
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
     </row>
-    <row r="22" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="19"/>
       <c r="C22" s="4"/>
@@ -2803,7 +2806,7 @@
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
     </row>
-    <row r="23" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="19" t="s">
         <v>30</v>
@@ -2844,7 +2847,7 @@
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
     </row>
-    <row r="24" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="19"/>
       <c r="C24" s="4"/>
@@ -2877,7 +2880,7 @@
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
     </row>
-    <row r="25" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="19">
         <v>2</v>
@@ -2918,7 +2921,7 @@
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
     </row>
-    <row r="26" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="5" t="s">
         <v>13</v>
@@ -2959,7 +2962,7 @@
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
     </row>
-    <row r="27" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="5" t="s">
         <v>19</v>
@@ -3000,7 +3003,7 @@
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
     </row>
-    <row r="28" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="5" t="s">
         <v>24</v>
@@ -3041,21 +3044,21 @@
       <c r="AD28" s="4"/>
       <c r="AE28" s="4"/>
     </row>
-    <row r="29" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="27"/>
       <c r="D29" s="28"/>
       <c r="E29" s="29"/>
       <c r="F29" s="30"/>
-      <c r="G29" s="159" t="s">
+      <c r="G29" s="156" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="152"/>
-      <c r="I29" s="169" t="s">
+      <c r="H29" s="157"/>
+      <c r="I29" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="152"/>
+      <c r="J29" s="157"/>
       <c r="K29" s="31" t="s">
         <v>43</v>
       </c>
@@ -3080,7 +3083,7 @@
       <c r="AD29" s="4"/>
       <c r="AE29" s="4"/>
     </row>
-    <row r="30" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="5" t="s">
         <v>30</v>
@@ -3093,15 +3096,15 @@
       <c r="F30" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="170" t="s">
+      <c r="G30" s="159" t="s">
         <v>45</v>
       </c>
-      <c r="H30" s="171"/>
-      <c r="I30" s="169" t="str">
+      <c r="H30" s="160"/>
+      <c r="I30" s="158" t="str">
         <f>G30</f>
         <v>MEXC19606KT080595</v>
       </c>
-      <c r="J30" s="152"/>
+      <c r="J30" s="157"/>
       <c r="K30" s="31" t="str">
         <f>G30</f>
         <v>MEXC19606KT080595</v>
@@ -3127,7 +3130,7 @@
       <c r="AD30" s="4"/>
       <c r="AE30" s="4"/>
     </row>
-    <row r="31" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="5" t="s">
         <v>46</v>
@@ -3140,15 +3143,15 @@
       <c r="F31" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="159" t="s">
+      <c r="G31" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="152"/>
-      <c r="I31" s="160" t="str">
+      <c r="H31" s="157"/>
+      <c r="I31" s="168" t="str">
         <f>G31</f>
         <v>CBZL12533</v>
       </c>
-      <c r="J31" s="161"/>
+      <c r="J31" s="169"/>
       <c r="K31" s="37" t="str">
         <f>G31</f>
         <v>CBZL12533</v>
@@ -3174,7 +3177,7 @@
       <c r="AD31" s="4"/>
       <c r="AE31" s="4"/>
     </row>
-    <row r="32" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="5" t="s">
         <v>49</v>
@@ -3219,7 +3222,7 @@
       <c r="AD32" s="4"/>
       <c r="AE32" s="4"/>
     </row>
-    <row r="33" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="5" t="s">
         <v>52</v>
@@ -3264,7 +3267,7 @@
       <c r="AD33" s="4"/>
       <c r="AE33" s="4"/>
     </row>
-    <row r="34" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="5" t="s">
         <v>55</v>
@@ -3309,7 +3312,7 @@
       <c r="AD34" s="4"/>
       <c r="AE34" s="4"/>
     </row>
-    <row r="35" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="5" t="s">
         <v>58</v>
@@ -3354,7 +3357,7 @@
       <c r="AD35" s="4"/>
       <c r="AE35" s="4"/>
     </row>
-    <row r="36" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="5" t="s">
         <v>61</v>
@@ -3399,7 +3402,7 @@
       <c r="AD36" s="4"/>
       <c r="AE36" s="4"/>
     </row>
-    <row r="37" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="5" t="s">
         <v>63</v>
@@ -3444,7 +3447,7 @@
       <c r="AD37" s="4"/>
       <c r="AE37" s="4"/>
     </row>
-    <row r="38" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="5" t="s">
         <v>65</v>
@@ -3489,7 +3492,7 @@
       <c r="AD38" s="4"/>
       <c r="AE38" s="4"/>
     </row>
-    <row r="39" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="4" t="s">
@@ -3528,7 +3531,7 @@
       <c r="AD39" s="4"/>
       <c r="AE39" s="4"/>
     </row>
-    <row r="40" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="4" t="s">
@@ -3575,7 +3578,7 @@
       <c r="AD40" s="4"/>
       <c r="AE40" s="4"/>
     </row>
-    <row r="41" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
       <c r="C41" s="4" t="s">
@@ -3618,7 +3621,7 @@
       <c r="AD41" s="4"/>
       <c r="AE41" s="4"/>
     </row>
-    <row r="42" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
       <c r="C42" s="4" t="s">
@@ -3661,7 +3664,7 @@
       <c r="AD42" s="4"/>
       <c r="AE42" s="4"/>
     </row>
-    <row r="43" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="5" t="s">
         <v>73</v>
@@ -3702,7 +3705,7 @@
       <c r="AD43" s="4"/>
       <c r="AE43" s="4"/>
     </row>
-    <row r="44" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="5" t="s">
         <v>75</v>
@@ -3745,7 +3748,7 @@
       <c r="AD44" s="4"/>
       <c r="AE44" s="4"/>
     </row>
-    <row r="45" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="5" t="s">
         <v>79</v>
@@ -3790,7 +3793,7 @@
       <c r="AD45" s="4"/>
       <c r="AE45" s="4"/>
     </row>
-    <row r="46" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="5" t="s">
         <v>84</v>
@@ -3829,7 +3832,7 @@
       <c r="AD46" s="4"/>
       <c r="AE46" s="4"/>
     </row>
-    <row r="47" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="19">
         <v>3</v>
@@ -3870,7 +3873,7 @@
       <c r="AD47" s="4"/>
       <c r="AE47" s="4"/>
     </row>
-    <row r="48" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="5" t="s">
         <v>13</v>
@@ -3919,7 +3922,7 @@
       <c r="AD48" s="4"/>
       <c r="AE48" s="4"/>
     </row>
-    <row r="49" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
       <c r="C49" s="4" t="s">
@@ -3958,7 +3961,7 @@
       <c r="AD49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
       <c r="C50" s="4" t="s">
@@ -3997,7 +4000,7 @@
       <c r="AD50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="5" t="s">
         <v>19</v>
@@ -4040,7 +4043,7 @@
       <c r="AD51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="5" t="s">
         <v>24</v>
@@ -4081,7 +4084,7 @@
       <c r="AD52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="5" t="s">
         <v>30</v>
@@ -4122,7 +4125,7 @@
       <c r="AD53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="5" t="s">
         <v>46</v>
@@ -4167,7 +4170,7 @@
       <c r="AD54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="5" t="s">
         <v>49</v>
@@ -4208,7 +4211,7 @@
       <c r="AD55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
       <c r="C56" s="4"/>
@@ -4245,7 +4248,7 @@
       <c r="AD56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="19">
         <v>4</v>
@@ -4286,7 +4289,7 @@
       <c r="AD57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="5" t="s">
         <v>13</v>
@@ -4327,7 +4330,7 @@
       <c r="AD58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="5" t="s">
         <v>19</v>
@@ -4368,7 +4371,7 @@
       <c r="AD59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="4"/>
@@ -4405,7 +4408,7 @@
       <c r="AD60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="19">
         <v>5</v>
@@ -4446,7 +4449,7 @@
       <c r="AD61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="4" t="s">
@@ -4489,7 +4492,7 @@
       <c r="AD62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="4" t="s">
@@ -4534,7 +4537,7 @@
       <c r="AD63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
       <c r="C64" s="4" t="s">
@@ -4573,7 +4576,7 @@
       <c r="AD64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
       <c r="C65" s="4" t="s">
@@ -4612,7 +4615,7 @@
       <c r="AD65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
       <c r="C66" s="4"/>
@@ -4645,7 +4648,7 @@
       <c r="AD66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
       <c r="C67" s="4"/>
@@ -4678,7 +4681,7 @@
       <c r="AD67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" s="19">
         <v>6</v>
@@ -4715,7 +4718,7 @@
       <c r="AD68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="19"/>
       <c r="C69" s="4" t="s">
@@ -4758,7 +4761,7 @@
       <c r="AD69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" s="19"/>
       <c r="C70" s="4" t="s">
@@ -4797,7 +4800,7 @@
       <c r="AD70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" s="19"/>
       <c r="C71" s="4" t="s">
@@ -4836,7 +4839,7 @@
       <c r="AD71" s="4"/>
       <c r="AE71" s="4"/>
     </row>
-    <row r="72" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
       <c r="C72" s="4" t="s">
@@ -4873,7 +4876,7 @@
       <c r="AD72" s="4"/>
       <c r="AE72" s="4"/>
     </row>
-    <row r="73" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="19">
         <v>7</v>
@@ -4914,7 +4917,7 @@
       <c r="AD73" s="4"/>
       <c r="AE73" s="4"/>
     </row>
-    <row r="74" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="19"/>
       <c r="C74" s="9"/>
@@ -4947,7 +4950,7 @@
       <c r="AD74" s="4"/>
       <c r="AE74" s="4"/>
     </row>
-    <row r="75" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="19">
         <v>8</v>
@@ -4988,7 +4991,7 @@
       <c r="AD75" s="4"/>
       <c r="AE75" s="4"/>
     </row>
-    <row r="76" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="4"/>
@@ -5021,7 +5024,7 @@
       <c r="AD76" s="4"/>
       <c r="AE76" s="4"/>
     </row>
-    <row r="77" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="19">
         <v>9</v>
@@ -5058,7 +5061,7 @@
       <c r="AD77" s="4"/>
       <c r="AE77" s="4"/>
     </row>
-    <row r="78" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="19"/>
       <c r="C78" s="4" t="s">
@@ -5093,20 +5096,20 @@
       <c r="AD78" s="4"/>
       <c r="AE78" s="4"/>
     </row>
-    <row r="79" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="19"/>
-      <c r="C79" s="162" t="s">
+      <c r="C79" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="D79" s="163"/>
-      <c r="E79" s="164"/>
-      <c r="F79" s="165"/>
-      <c r="G79" s="165"/>
-      <c r="H79" s="164"/>
-      <c r="I79" s="164"/>
-      <c r="J79" s="164"/>
-      <c r="K79" s="165"/>
+      <c r="D79" s="153"/>
+      <c r="E79" s="154"/>
+      <c r="F79" s="155"/>
+      <c r="G79" s="155"/>
+      <c r="H79" s="154"/>
+      <c r="I79" s="154"/>
+      <c r="J79" s="154"/>
+      <c r="K79" s="155"/>
       <c r="L79" s="4"/>
       <c r="M79" s="5"/>
       <c r="N79" s="7"/>
@@ -5128,7 +5131,7 @@
       <c r="AD79" s="4"/>
       <c r="AE79" s="4"/>
     </row>
-    <row r="80" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="4"/>
@@ -5165,7 +5168,7 @@
       <c r="AD80" s="4"/>
       <c r="AE80" s="4"/>
     </row>
-    <row r="81" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="19">
         <v>10</v>
@@ -5206,20 +5209,20 @@
       <c r="AD81" s="4"/>
       <c r="AE81" s="4"/>
     </row>
-    <row r="82" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="19"/>
-      <c r="C82" s="162" t="s">
+      <c r="C82" s="170" t="s">
         <v>147</v>
       </c>
-      <c r="D82" s="163"/>
-      <c r="E82" s="164"/>
-      <c r="F82" s="165"/>
-      <c r="G82" s="165"/>
-      <c r="H82" s="164"/>
-      <c r="I82" s="164"/>
-      <c r="J82" s="164"/>
-      <c r="K82" s="165"/>
+      <c r="D82" s="153"/>
+      <c r="E82" s="154"/>
+      <c r="F82" s="155"/>
+      <c r="G82" s="155"/>
+      <c r="H82" s="154"/>
+      <c r="I82" s="154"/>
+      <c r="J82" s="154"/>
+      <c r="K82" s="155"/>
       <c r="L82" s="4"/>
       <c r="M82" s="5"/>
       <c r="N82" s="7"/>
@@ -5241,7 +5244,7 @@
       <c r="AD82" s="4"/>
       <c r="AE82" s="4"/>
     </row>
-    <row r="83" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="48"/>
       <c r="B83" s="5"/>
       <c r="C83" s="4"/>
@@ -5274,7 +5277,7 @@
       <c r="AD83" s="4"/>
       <c r="AE83" s="4"/>
     </row>
-    <row r="84" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="19">
         <v>11</v>
@@ -5311,7 +5314,7 @@
       <c r="AD84" s="4"/>
       <c r="AE84" s="4"/>
     </row>
-    <row r="85" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="19"/>
       <c r="C85" s="4" t="s">
@@ -5346,7 +5349,7 @@
       <c r="AD85" s="4"/>
       <c r="AE85" s="4"/>
     </row>
-    <row r="86" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="19"/>
       <c r="C86" s="4"/>
@@ -5379,7 +5382,7 @@
       <c r="AD86" s="4"/>
       <c r="AE86" s="4"/>
     </row>
-    <row r="87" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="19">
         <v>12</v>
@@ -5416,7 +5419,7 @@
       <c r="AD87" s="4"/>
       <c r="AE87" s="4"/>
     </row>
-    <row r="88" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="38">
         <v>1</v>
@@ -5453,7 +5456,7 @@
       <c r="AD88" s="4"/>
       <c r="AE88" s="4"/>
     </row>
-    <row r="89" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="38">
         <v>2</v>
@@ -5494,7 +5497,7 @@
       <c r="AD89" s="4"/>
       <c r="AE89" s="4"/>
     </row>
-    <row r="90" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="38">
         <v>3</v>
@@ -5535,7 +5538,7 @@
       <c r="AD90" s="4"/>
       <c r="AE90" s="4"/>
     </row>
-    <row r="91" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="38">
         <v>4</v>
@@ -5576,7 +5579,7 @@
       <c r="AD91" s="4"/>
       <c r="AE91" s="4"/>
     </row>
-    <row r="92" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="38"/>
       <c r="C92" s="9"/>
@@ -5609,7 +5612,7 @@
       <c r="AD92" s="4"/>
       <c r="AE92" s="4"/>
     </row>
-    <row r="93" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="19">
         <v>13</v>
@@ -5646,7 +5649,7 @@
       <c r="AD93" s="4"/>
       <c r="AE93" s="4"/>
     </row>
-    <row r="94" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="19"/>
       <c r="C94" s="4"/>
@@ -5679,7 +5682,7 @@
       <c r="AD94" s="4"/>
       <c r="AE94" s="4"/>
     </row>
-    <row r="95" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="49"/>
       <c r="C95" s="50"/>
@@ -5716,7 +5719,7 @@
       <c r="AD95" s="4"/>
       <c r="AE95" s="4"/>
     </row>
-    <row r="96" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="55" t="s">
         <v>159</v>
@@ -5759,7 +5762,7 @@
       <c r="AD96" s="4"/>
       <c r="AE96" s="4"/>
     </row>
-    <row r="97" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="49" t="s">
         <v>161</v>
@@ -5800,7 +5803,7 @@
       <c r="AD97" s="4"/>
       <c r="AE97" s="4"/>
     </row>
-    <row r="98" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="59"/>
       <c r="C98" s="60"/>
@@ -5833,7 +5836,7 @@
       <c r="AD98" s="4"/>
       <c r="AE98" s="4"/>
     </row>
-    <row r="99" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="11"/>
       <c r="C99" s="12"/>
@@ -5872,7 +5875,7 @@
       <c r="AD99" s="4"/>
       <c r="AE99" s="4"/>
     </row>
-    <row r="100" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="63" t="s">
         <v>164</v>
@@ -5921,7 +5924,7 @@
       <c r="AD100" s="4"/>
       <c r="AE100" s="4"/>
     </row>
-    <row r="101" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
       <c r="B101" s="33">
         <v>1</v>
@@ -5964,7 +5967,7 @@
       <c r="AD101" s="4"/>
       <c r="AE101" s="4"/>
     </row>
-    <row r="102" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
       <c r="B102" s="73">
         <v>2</v>
@@ -6007,7 +6010,7 @@
       <c r="AD102" s="4"/>
       <c r="AE102" s="4"/>
     </row>
-    <row r="103" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
       <c r="B103" s="73">
         <v>3</v>
@@ -6050,7 +6053,7 @@
       <c r="AD103" s="4"/>
       <c r="AE103" s="4"/>
     </row>
-    <row r="104" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4"/>
       <c r="B104" s="73">
         <v>4</v>
@@ -6093,7 +6096,7 @@
       <c r="AD104" s="4"/>
       <c r="AE104" s="4"/>
     </row>
-    <row r="105" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
       <c r="B105" s="73">
         <v>5</v>
@@ -6136,7 +6139,7 @@
       <c r="AD105" s="4"/>
       <c r="AE105" s="4"/>
     </row>
-    <row r="106" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
       <c r="B106" s="73">
         <v>6</v>
@@ -6179,7 +6182,7 @@
       <c r="AD106" s="4"/>
       <c r="AE106" s="4"/>
     </row>
-    <row r="107" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
       <c r="B107" s="73">
         <v>7</v>
@@ -6222,7 +6225,7 @@
       <c r="AD107" s="4"/>
       <c r="AE107" s="4"/>
     </row>
-    <row r="108" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
       <c r="B108" s="73">
         <v>8</v>
@@ -6265,7 +6268,7 @@
       <c r="AD108" s="4"/>
       <c r="AE108" s="4"/>
     </row>
-    <row r="109" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
       <c r="B109" s="73">
         <v>9</v>
@@ -6308,7 +6311,7 @@
       <c r="AD109" s="4"/>
       <c r="AE109" s="4"/>
     </row>
-    <row r="110" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
       <c r="B110" s="73">
         <v>10</v>
@@ -6351,7 +6354,7 @@
       <c r="AD110" s="4"/>
       <c r="AE110" s="4"/>
     </row>
-    <row r="111" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
       <c r="B111" s="73">
         <v>11</v>
@@ -6394,7 +6397,7 @@
       <c r="AD111" s="4"/>
       <c r="AE111" s="4"/>
     </row>
-    <row r="112" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
       <c r="B112" s="73">
         <v>12</v>
@@ -6437,7 +6440,7 @@
       <c r="AD112" s="4"/>
       <c r="AE112" s="4"/>
     </row>
-    <row r="113" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="73">
         <v>13</v>
@@ -6480,7 +6483,7 @@
       <c r="AD113" s="4"/>
       <c r="AE113" s="4"/>
     </row>
-    <row r="114" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4"/>
       <c r="B114" s="73">
         <v>14</v>
@@ -6523,7 +6526,7 @@
       <c r="AD114" s="4"/>
       <c r="AE114" s="4"/>
     </row>
-    <row r="115" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4"/>
       <c r="B115" s="73">
         <v>15</v>
@@ -6566,7 +6569,7 @@
       <c r="AD115" s="4"/>
       <c r="AE115" s="4"/>
     </row>
-    <row r="116" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4"/>
       <c r="B116" s="73">
         <v>16</v>
@@ -6611,7 +6614,7 @@
       <c r="AD116" s="4"/>
       <c r="AE116" s="4"/>
     </row>
-    <row r="117" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="73">
         <v>17</v>
@@ -6656,15 +6659,23 @@
       <c r="AD117" s="4"/>
       <c r="AE117" s="4"/>
     </row>
-    <row r="118" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4"/>
-      <c r="B118" s="73"/>
-      <c r="C118" s="4"/>
+      <c r="B118" s="73">
+        <v>18</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>253</v>
+      </c>
       <c r="D118" s="6"/>
       <c r="E118" s="71"/>
-      <c r="F118" s="72"/>
+      <c r="F118" s="72">
+        <v>150</v>
+      </c>
       <c r="G118" s="72"/>
-      <c r="H118" s="72"/>
+      <c r="H118" s="72">
+        <v>500</v>
+      </c>
       <c r="I118" s="72"/>
       <c r="J118" s="7"/>
       <c r="K118" s="5"/>
@@ -6689,7 +6700,7 @@
       <c r="AD118" s="4"/>
       <c r="AE118" s="4"/>
     </row>
-    <row r="119" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4"/>
       <c r="B119" s="73"/>
       <c r="C119" s="4"/>
@@ -6722,7 +6733,7 @@
       <c r="AD119" s="4"/>
       <c r="AE119" s="4"/>
     </row>
-    <row r="120" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4"/>
       <c r="B120" s="73"/>
       <c r="C120" s="4"/>
@@ -6755,7 +6766,7 @@
       <c r="AD120" s="4"/>
       <c r="AE120" s="4"/>
     </row>
-    <row r="121" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="73"/>
       <c r="C121" s="4"/>
@@ -6788,7 +6799,7 @@
       <c r="AD121" s="4"/>
       <c r="AE121" s="4"/>
     </row>
-    <row r="122" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4"/>
       <c r="B122" s="73"/>
       <c r="C122" s="4"/>
@@ -6821,7 +6832,7 @@
       <c r="AD122" s="4"/>
       <c r="AE122" s="4"/>
     </row>
-    <row r="123" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4"/>
       <c r="B123" s="73"/>
       <c r="C123" s="4"/>
@@ -6854,7 +6865,7 @@
       <c r="AD123" s="4"/>
       <c r="AE123" s="4"/>
     </row>
-    <row r="124" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4"/>
       <c r="B124" s="73"/>
       <c r="C124" s="4"/>
@@ -6887,7 +6898,7 @@
       <c r="AD124" s="4"/>
       <c r="AE124" s="4"/>
     </row>
-    <row r="125" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
       <c r="B125" s="73"/>
       <c r="C125" s="4"/>
@@ -6920,7 +6931,7 @@
       <c r="AD125" s="4"/>
       <c r="AE125" s="4"/>
     </row>
-    <row r="126" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
       <c r="B126" s="73"/>
       <c r="C126" s="4"/>
@@ -6953,7 +6964,7 @@
       <c r="AD126" s="4"/>
       <c r="AE126" s="4"/>
     </row>
-    <row r="127" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4"/>
       <c r="B127" s="73"/>
       <c r="C127" s="4"/>
@@ -6986,7 +6997,7 @@
       <c r="AD127" s="4"/>
       <c r="AE127" s="4"/>
     </row>
-    <row r="128" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4"/>
       <c r="B128" s="73"/>
       <c r="C128" s="4"/>
@@ -7019,7 +7030,7 @@
       <c r="AD128" s="4"/>
       <c r="AE128" s="4"/>
     </row>
-    <row r="129" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
       <c r="B129" s="73"/>
       <c r="C129" s="4"/>
@@ -7052,7 +7063,7 @@
       <c r="AD129" s="4"/>
       <c r="AE129" s="4"/>
     </row>
-    <row r="130" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4"/>
       <c r="B130" s="73"/>
       <c r="C130" s="4"/>
@@ -7085,7 +7096,7 @@
       <c r="AD130" s="4"/>
       <c r="AE130" s="4"/>
     </row>
-    <row r="131" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4"/>
       <c r="B131" s="73"/>
       <c r="C131" s="4"/>
@@ -7118,7 +7129,7 @@
       <c r="AD131" s="4"/>
       <c r="AE131" s="4"/>
     </row>
-    <row r="132" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4"/>
       <c r="B132" s="73"/>
       <c r="C132" s="4"/>
@@ -7151,7 +7162,7 @@
       <c r="AD132" s="4"/>
       <c r="AE132" s="4"/>
     </row>
-    <row r="133" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4"/>
       <c r="B133" s="73"/>
       <c r="C133" s="4"/>
@@ -7184,7 +7195,7 @@
       <c r="AD133" s="4"/>
       <c r="AE133" s="4"/>
     </row>
-    <row r="134" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4"/>
       <c r="B134" s="73"/>
       <c r="C134" s="4"/>
@@ -7217,7 +7228,7 @@
       <c r="AD134" s="4"/>
       <c r="AE134" s="4"/>
     </row>
-    <row r="135" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4"/>
       <c r="B135" s="77"/>
       <c r="C135" s="78"/>
@@ -7252,7 +7263,7 @@
       <c r="AD135" s="4"/>
       <c r="AE135" s="4"/>
     </row>
-    <row r="136" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4"/>
       <c r="B136" s="55" t="s">
         <v>190</v>
@@ -7262,7 +7273,7 @@
       <c r="E136" s="71"/>
       <c r="F136" s="72">
         <f>SUM(F101:F135)</f>
-        <v>139226</v>
+        <v>139376</v>
       </c>
       <c r="G136" s="83">
         <f>SUM(G101:G135)</f>
@@ -7270,7 +7281,7 @@
       </c>
       <c r="H136" s="84">
         <f>SUM(H101:H135)</f>
-        <v>539</v>
+        <v>1039</v>
       </c>
       <c r="I136" s="84">
         <f>SUM(I101:I135)</f>
@@ -7302,7 +7313,7 @@
       <c r="AD136" s="4"/>
       <c r="AE136" s="4"/>
     </row>
-    <row r="137" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="85"/>
       <c r="B137" s="86">
         <v>18</v>
@@ -7314,7 +7325,7 @@
       <c r="E137" s="65"/>
       <c r="F137" s="87">
         <f>B137*F136/100</f>
-        <v>25060.68</v>
+        <v>25087.68</v>
       </c>
       <c r="G137" s="87">
         <f>B137*G136/100</f>
@@ -7322,7 +7333,7 @@
       </c>
       <c r="H137" s="87">
         <f>B137*H136/100</f>
-        <v>97.02</v>
+        <v>187.02</v>
       </c>
       <c r="I137" s="87">
         <f>18*I136/100</f>
@@ -7351,7 +7362,7 @@
       <c r="AD137" s="4"/>
       <c r="AE137" s="4"/>
     </row>
-    <row r="138" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
       <c r="B138" s="55" t="s">
         <v>190</v>
@@ -7361,7 +7372,7 @@
       <c r="E138" s="7"/>
       <c r="F138" s="83">
         <f>SUM(F136:F137)</f>
-        <v>164286.68</v>
+        <v>164463.67999999999</v>
       </c>
       <c r="G138" s="83">
         <f>SUM(G136:G137)</f>
@@ -7369,7 +7380,7 @@
       </c>
       <c r="H138" s="83">
         <f>SUM(H136:H137)</f>
-        <v>636.02</v>
+        <v>1226.02</v>
       </c>
       <c r="I138" s="84">
         <f>SUM(I136:I137)</f>
@@ -7398,7 +7409,7 @@
       <c r="AD138" s="4"/>
       <c r="AE138" s="4"/>
     </row>
-    <row r="139" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
       <c r="B139" s="88" t="s">
         <v>192</v>
@@ -7433,7 +7444,7 @@
       <c r="AD139" s="4"/>
       <c r="AE139" s="4"/>
     </row>
-    <row r="140" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4"/>
       <c r="B140" s="89">
         <f>J96</f>
@@ -7451,7 +7462,7 @@
       </c>
       <c r="H140" s="90">
         <f>H138/2</f>
-        <v>318.01</v>
+        <v>613.01</v>
       </c>
       <c r="I140" s="84">
         <v>0</v>
@@ -7479,7 +7490,7 @@
       <c r="AD140" s="4"/>
       <c r="AE140" s="4"/>
     </row>
-    <row r="141" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
       <c r="B141" s="49" t="s">
         <v>194</v>
@@ -7489,7 +7500,7 @@
       <c r="E141" s="91"/>
       <c r="F141" s="92">
         <f>F138</f>
-        <v>164286.68</v>
+        <v>164463.67999999999</v>
       </c>
       <c r="G141" s="93">
         <f>G138-G140</f>
@@ -7497,7 +7508,7 @@
       </c>
       <c r="H141" s="92">
         <f>H138-H140</f>
-        <v>318.01</v>
+        <v>613.01</v>
       </c>
       <c r="I141" s="93">
         <f>I138-I140</f>
@@ -7526,7 +7537,7 @@
       <c r="AD141" s="4"/>
       <c r="AE141" s="4"/>
     </row>
-    <row r="142" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4"/>
       <c r="B142" s="63" t="s">
         <v>195</v>
@@ -7536,11 +7547,11 @@
       <c r="E142" s="94"/>
       <c r="F142" s="95">
         <f>F141</f>
-        <v>164286.68</v>
+        <v>164463.67999999999</v>
       </c>
       <c r="G142" s="96">
         <f>G141+H141+I141+J141</f>
-        <v>4124.8197999999993</v>
+        <v>4419.8197999999993</v>
       </c>
       <c r="H142" s="97"/>
       <c r="I142" s="91"/>
@@ -7567,7 +7578,7 @@
       <c r="AD142" s="4"/>
       <c r="AE142" s="4"/>
     </row>
-    <row r="143" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4"/>
       <c r="B143" s="19"/>
       <c r="C143" s="4"/>
@@ -7600,7 +7611,7 @@
       <c r="AD143" s="4"/>
       <c r="AE143" s="4"/>
     </row>
-    <row r="144" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4"/>
       <c r="B144" s="19" t="s">
         <v>196</v>
@@ -7611,7 +7622,7 @@
       <c r="F144" s="5"/>
       <c r="G144" s="20">
         <f>G140+H140+J140+I140</f>
-        <v>318.01</v>
+        <v>613.01</v>
       </c>
       <c r="H144" s="7"/>
       <c r="I144" s="7"/>
@@ -7638,7 +7649,7 @@
       <c r="AD144" s="4"/>
       <c r="AE144" s="4"/>
     </row>
-    <row r="145" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="4"/>
@@ -7671,7 +7682,7 @@
       <c r="AD145" s="4"/>
       <c r="AE145" s="4"/>
     </row>
-    <row r="146" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="4"/>
@@ -7704,7 +7715,7 @@
       <c r="AD146" s="4"/>
       <c r="AE146" s="4"/>
     </row>
-    <row r="147" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="4"/>
@@ -7737,7 +7748,7 @@
       <c r="AD147" s="4"/>
       <c r="AE147" s="4"/>
     </row>
-    <row r="148" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="4"/>
@@ -7770,7 +7781,7 @@
       <c r="AD148" s="4"/>
       <c r="AE148" s="4"/>
     </row>
-    <row r="149" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="4"/>
@@ -7803,7 +7814,7 @@
       <c r="AD149" s="4"/>
       <c r="AE149" s="4"/>
     </row>
-    <row r="150" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="4"/>
@@ -7836,7 +7847,7 @@
       <c r="AD150" s="4"/>
       <c r="AE150" s="4"/>
     </row>
-    <row r="151" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="4"/>
@@ -7869,7 +7880,7 @@
       <c r="AD151" s="4"/>
       <c r="AE151" s="4"/>
     </row>
-    <row r="152" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="4"/>
@@ -7902,7 +7913,7 @@
       <c r="AD152" s="4"/>
       <c r="AE152" s="4"/>
     </row>
-    <row r="153" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4"/>
       <c r="B153" s="22" t="s">
         <v>197</v>
@@ -7937,7 +7948,7 @@
       <c r="AD153" s="4"/>
       <c r="AE153" s="4"/>
     </row>
-    <row r="154" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="4"/>
@@ -7970,7 +7981,7 @@
       <c r="AD154" s="4"/>
       <c r="AE154" s="4"/>
     </row>
-    <row r="155" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4"/>
       <c r="B155" s="98" t="s">
         <v>198</v>
@@ -8005,7 +8016,7 @@
       <c r="AD155" s="4"/>
       <c r="AE155" s="4"/>
     </row>
-    <row r="156" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4"/>
       <c r="B156" s="100" t="s">
         <v>164</v>
@@ -8050,7 +8061,7 @@
       <c r="AD156" s="4"/>
       <c r="AE156" s="4"/>
     </row>
-    <row r="157" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
       <c r="B157" s="73">
         <v>1</v>
@@ -8089,7 +8100,7 @@
       <c r="AD157" s="4"/>
       <c r="AE157" s="4"/>
     </row>
-    <row r="158" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4"/>
       <c r="B158" s="73">
         <v>2</v>
@@ -8128,7 +8139,7 @@
       <c r="AD158" s="4"/>
       <c r="AE158" s="4"/>
     </row>
-    <row r="159" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4"/>
       <c r="B159" s="73">
         <v>3</v>
@@ -8167,7 +8178,7 @@
       <c r="AD159" s="4"/>
       <c r="AE159" s="4"/>
     </row>
-    <row r="160" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4"/>
       <c r="B160" s="73"/>
       <c r="C160" s="4"/>
@@ -8200,7 +8211,7 @@
       <c r="AD160" s="4"/>
       <c r="AE160" s="4"/>
     </row>
-    <row r="161" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4"/>
       <c r="B161" s="73"/>
       <c r="C161" s="4"/>
@@ -8233,7 +8244,7 @@
       <c r="AD161" s="4"/>
       <c r="AE161" s="4"/>
     </row>
-    <row r="162" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4"/>
       <c r="B162" s="107" t="s">
         <v>190</v>
@@ -8280,7 +8291,7 @@
       <c r="AD162" s="4"/>
       <c r="AE162" s="4"/>
     </row>
-    <row r="163" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4"/>
       <c r="B163" s="109"/>
       <c r="C163" s="12"/>
@@ -8313,7 +8324,7 @@
       <c r="AD163" s="4"/>
       <c r="AE163" s="4"/>
     </row>
-    <row r="164" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="85"/>
       <c r="B164" s="98" t="s">
         <v>190</v>
@@ -8360,7 +8371,7 @@
       <c r="AD164" s="4"/>
       <c r="AE164" s="4"/>
     </row>
-    <row r="165" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4"/>
       <c r="B165" s="63"/>
       <c r="C165" s="12"/>
@@ -8398,7 +8409,7 @@
       <c r="AD165" s="4"/>
       <c r="AE165" s="4"/>
     </row>
-    <row r="166" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4"/>
       <c r="B166" s="115"/>
       <c r="C166" s="60"/>
@@ -8431,7 +8442,7 @@
       <c r="AD166" s="4"/>
       <c r="AE166" s="4"/>
     </row>
-    <row r="167" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4"/>
       <c r="B167" s="98" t="s">
         <v>208</v>
@@ -8470,7 +8481,7 @@
       <c r="AD167" s="4"/>
       <c r="AE167" s="4"/>
     </row>
-    <row r="168" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4"/>
       <c r="B168" s="88"/>
       <c r="C168" s="4"/>
@@ -8509,7 +8520,7 @@
       <c r="AD168" s="4"/>
       <c r="AE168" s="4"/>
     </row>
-    <row r="169" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4"/>
       <c r="B169" s="118">
         <f>J97</f>
@@ -8553,7 +8564,7 @@
       <c r="AD169" s="4"/>
       <c r="AE169" s="4"/>
     </row>
-    <row r="170" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4"/>
       <c r="B170" s="98" t="s">
         <v>210</v>
@@ -8594,7 +8605,7 @@
       <c r="AD170" s="4"/>
       <c r="AE170" s="4"/>
     </row>
-    <row r="171" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="4"/>
@@ -8627,7 +8638,7 @@
       <c r="AD171" s="4"/>
       <c r="AE171" s="4"/>
     </row>
-    <row r="172" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4"/>
       <c r="B172" s="19" t="s">
         <v>211</v>
@@ -8665,7 +8676,7 @@
       <c r="AD172" s="4"/>
       <c r="AE172" s="4"/>
     </row>
-    <row r="173" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
       <c r="B173" s="11"/>
       <c r="C173" s="12"/>
@@ -8698,7 +8709,7 @@
       <c r="AD173" s="4"/>
       <c r="AE173" s="4"/>
     </row>
-    <row r="174" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4"/>
       <c r="B174" s="63" t="s">
         <v>212</v>
@@ -8737,7 +8748,7 @@
       <c r="AD174" s="4"/>
       <c r="AE174" s="4"/>
     </row>
-    <row r="175" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4"/>
       <c r="B175" s="120" t="s">
         <v>213</v>
@@ -8747,11 +8758,11 @@
       <c r="E175" s="62"/>
       <c r="F175" s="106">
         <f>F142</f>
-        <v>164286.68</v>
+        <v>164463.67999999999</v>
       </c>
       <c r="G175" s="112">
         <f>G142</f>
-        <v>4124.8197999999993</v>
+        <v>4419.8197999999993</v>
       </c>
       <c r="H175" s="7"/>
       <c r="I175" s="7"/>
@@ -8778,7 +8789,7 @@
       <c r="AD175" s="4"/>
       <c r="AE175" s="4"/>
     </row>
-    <row r="176" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4"/>
       <c r="B176" s="109" t="s">
         <v>214</v>
@@ -8819,7 +8830,7 @@
       <c r="AD176" s="4"/>
       <c r="AE176" s="4"/>
     </row>
-    <row r="177" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4"/>
       <c r="B177" s="55" t="s">
         <v>190</v>
@@ -8829,11 +8840,11 @@
       <c r="E177" s="71"/>
       <c r="F177" s="72">
         <f>F175+F176</f>
-        <v>164286.68</v>
+        <v>164463.67999999999</v>
       </c>
       <c r="G177" s="72">
         <f>G175+G176</f>
-        <v>4142.5197999999991</v>
+        <v>4437.5197999999991</v>
       </c>
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
@@ -8860,7 +8871,7 @@
       <c r="AD177" s="4"/>
       <c r="AE177" s="4"/>
     </row>
-    <row r="178" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4"/>
       <c r="B178" s="109" t="s">
         <v>215</v>
@@ -8898,7 +8909,7 @@
       <c r="AD178" s="4"/>
       <c r="AE178" s="4"/>
     </row>
-    <row r="179" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4"/>
       <c r="B179" s="63" t="s">
         <v>216</v>
@@ -8908,11 +8919,11 @@
       <c r="E179" s="94"/>
       <c r="F179" s="119">
         <f>F177</f>
-        <v>164286.68</v>
+        <v>164463.67999999999</v>
       </c>
       <c r="G179" s="121">
         <f>G177-G178</f>
-        <v>3642.5197999999991</v>
+        <v>3937.5197999999991</v>
       </c>
       <c r="H179" s="7"/>
       <c r="I179" s="7"/>
@@ -8939,7 +8950,7 @@
       <c r="AD179" s="4"/>
       <c r="AE179" s="4"/>
     </row>
-    <row r="180" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="4"/>
@@ -8972,7 +8983,7 @@
       <c r="AD180" s="4"/>
       <c r="AE180" s="4"/>
     </row>
-    <row r="181" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
       <c r="B181" s="5" t="s">
         <v>217</v>
@@ -9009,7 +9020,7 @@
       <c r="AD181" s="4"/>
       <c r="AE181" s="4"/>
     </row>
-    <row r="182" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4"/>
       <c r="B182" s="98" t="s">
         <v>218</v>
@@ -9020,7 +9031,7 @@
       <c r="F182" s="53"/>
       <c r="G182" s="68">
         <f>G179-G181</f>
-        <v>3642.5197999999991</v>
+        <v>3937.5197999999991</v>
       </c>
       <c r="H182" s="7"/>
       <c r="I182" s="56"/>
@@ -9047,7 +9058,7 @@
       <c r="AD182" s="4"/>
       <c r="AE182" s="4"/>
     </row>
-    <row r="183" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="4"/>
@@ -9080,20 +9091,20 @@
       <c r="AD183" s="4"/>
       <c r="AE183" s="4"/>
     </row>
-    <row r="184" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4"/>
-      <c r="B184" s="166" t="s">
+      <c r="B184" s="171" t="s">
         <v>219</v>
       </c>
-      <c r="C184" s="167"/>
-      <c r="D184" s="163"/>
-      <c r="E184" s="164"/>
-      <c r="F184" s="165"/>
-      <c r="G184" s="165"/>
-      <c r="H184" s="164"/>
-      <c r="I184" s="164"/>
-      <c r="J184" s="164"/>
-      <c r="K184" s="165"/>
+      <c r="C184" s="152"/>
+      <c r="D184" s="153"/>
+      <c r="E184" s="154"/>
+      <c r="F184" s="155"/>
+      <c r="G184" s="155"/>
+      <c r="H184" s="154"/>
+      <c r="I184" s="154"/>
+      <c r="J184" s="154"/>
+      <c r="K184" s="155"/>
       <c r="L184" s="4"/>
       <c r="M184" s="5"/>
       <c r="N184" s="7"/>
@@ -9115,7 +9126,7 @@
       <c r="AD184" s="4"/>
       <c r="AE184" s="4"/>
     </row>
-    <row r="185" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4"/>
       <c r="B185" s="23"/>
       <c r="C185" s="47"/>
@@ -9148,7 +9159,7 @@
       <c r="AD185" s="4"/>
       <c r="AE185" s="4"/>
     </row>
-    <row r="186" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4"/>
       <c r="B186" s="124" t="s">
         <v>220</v>
@@ -9183,7 +9194,7 @@
       <c r="AD186" s="4"/>
       <c r="AE186" s="4"/>
     </row>
-    <row r="187" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4"/>
       <c r="B187" s="19"/>
       <c r="C187" s="4"/>
@@ -9216,7 +9227,7 @@
       <c r="AD187" s="4"/>
       <c r="AE187" s="4"/>
     </row>
-    <row r="188" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4"/>
       <c r="B188" s="5">
         <v>1</v>
@@ -9258,7 +9269,7 @@
       <c r="AD188" s="4"/>
       <c r="AE188" s="4"/>
     </row>
-    <row r="189" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="4"/>
@@ -9291,7 +9302,7 @@
       <c r="AD189" s="4"/>
       <c r="AE189" s="4"/>
     </row>
-    <row r="190" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4"/>
       <c r="B190" s="5">
         <v>2</v>
@@ -9333,7 +9344,7 @@
       <c r="AD190" s="4"/>
       <c r="AE190" s="4"/>
     </row>
-    <row r="191" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4"/>
       <c r="B191" s="19"/>
       <c r="C191" s="4"/>
@@ -9366,7 +9377,7 @@
       <c r="AD191" s="4"/>
       <c r="AE191" s="4"/>
     </row>
-    <row r="192" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4"/>
       <c r="B192" s="19"/>
       <c r="C192" s="125" t="s">
@@ -9403,7 +9414,7 @@
       <c r="AD192" s="4"/>
       <c r="AE192" s="4"/>
     </row>
-    <row r="193" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="32"/>
@@ -9436,7 +9447,7 @@
       <c r="AD193" s="4"/>
       <c r="AE193" s="4"/>
     </row>
-    <row r="194" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4"/>
       <c r="B194" s="19"/>
       <c r="C194" s="126" t="s">
@@ -9471,7 +9482,7 @@
       <c r="AD194" s="4"/>
       <c r="AE194" s="4"/>
     </row>
-    <row r="195" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4"/>
       <c r="B195" s="19"/>
       <c r="C195" s="4"/>
@@ -9504,7 +9515,7 @@
       <c r="AD195" s="4"/>
       <c r="AE195" s="4"/>
     </row>
-    <row r="196" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4"/>
       <c r="B196" s="19"/>
       <c r="C196" s="4"/>
@@ -9537,7 +9548,7 @@
       <c r="AD196" s="4"/>
       <c r="AE196" s="4"/>
     </row>
-    <row r="197" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4"/>
       <c r="B197" s="19"/>
       <c r="C197" s="4"/>
@@ -9570,7 +9581,7 @@
       <c r="AD197" s="4"/>
       <c r="AE197" s="4"/>
     </row>
-    <row r="198" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="4" t="s">
@@ -9615,7 +9626,7 @@
       <c r="AD198" s="4"/>
       <c r="AE198" s="4"/>
     </row>
-    <row r="199" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="4"/>
@@ -9648,7 +9659,7 @@
       <c r="AD199" s="4"/>
       <c r="AE199" s="4"/>
     </row>
-    <row r="200" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="4"/>
@@ -9667,22 +9678,22 @@
       <c r="N200" s="130" t="s">
         <v>229</v>
       </c>
-      <c r="O200" s="151" t="s">
+      <c r="O200" s="161" t="s">
         <v>230</v>
       </c>
-      <c r="P200" s="152"/>
-      <c r="Q200" s="151" t="s">
+      <c r="P200" s="157"/>
+      <c r="Q200" s="161" t="s">
         <v>231</v>
       </c>
-      <c r="R200" s="152"/>
-      <c r="S200" s="153" t="s">
+      <c r="R200" s="157"/>
+      <c r="S200" s="162" t="s">
         <v>232</v>
       </c>
-      <c r="T200" s="154"/>
-      <c r="U200" s="155" t="s">
+      <c r="T200" s="163"/>
+      <c r="U200" s="164" t="s">
         <v>233</v>
       </c>
-      <c r="V200" s="156"/>
+      <c r="V200" s="165"/>
       <c r="W200" s="4"/>
       <c r="X200" s="4"/>
       <c r="Y200" s="4"/>
@@ -9693,7 +9704,7 @@
       <c r="AD200" s="4"/>
       <c r="AE200" s="4"/>
     </row>
-    <row r="201" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="4"/>
@@ -9726,8 +9737,8 @@
       <c r="T201" s="136" t="s">
         <v>235</v>
       </c>
-      <c r="U201" s="157"/>
-      <c r="V201" s="158"/>
+      <c r="U201" s="166"/>
+      <c r="V201" s="167"/>
       <c r="W201" s="4"/>
       <c r="X201" s="4"/>
       <c r="Y201" s="4"/>
@@ -9738,7 +9749,7 @@
       <c r="AD201" s="4"/>
       <c r="AE201" s="4"/>
     </row>
-    <row r="202" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4"/>
       <c r="B202" s="19"/>
       <c r="C202" s="4" t="s">
@@ -9758,27 +9769,27 @@
       <c r="M202" s="137"/>
       <c r="N202" s="43">
         <f>G136+H136</f>
-        <v>2742.11</v>
+        <v>3242.11</v>
       </c>
       <c r="O202" s="137">
         <v>14</v>
       </c>
       <c r="P202" s="138">
         <f>14*N202/100</f>
-        <v>383.8954</v>
+        <v>453.8954</v>
       </c>
       <c r="Q202" s="139">
         <v>14</v>
       </c>
       <c r="R202" s="138">
         <f>P202</f>
-        <v>383.8954</v>
+        <v>453.8954</v>
       </c>
       <c r="S202" s="70"/>
       <c r="T202" s="85"/>
       <c r="U202" s="56">
         <f>P202+R202</f>
-        <v>767.79079999999999</v>
+        <v>907.79079999999999</v>
       </c>
       <c r="V202" s="85"/>
       <c r="W202" s="4"/>
@@ -9791,7 +9802,7 @@
       <c r="AD202" s="4"/>
       <c r="AE202" s="4"/>
     </row>
-    <row r="203" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4"/>
       <c r="B203" s="19"/>
       <c r="C203" s="4"/>
@@ -9840,7 +9851,7 @@
       <c r="AD203" s="4"/>
       <c r="AE203" s="4"/>
     </row>
-    <row r="204" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4"/>
       <c r="B204" s="19"/>
       <c r="C204" s="4"/>
@@ -9889,7 +9900,7 @@
       <c r="AD204" s="4"/>
       <c r="AE204" s="4"/>
     </row>
-    <row r="205" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4"/>
       <c r="B205" s="19"/>
       <c r="C205" s="4"/>
@@ -9940,7 +9951,7 @@
       <c r="AD205" s="4"/>
       <c r="AE205" s="4"/>
     </row>
-    <row r="206" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="4"/>
@@ -9969,7 +9980,7 @@
       <c r="T206" s="101"/>
       <c r="U206" s="99">
         <f>SUM(U202:U205)</f>
-        <v>4873.4431999999997</v>
+        <v>5013.4431999999997</v>
       </c>
       <c r="V206" s="147"/>
       <c r="W206" s="4"/>
@@ -9982,7 +9993,7 @@
       <c r="AD206" s="4"/>
       <c r="AE206" s="4"/>
     </row>
-    <row r="207" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="4"/>
@@ -10015,7 +10026,7 @@
       <c r="AD207" s="4"/>
       <c r="AE207" s="4"/>
     </row>
-    <row r="208" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="4"/>
@@ -10048,7 +10059,7 @@
       <c r="AD208" s="4"/>
       <c r="AE208" s="4"/>
     </row>
-    <row r="209" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4"/>
       <c r="B209" s="19"/>
       <c r="C209" s="4"/>
@@ -10081,7 +10092,7 @@
       <c r="AD209" s="4"/>
       <c r="AE209" s="4"/>
     </row>
-    <row r="210" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4"/>
       <c r="B210" s="19"/>
       <c r="C210" s="4"/>
@@ -10114,7 +10125,7 @@
       <c r="AD210" s="4"/>
       <c r="AE210" s="4"/>
     </row>
-    <row r="211" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4"/>
       <c r="B211" s="19"/>
       <c r="C211" s="4"/>
@@ -10147,7 +10158,7 @@
       <c r="AD211" s="4"/>
       <c r="AE211" s="4"/>
     </row>
-    <row r="212" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4"/>
       <c r="B212" s="19"/>
       <c r="C212" s="4"/>
@@ -10180,7 +10191,7 @@
       <c r="AD212" s="4"/>
       <c r="AE212" s="4"/>
     </row>
-    <row r="213" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4"/>
       <c r="B213" s="19"/>
       <c r="C213" s="4"/>
@@ -10213,7 +10224,7 @@
       <c r="AD213" s="4"/>
       <c r="AE213" s="4"/>
     </row>
-    <row r="214" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4"/>
       <c r="B214" s="19"/>
       <c r="C214" s="4"/>
@@ -10246,7 +10257,7 @@
       <c r="AD214" s="4"/>
       <c r="AE214" s="4"/>
     </row>
-    <row r="215" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4"/>
       <c r="B215" s="19"/>
       <c r="C215" s="4"/>
@@ -10279,7 +10290,7 @@
       <c r="AD215" s="4"/>
       <c r="AE215" s="4"/>
     </row>
-    <row r="216" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4"/>
       <c r="B216" s="19"/>
       <c r="C216" s="4"/>
@@ -10312,7 +10323,7 @@
       <c r="AD216" s="4"/>
       <c r="AE216" s="4"/>
     </row>
-    <row r="217" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4"/>
       <c r="B217" s="19"/>
       <c r="C217" s="4"/>
@@ -10345,7 +10356,7 @@
       <c r="AD217" s="4"/>
       <c r="AE217" s="4"/>
     </row>
-    <row r="218" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4"/>
       <c r="B218" s="19"/>
       <c r="C218" s="4"/>
@@ -10378,7 +10389,7 @@
       <c r="AD218" s="4"/>
       <c r="AE218" s="4"/>
     </row>
-    <row r="219" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4"/>
       <c r="B219" s="19"/>
       <c r="C219" s="4"/>
@@ -10411,7 +10422,7 @@
       <c r="AD219" s="4"/>
       <c r="AE219" s="4"/>
     </row>
-    <row r="220" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4"/>
       <c r="B220" s="19"/>
       <c r="C220" s="4"/>
@@ -10444,7 +10455,7 @@
       <c r="AD220" s="4"/>
       <c r="AE220" s="4"/>
     </row>
-    <row r="221" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4"/>
       <c r="B221" s="19"/>
       <c r="C221" s="4"/>
@@ -10477,7 +10488,7 @@
       <c r="AD221" s="4"/>
       <c r="AE221" s="4"/>
     </row>
-    <row r="222" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4"/>
       <c r="B222" s="19"/>
       <c r="C222" s="4"/>
@@ -10510,7 +10521,7 @@
       <c r="AD222" s="4"/>
       <c r="AE222" s="4"/>
     </row>
-    <row r="223" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4"/>
       <c r="B223" s="19"/>
       <c r="C223" s="4"/>
@@ -10543,7 +10554,7 @@
       <c r="AD223" s="4"/>
       <c r="AE223" s="4"/>
     </row>
-    <row r="224" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4"/>
       <c r="B224" s="19"/>
       <c r="C224" s="4"/>
@@ -10576,7 +10587,7 @@
       <c r="AD224" s="4"/>
       <c r="AE224" s="4"/>
     </row>
-    <row r="225" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4"/>
       <c r="B225" s="19"/>
       <c r="C225" s="4"/>
@@ -10609,7 +10620,7 @@
       <c r="AD225" s="4"/>
       <c r="AE225" s="4"/>
     </row>
-    <row r="226" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4"/>
       <c r="B226" s="19"/>
       <c r="C226" s="4"/>
@@ -10642,7 +10653,7 @@
       <c r="AD226" s="4"/>
       <c r="AE226" s="4"/>
     </row>
-    <row r="227" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4"/>
       <c r="B227" s="19"/>
       <c r="C227" s="4"/>
@@ -10675,7 +10686,7 @@
       <c r="AD227" s="4"/>
       <c r="AE227" s="4"/>
     </row>
-    <row r="228" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4"/>
       <c r="B228" s="19"/>
       <c r="C228" s="4"/>
@@ -10708,7 +10719,7 @@
       <c r="AD228" s="4"/>
       <c r="AE228" s="4"/>
     </row>
-    <row r="229" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4"/>
       <c r="B229" s="19"/>
       <c r="C229" s="4"/>
@@ -10741,7 +10752,7 @@
       <c r="AD229" s="4"/>
       <c r="AE229" s="4"/>
     </row>
-    <row r="230" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4"/>
       <c r="B230" s="19"/>
       <c r="C230" s="4"/>
@@ -10774,7 +10785,7 @@
       <c r="AD230" s="4"/>
       <c r="AE230" s="4"/>
     </row>
-    <row r="231" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4"/>
       <c r="B231" s="19"/>
       <c r="C231" s="4"/>
@@ -10807,7 +10818,7 @@
       <c r="AD231" s="4"/>
       <c r="AE231" s="4"/>
     </row>
-    <row r="232" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4"/>
       <c r="B232" s="19"/>
       <c r="C232" s="4"/>
@@ -10840,7 +10851,7 @@
       <c r="AD232" s="4"/>
       <c r="AE232" s="4"/>
     </row>
-    <row r="233" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4"/>
       <c r="B233" s="19"/>
       <c r="C233" s="4"/>
@@ -10873,7 +10884,7 @@
       <c r="AD233" s="4"/>
       <c r="AE233" s="4"/>
     </row>
-    <row r="234" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4"/>
       <c r="B234" s="19"/>
       <c r="C234" s="4"/>
@@ -10906,7 +10917,7 @@
       <c r="AD234" s="4"/>
       <c r="AE234" s="4"/>
     </row>
-    <row r="235" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4"/>
       <c r="B235" s="19"/>
       <c r="C235" s="4"/>
@@ -10939,7 +10950,7 @@
       <c r="AD235" s="4"/>
       <c r="AE235" s="4"/>
     </row>
-    <row r="236" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4"/>
       <c r="B236" s="19"/>
       <c r="C236" s="4"/>
@@ -10972,7 +10983,7 @@
       <c r="AD236" s="4"/>
       <c r="AE236" s="4"/>
     </row>
-    <row r="237" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4"/>
       <c r="B237" s="19"/>
       <c r="C237" s="4"/>
@@ -11005,7 +11016,7 @@
       <c r="AD237" s="4"/>
       <c r="AE237" s="4"/>
     </row>
-    <row r="238" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4"/>
       <c r="B238" s="19"/>
       <c r="C238" s="4"/>
@@ -11038,7 +11049,7 @@
       <c r="AD238" s="4"/>
       <c r="AE238" s="4"/>
     </row>
-    <row r="239" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4"/>
       <c r="B239" s="19"/>
       <c r="C239" s="4"/>
@@ -11071,7 +11082,7 @@
       <c r="AD239" s="4"/>
       <c r="AE239" s="4"/>
     </row>
-    <row r="240" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4"/>
       <c r="B240" s="19"/>
       <c r="C240" s="4"/>
@@ -11104,7 +11115,7 @@
       <c r="AD240" s="4"/>
       <c r="AE240" s="4"/>
     </row>
-    <row r="241" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4"/>
       <c r="B241" s="19"/>
       <c r="C241" s="4"/>
@@ -11137,7 +11148,7 @@
       <c r="AD241" s="4"/>
       <c r="AE241" s="4"/>
     </row>
-    <row r="242" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4"/>
       <c r="B242" s="19"/>
       <c r="C242" s="4"/>
@@ -11170,7 +11181,7 @@
       <c r="AD242" s="4"/>
       <c r="AE242" s="4"/>
     </row>
-    <row r="243" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4"/>
       <c r="B243" s="19"/>
       <c r="C243" s="4"/>
@@ -11203,7 +11214,7 @@
       <c r="AD243" s="4"/>
       <c r="AE243" s="4"/>
     </row>
-    <row r="244" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4"/>
       <c r="B244" s="19"/>
       <c r="C244" s="4"/>
@@ -11236,7 +11247,7 @@
       <c r="AD244" s="4"/>
       <c r="AE244" s="4"/>
     </row>
-    <row r="245" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4"/>
       <c r="B245" s="19"/>
       <c r="C245" s="4"/>
@@ -11269,7 +11280,7 @@
       <c r="AD245" s="4"/>
       <c r="AE245" s="4"/>
     </row>
-    <row r="246" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4"/>
       <c r="B246" s="19"/>
       <c r="C246" s="4"/>
@@ -11302,7 +11313,7 @@
       <c r="AD246" s="4"/>
       <c r="AE246" s="4"/>
     </row>
-    <row r="247" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4"/>
       <c r="B247" s="19"/>
       <c r="C247" s="4"/>
@@ -11335,7 +11346,7 @@
       <c r="AD247" s="4"/>
       <c r="AE247" s="4"/>
     </row>
-    <row r="248" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4"/>
       <c r="B248" s="19"/>
       <c r="C248" s="4"/>
@@ -11368,7 +11379,7 @@
       <c r="AD248" s="4"/>
       <c r="AE248" s="4"/>
     </row>
-    <row r="249" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4"/>
       <c r="B249" s="19"/>
       <c r="C249" s="4"/>
@@ -11401,7 +11412,7 @@
       <c r="AD249" s="4"/>
       <c r="AE249" s="4"/>
     </row>
-    <row r="250" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4"/>
       <c r="B250" s="19"/>
       <c r="C250" s="4"/>
@@ -11434,7 +11445,7 @@
       <c r="AD250" s="4"/>
       <c r="AE250" s="4"/>
     </row>
-    <row r="251" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4"/>
       <c r="B251" s="19"/>
       <c r="C251" s="4"/>
@@ -11467,7 +11478,7 @@
       <c r="AD251" s="4"/>
       <c r="AE251" s="4"/>
     </row>
-    <row r="252" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="4"/>
@@ -11500,7 +11511,7 @@
       <c r="AD252" s="4"/>
       <c r="AE252" s="4"/>
     </row>
-    <row r="253" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="4"/>
@@ -11533,7 +11544,7 @@
       <c r="AD253" s="4"/>
       <c r="AE253" s="4"/>
     </row>
-    <row r="254" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="4"/>
@@ -11566,7 +11577,7 @@
       <c r="AD254" s="4"/>
       <c r="AE254" s="4"/>
     </row>
-    <row r="255" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="4"/>
@@ -11599,7 +11610,7 @@
       <c r="AD255" s="4"/>
       <c r="AE255" s="4"/>
     </row>
-    <row r="256" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="4"/>
@@ -11632,7 +11643,7 @@
       <c r="AD256" s="4"/>
       <c r="AE256" s="4"/>
     </row>
-    <row r="257" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="4"/>
@@ -11665,7 +11676,7 @@
       <c r="AD257" s="4"/>
       <c r="AE257" s="4"/>
     </row>
-    <row r="258" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="4"/>
@@ -11698,7 +11709,7 @@
       <c r="AD258" s="4"/>
       <c r="AE258" s="4"/>
     </row>
-    <row r="259" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="4" t="s">
@@ -11735,7 +11746,7 @@
       <c r="AD259" s="4"/>
       <c r="AE259" s="4"/>
     </row>
-    <row r="260" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="4" t="s">
@@ -11770,7 +11781,7 @@
       <c r="AD260" s="4"/>
       <c r="AE260" s="4"/>
     </row>
-    <row r="261" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="4"/>
@@ -11803,7 +11814,7 @@
       <c r="AD261" s="4"/>
       <c r="AE261" s="4"/>
     </row>
-    <row r="262" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="4"/>
@@ -11839,7 +11850,7 @@
       <c r="AD262" s="4"/>
       <c r="AE262" s="4"/>
     </row>
-    <row r="263" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="4"/>
@@ -11872,7 +11883,7 @@
       <c r="AD263" s="4"/>
       <c r="AE263" s="4"/>
     </row>
-    <row r="264" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="4"/>
@@ -11905,7 +11916,7 @@
       <c r="AD264" s="4"/>
       <c r="AE264" s="4"/>
     </row>
-    <row r="265" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="4"/>
@@ -11938,7 +11949,7 @@
       <c r="AD265" s="4"/>
       <c r="AE265" s="4"/>
     </row>
-    <row r="266" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="4"/>
@@ -11971,7 +11982,7 @@
       <c r="AD266" s="4"/>
       <c r="AE266" s="4"/>
     </row>
-    <row r="267" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="4"/>
@@ -12004,7 +12015,7 @@
       <c r="AD267" s="4"/>
       <c r="AE267" s="4"/>
     </row>
-    <row r="268" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="4"/>
@@ -12037,7 +12048,7 @@
       <c r="AD268" s="4"/>
       <c r="AE268" s="4"/>
     </row>
-    <row r="269" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="4"/>
@@ -12070,7 +12081,7 @@
       <c r="AD269" s="4"/>
       <c r="AE269" s="4"/>
     </row>
-    <row r="270" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="4"/>
@@ -12103,7 +12114,7 @@
       <c r="AD270" s="4"/>
       <c r="AE270" s="4"/>
     </row>
-    <row r="271" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D271" s="6"/>
       <c r="E271" s="7"/>
       <c r="F271" s="5"/>
@@ -12133,7 +12144,7 @@
       <c r="AD271" s="4"/>
       <c r="AE271" s="4"/>
     </row>
-    <row r="272" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D272" s="6"/>
       <c r="E272" s="7"/>
       <c r="F272" s="5"/>
@@ -12163,7 +12174,7 @@
       <c r="AD272" s="4"/>
       <c r="AE272" s="4"/>
     </row>
-    <row r="273" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D273" s="6"/>
       <c r="E273" s="7"/>
       <c r="F273" s="5"/>
@@ -12193,7 +12204,7 @@
       <c r="AD273" s="4"/>
       <c r="AE273" s="4"/>
     </row>
-    <row r="274" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D274" s="6"/>
       <c r="E274" s="7"/>
       <c r="F274" s="5"/>
@@ -12223,7 +12234,7 @@
       <c r="AD274" s="4"/>
       <c r="AE274" s="4"/>
     </row>
-    <row r="275" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D275" s="6"/>
       <c r="E275" s="7"/>
       <c r="F275" s="5"/>
@@ -12253,7 +12264,7 @@
       <c r="AD275" s="4"/>
       <c r="AE275" s="4"/>
     </row>
-    <row r="276" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D276" s="6"/>
       <c r="E276" s="7"/>
       <c r="F276" s="5"/>
@@ -12283,7 +12294,7 @@
       <c r="AD276" s="4"/>
       <c r="AE276" s="4"/>
     </row>
-    <row r="277" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D277" s="6"/>
       <c r="E277" s="7"/>
       <c r="F277" s="5"/>
@@ -12313,7 +12324,7 @@
       <c r="AD277" s="4"/>
       <c r="AE277" s="4"/>
     </row>
-    <row r="278" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D278" s="6"/>
       <c r="E278" s="7"/>
       <c r="F278" s="5"/>
@@ -12343,7 +12354,7 @@
       <c r="AD278" s="4"/>
       <c r="AE278" s="4"/>
     </row>
-    <row r="279" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D279" s="6"/>
       <c r="E279" s="7"/>
       <c r="F279" s="5"/>
@@ -12373,7 +12384,7 @@
       <c r="AD279" s="4"/>
       <c r="AE279" s="4"/>
     </row>
-    <row r="280" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D280" s="6"/>
       <c r="E280" s="7"/>
       <c r="F280" s="5"/>
@@ -12403,7 +12414,7 @@
       <c r="AD280" s="4"/>
       <c r="AE280" s="4"/>
     </row>
-    <row r="281" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D281" s="6"/>
       <c r="E281" s="7"/>
       <c r="F281" s="5"/>
@@ -12433,7 +12444,7 @@
       <c r="AD281" s="4"/>
       <c r="AE281" s="4"/>
     </row>
-    <row r="282" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D282" s="6"/>
       <c r="E282" s="7"/>
       <c r="F282" s="5"/>
@@ -12463,7 +12474,7 @@
       <c r="AD282" s="4"/>
       <c r="AE282" s="4"/>
     </row>
-    <row r="283" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D283" s="6"/>
       <c r="E283" s="7"/>
       <c r="F283" s="5"/>
@@ -12493,7 +12504,7 @@
       <c r="AD283" s="4"/>
       <c r="AE283" s="4"/>
     </row>
-    <row r="284" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D284" s="6"/>
       <c r="E284" s="7"/>
       <c r="F284" s="5"/>
@@ -12523,7 +12534,7 @@
       <c r="AD284" s="4"/>
       <c r="AE284" s="4"/>
     </row>
-    <row r="285" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D285" s="6"/>
       <c r="E285" s="7"/>
       <c r="F285" s="5"/>
@@ -12553,7 +12564,7 @@
       <c r="AD285" s="4"/>
       <c r="AE285" s="4"/>
     </row>
-    <row r="286" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D286" s="6"/>
       <c r="E286" s="7"/>
       <c r="F286" s="5"/>
@@ -12583,7 +12594,7 @@
       <c r="AD286" s="4"/>
       <c r="AE286" s="4"/>
     </row>
-    <row r="287" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D287" s="6"/>
       <c r="E287" s="7"/>
       <c r="F287" s="5"/>
@@ -12613,7 +12624,7 @@
       <c r="AD287" s="4"/>
       <c r="AE287" s="4"/>
     </row>
-    <row r="288" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D288" s="6"/>
       <c r="E288" s="7"/>
       <c r="F288" s="5"/>
@@ -12643,7 +12654,7 @@
       <c r="AD288" s="4"/>
       <c r="AE288" s="4"/>
     </row>
-    <row r="289" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D289" s="6"/>
       <c r="E289" s="7"/>
       <c r="F289" s="5"/>
@@ -12673,7 +12684,7 @@
       <c r="AD289" s="4"/>
       <c r="AE289" s="4"/>
     </row>
-    <row r="290" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D290" s="6"/>
       <c r="E290" s="7"/>
       <c r="F290" s="5"/>
@@ -12703,7 +12714,7 @@
       <c r="AD290" s="4"/>
       <c r="AE290" s="4"/>
     </row>
-    <row r="291" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D291" s="6"/>
       <c r="E291" s="7"/>
       <c r="F291" s="5"/>
@@ -12733,7 +12744,7 @@
       <c r="AD291" s="4"/>
       <c r="AE291" s="4"/>
     </row>
-    <row r="292" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D292" s="6"/>
       <c r="E292" s="7"/>
       <c r="F292" s="5"/>
@@ -12763,7 +12774,7 @@
       <c r="AD292" s="4"/>
       <c r="AE292" s="4"/>
     </row>
-    <row r="293" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D293" s="6"/>
       <c r="E293" s="7"/>
       <c r="F293" s="5"/>
@@ -12793,7 +12804,7 @@
       <c r="AD293" s="4"/>
       <c r="AE293" s="4"/>
     </row>
-    <row r="294" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D294" s="6"/>
       <c r="E294" s="7"/>
       <c r="F294" s="5"/>
@@ -12825,11 +12836,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
     <mergeCell ref="O200:P200"/>
     <mergeCell ref="Q200:R200"/>
     <mergeCell ref="S200:T200"/>
@@ -12839,6 +12845,11 @@
     <mergeCell ref="C79:K79"/>
     <mergeCell ref="C82:K82"/>
     <mergeCell ref="B184:K184"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/OIC DOCS/dummy.xlsx
+++ b/OIC DOCS/dummy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jadav\Coding\Automation\UIIC\uiic_automation\OIC DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E86E18-178E-485C-9405-7C1D21E7DE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C5E2C4-DE6A-47E9-90AE-955D89370F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1634,27 +1634,60 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1663,39 +1696,6 @@
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2385,18 +2385,18 @@
     </row>
     <row r="12" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="151" t="s">
+      <c r="B12" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="152"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="154"/>
-      <c r="F12" s="155"/>
-      <c r="G12" s="155"/>
-      <c r="H12" s="154"/>
-      <c r="I12" s="154"/>
-      <c r="J12" s="154"/>
-      <c r="K12" s="155"/>
+      <c r="C12" s="167"/>
+      <c r="D12" s="163"/>
+      <c r="E12" s="164"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="164"/>
+      <c r="I12" s="164"/>
+      <c r="J12" s="164"/>
+      <c r="K12" s="165"/>
       <c r="L12" s="4"/>
       <c r="M12" s="5"/>
       <c r="N12" s="7"/>
@@ -3051,14 +3051,14 @@
       <c r="D29" s="28"/>
       <c r="E29" s="29"/>
       <c r="F29" s="30"/>
-      <c r="G29" s="156" t="s">
+      <c r="G29" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="157"/>
-      <c r="I29" s="158" t="s">
+      <c r="H29" s="152"/>
+      <c r="I29" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="157"/>
+      <c r="J29" s="152"/>
       <c r="K29" s="31" t="s">
         <v>43</v>
       </c>
@@ -3096,15 +3096,15 @@
       <c r="F30" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="159" t="s">
+      <c r="G30" s="170" t="s">
         <v>45</v>
       </c>
-      <c r="H30" s="160"/>
-      <c r="I30" s="158" t="str">
+      <c r="H30" s="171"/>
+      <c r="I30" s="169" t="str">
         <f>G30</f>
         <v>MEXC19606KT080595</v>
       </c>
-      <c r="J30" s="157"/>
+      <c r="J30" s="152"/>
       <c r="K30" s="31" t="str">
         <f>G30</f>
         <v>MEXC19606KT080595</v>
@@ -3143,15 +3143,15 @@
       <c r="F31" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="156" t="s">
+      <c r="G31" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="157"/>
-      <c r="I31" s="168" t="str">
+      <c r="H31" s="152"/>
+      <c r="I31" s="160" t="str">
         <f>G31</f>
         <v>CBZL12533</v>
       </c>
-      <c r="J31" s="169"/>
+      <c r="J31" s="161"/>
       <c r="K31" s="37" t="str">
         <f>G31</f>
         <v>CBZL12533</v>
@@ -5099,17 +5099,17 @@
     <row r="79" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="19"/>
-      <c r="C79" s="170" t="s">
+      <c r="C79" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="D79" s="153"/>
-      <c r="E79" s="154"/>
-      <c r="F79" s="155"/>
-      <c r="G79" s="155"/>
-      <c r="H79" s="154"/>
-      <c r="I79" s="154"/>
-      <c r="J79" s="154"/>
-      <c r="K79" s="155"/>
+      <c r="D79" s="163"/>
+      <c r="E79" s="164"/>
+      <c r="F79" s="165"/>
+      <c r="G79" s="165"/>
+      <c r="H79" s="164"/>
+      <c r="I79" s="164"/>
+      <c r="J79" s="164"/>
+      <c r="K79" s="165"/>
       <c r="L79" s="4"/>
       <c r="M79" s="5"/>
       <c r="N79" s="7"/>
@@ -5212,17 +5212,17 @@
     <row r="82" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="19"/>
-      <c r="C82" s="170" t="s">
+      <c r="C82" s="162" t="s">
         <v>147</v>
       </c>
-      <c r="D82" s="153"/>
-      <c r="E82" s="154"/>
-      <c r="F82" s="155"/>
-      <c r="G82" s="155"/>
-      <c r="H82" s="154"/>
-      <c r="I82" s="154"/>
-      <c r="J82" s="154"/>
-      <c r="K82" s="155"/>
+      <c r="D82" s="163"/>
+      <c r="E82" s="164"/>
+      <c r="F82" s="165"/>
+      <c r="G82" s="165"/>
+      <c r="H82" s="164"/>
+      <c r="I82" s="164"/>
+      <c r="J82" s="164"/>
+      <c r="K82" s="165"/>
       <c r="L82" s="4"/>
       <c r="M82" s="5"/>
       <c r="N82" s="7"/>
@@ -6066,13 +6066,9 @@
       <c r="F104" s="72">
         <v>8861</v>
       </c>
-      <c r="G104" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H104" s="72">
+      <c r="I104" s="3">
         <v>5</v>
       </c>
-      <c r="I104" s="72"/>
       <c r="J104" s="7"/>
       <c r="K104" s="5"/>
       <c r="L104" s="4"/>
@@ -6109,13 +6105,6 @@
       <c r="F105" s="72">
         <v>9110</v>
       </c>
-      <c r="G105" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H105" s="72">
-        <v>5</v>
-      </c>
-      <c r="I105" s="72"/>
       <c r="J105" s="7"/>
       <c r="K105" s="5"/>
       <c r="L105" s="4"/>
@@ -6152,13 +6141,6 @@
       <c r="F106" s="72">
         <v>3030</v>
       </c>
-      <c r="G106" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H106" s="72">
-        <v>4</v>
-      </c>
-      <c r="I106" s="72"/>
       <c r="J106" s="7"/>
       <c r="K106" s="5"/>
       <c r="L106" s="4"/>
@@ -6195,20 +6177,17 @@
       <c r="F107" s="72">
         <v>1560</v>
       </c>
-      <c r="G107" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H107" s="72"/>
-      <c r="I107" s="72">
-        <v>5</v>
-      </c>
       <c r="J107" s="7"/>
       <c r="K107" s="5"/>
       <c r="L107" s="4"/>
       <c r="M107" s="5"/>
-      <c r="N107" s="7"/>
-      <c r="O107" s="5"/>
-      <c r="P107" s="7"/>
+      <c r="N107" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O107" s="72">
+        <v>5</v>
+      </c>
+      <c r="P107" s="72"/>
       <c r="Q107" s="5"/>
       <c r="R107" s="7"/>
       <c r="S107" s="4"/>
@@ -6238,20 +6217,17 @@
       <c r="F108" s="72">
         <v>8570</v>
       </c>
-      <c r="G108" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H108" s="72">
-        <v>4</v>
-      </c>
-      <c r="I108" s="72"/>
       <c r="J108" s="7"/>
       <c r="K108" s="5"/>
       <c r="L108" s="4"/>
       <c r="M108" s="5"/>
-      <c r="N108" s="7"/>
-      <c r="O108" s="5"/>
-      <c r="P108" s="7"/>
+      <c r="N108" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O108" s="72">
+        <v>5</v>
+      </c>
+      <c r="P108" s="72"/>
       <c r="Q108" s="5"/>
       <c r="R108" s="7"/>
       <c r="S108" s="4"/>
@@ -6281,20 +6257,17 @@
       <c r="F109" s="72">
         <v>9110</v>
       </c>
-      <c r="G109" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H109" s="72">
-        <v>4</v>
-      </c>
-      <c r="I109" s="72"/>
       <c r="J109" s="7"/>
       <c r="K109" s="5"/>
       <c r="L109" s="4"/>
       <c r="M109" s="5"/>
-      <c r="N109" s="7"/>
-      <c r="O109" s="5"/>
-      <c r="P109" s="7"/>
+      <c r="N109" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O109" s="72">
+        <v>4</v>
+      </c>
+      <c r="P109" s="72"/>
       <c r="Q109" s="5"/>
       <c r="R109" s="7"/>
       <c r="S109" s="4"/>
@@ -6324,20 +6297,17 @@
       <c r="F110" s="72">
         <v>8861</v>
       </c>
-      <c r="G110" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H110" s="72"/>
-      <c r="I110" s="72">
-        <v>5</v>
-      </c>
       <c r="J110" s="7"/>
       <c r="K110" s="5"/>
       <c r="L110" s="4"/>
       <c r="M110" s="5"/>
-      <c r="N110" s="7"/>
-      <c r="O110" s="5"/>
-      <c r="P110" s="7"/>
+      <c r="N110" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O110" s="72"/>
+      <c r="P110" s="72">
+        <v>5</v>
+      </c>
       <c r="Q110" s="5"/>
       <c r="R110" s="7"/>
       <c r="S110" s="4"/>
@@ -6367,20 +6337,17 @@
       <c r="F111" s="72">
         <v>2270</v>
       </c>
-      <c r="G111" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H111" s="72"/>
-      <c r="I111" s="72">
-        <v>4</v>
-      </c>
       <c r="J111" s="7"/>
       <c r="K111" s="5"/>
       <c r="L111" s="4"/>
       <c r="M111" s="5"/>
-      <c r="N111" s="7"/>
-      <c r="O111" s="5"/>
-      <c r="P111" s="7"/>
+      <c r="N111" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O111" s="72">
+        <v>4</v>
+      </c>
+      <c r="P111" s="72"/>
       <c r="Q111" s="5"/>
       <c r="R111" s="7"/>
       <c r="S111" s="4"/>
@@ -6410,20 +6377,17 @@
       <c r="F112" s="72">
         <v>2270</v>
       </c>
-      <c r="G112" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H112" s="72">
-        <v>5</v>
-      </c>
-      <c r="I112" s="72"/>
       <c r="J112" s="7"/>
       <c r="K112" s="5"/>
       <c r="L112" s="4"/>
       <c r="M112" s="5"/>
-      <c r="N112" s="7"/>
-      <c r="O112" s="5"/>
-      <c r="P112" s="7"/>
+      <c r="N112" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O112" s="72">
+        <v>4</v>
+      </c>
+      <c r="P112" s="72"/>
       <c r="Q112" s="5"/>
       <c r="R112" s="7"/>
       <c r="S112" s="4"/>
@@ -6453,20 +6417,17 @@
       <c r="F113" s="72">
         <v>302</v>
       </c>
-      <c r="G113" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H113" s="72">
-        <v>4</v>
-      </c>
-      <c r="I113" s="72"/>
       <c r="J113" s="7"/>
       <c r="K113" s="5"/>
       <c r="L113" s="4"/>
       <c r="M113" s="5"/>
-      <c r="N113" s="7"/>
-      <c r="O113" s="5"/>
-      <c r="P113" s="7"/>
+      <c r="N113" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O113" s="72"/>
+      <c r="P113" s="72">
+        <v>5</v>
+      </c>
       <c r="Q113" s="5"/>
       <c r="R113" s="7"/>
       <c r="S113" s="4"/>
@@ -6496,20 +6457,17 @@
       <c r="F114" s="72">
         <v>3560</v>
       </c>
-      <c r="G114" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H114" s="72"/>
-      <c r="I114" s="72">
-        <v>5</v>
-      </c>
       <c r="J114" s="7"/>
       <c r="K114" s="5"/>
       <c r="L114" s="4"/>
       <c r="M114" s="5"/>
-      <c r="N114" s="7"/>
-      <c r="O114" s="5"/>
-      <c r="P114" s="7"/>
+      <c r="N114" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O114" s="72"/>
+      <c r="P114" s="72">
+        <v>4</v>
+      </c>
       <c r="Q114" s="5"/>
       <c r="R114" s="7"/>
       <c r="S114" s="4"/>
@@ -6539,20 +6497,17 @@
       <c r="F115" s="72">
         <v>70000</v>
       </c>
-      <c r="G115" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H115" s="72">
-        <v>4</v>
-      </c>
-      <c r="I115" s="72"/>
       <c r="J115" s="7"/>
       <c r="K115" s="5"/>
       <c r="L115" s="4"/>
       <c r="M115" s="5"/>
-      <c r="N115" s="7"/>
-      <c r="O115" s="5"/>
-      <c r="P115" s="7"/>
+      <c r="N115" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O115" s="72">
+        <v>5</v>
+      </c>
+      <c r="P115" s="72"/>
       <c r="Q115" s="5"/>
       <c r="R115" s="7"/>
       <c r="S115" s="4"/>
@@ -6582,11 +6537,6 @@
       <c r="F116" s="72">
         <v>100</v>
       </c>
-      <c r="G116" s="72"/>
-      <c r="H116" s="72">
-        <v>4</v>
-      </c>
-      <c r="I116" s="72"/>
       <c r="J116" s="76">
         <v>1771.18</v>
       </c>
@@ -6595,9 +6545,13 @@
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
-      <c r="N116" s="7"/>
-      <c r="O116" s="5"/>
-      <c r="P116" s="7"/>
+      <c r="N116" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O116" s="72">
+        <v>4</v>
+      </c>
+      <c r="P116" s="72"/>
       <c r="Q116" s="5"/>
       <c r="R116" s="7"/>
       <c r="S116" s="4"/>
@@ -6627,11 +6581,6 @@
       <c r="F117" s="72">
         <v>12</v>
       </c>
-      <c r="G117" s="72"/>
-      <c r="H117" s="72"/>
-      <c r="I117" s="72">
-        <v>4</v>
-      </c>
       <c r="J117" s="69">
         <v>20000</v>
       </c>
@@ -6640,9 +6589,13 @@
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="5"/>
-      <c r="N117" s="7"/>
-      <c r="O117" s="5"/>
-      <c r="P117" s="7"/>
+      <c r="N117" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O117" s="72"/>
+      <c r="P117" s="72">
+        <v>5</v>
+      </c>
       <c r="Q117" s="5"/>
       <c r="R117" s="7"/>
       <c r="S117" s="4"/>
@@ -6672,18 +6625,17 @@
       <c r="F118" s="72">
         <v>150</v>
       </c>
-      <c r="G118" s="72"/>
-      <c r="H118" s="72">
-        <v>500</v>
-      </c>
-      <c r="I118" s="72"/>
       <c r="J118" s="7"/>
       <c r="K118" s="5"/>
       <c r="L118" s="4"/>
       <c r="M118" s="5"/>
-      <c r="N118" s="7"/>
-      <c r="O118" s="5"/>
-      <c r="P118" s="7"/>
+      <c r="N118" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="O118" s="72">
+        <v>4</v>
+      </c>
+      <c r="P118" s="72"/>
       <c r="Q118" s="5"/>
       <c r="R118" s="7"/>
       <c r="S118" s="4"/>
@@ -6714,9 +6666,11 @@
       <c r="K119" s="5"/>
       <c r="L119" s="4"/>
       <c r="M119" s="5"/>
-      <c r="N119" s="7"/>
-      <c r="O119" s="5"/>
-      <c r="P119" s="7"/>
+      <c r="N119" s="72"/>
+      <c r="O119" s="72">
+        <v>4</v>
+      </c>
+      <c r="P119" s="72"/>
       <c r="Q119" s="5"/>
       <c r="R119" s="7"/>
       <c r="S119" s="4"/>
@@ -6747,9 +6701,11 @@
       <c r="K120" s="5"/>
       <c r="L120" s="4"/>
       <c r="M120" s="5"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="5"/>
-      <c r="P120" s="7"/>
+      <c r="N120" s="72"/>
+      <c r="O120" s="72"/>
+      <c r="P120" s="72">
+        <v>4</v>
+      </c>
       <c r="Q120" s="5"/>
       <c r="R120" s="7"/>
       <c r="S120" s="4"/>
@@ -6780,9 +6736,11 @@
       <c r="K121" s="5"/>
       <c r="L121" s="4"/>
       <c r="M121" s="5"/>
-      <c r="N121" s="7"/>
-      <c r="O121" s="5"/>
-      <c r="P121" s="7"/>
+      <c r="N121" s="72"/>
+      <c r="O121" s="72">
+        <v>500</v>
+      </c>
+      <c r="P121" s="72"/>
       <c r="Q121" s="5"/>
       <c r="R121" s="7"/>
       <c r="S121" s="4"/>
@@ -7281,11 +7239,11 @@
       </c>
       <c r="H136" s="84">
         <f>SUM(H101:H135)</f>
-        <v>1039</v>
+        <v>500</v>
       </c>
       <c r="I136" s="84">
         <f>SUM(I101:I135)</f>
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="J136" s="56">
         <f>SUM(J101:J135)</f>
@@ -7333,11 +7291,11 @@
       </c>
       <c r="H137" s="87">
         <f>B137*H136/100</f>
-        <v>187.02</v>
+        <v>90</v>
       </c>
       <c r="I137" s="87">
         <f>18*I136/100</f>
-        <v>184.14</v>
+        <v>180.9</v>
       </c>
       <c r="J137" s="56"/>
       <c r="K137" s="5"/>
@@ -7380,11 +7338,11 @@
       </c>
       <c r="H138" s="83">
         <f>SUM(H136:H137)</f>
-        <v>1226.02</v>
+        <v>590</v>
       </c>
       <c r="I138" s="84">
         <f>SUM(I136:I137)</f>
-        <v>1207.1399999999999</v>
+        <v>1185.9000000000001</v>
       </c>
       <c r="J138" s="56"/>
       <c r="K138" s="5"/>
@@ -7462,7 +7420,7 @@
       </c>
       <c r="H140" s="90">
         <f>H138/2</f>
-        <v>613.01</v>
+        <v>295</v>
       </c>
       <c r="I140" s="84">
         <v>0</v>
@@ -7508,11 +7466,11 @@
       </c>
       <c r="H141" s="92">
         <f>H138-H140</f>
-        <v>613.01</v>
+        <v>295</v>
       </c>
       <c r="I141" s="93">
         <f>I138-I140</f>
-        <v>1207.1399999999999</v>
+        <v>1185.9000000000001</v>
       </c>
       <c r="J141" s="56"/>
       <c r="K141" s="5"/>
@@ -7551,7 +7509,7 @@
       </c>
       <c r="G142" s="96">
         <f>G141+H141+I141+J141</f>
-        <v>4419.8197999999993</v>
+        <v>4080.5698000000002</v>
       </c>
       <c r="H142" s="97"/>
       <c r="I142" s="91"/>
@@ -7622,7 +7580,7 @@
       <c r="F144" s="5"/>
       <c r="G144" s="20">
         <f>G140+H140+J140+I140</f>
-        <v>613.01</v>
+        <v>295</v>
       </c>
       <c r="H144" s="7"/>
       <c r="I144" s="7"/>
@@ -8762,7 +8720,7 @@
       </c>
       <c r="G175" s="112">
         <f>G142</f>
-        <v>4419.8197999999993</v>
+        <v>4080.5698000000002</v>
       </c>
       <c r="H175" s="7"/>
       <c r="I175" s="7"/>
@@ -8844,7 +8802,7 @@
       </c>
       <c r="G177" s="72">
         <f>G175+G176</f>
-        <v>4437.5197999999991</v>
+        <v>4098.2698</v>
       </c>
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
@@ -8923,7 +8881,7 @@
       </c>
       <c r="G179" s="121">
         <f>G177-G178</f>
-        <v>3937.5197999999991</v>
+        <v>3598.2698</v>
       </c>
       <c r="H179" s="7"/>
       <c r="I179" s="7"/>
@@ -9031,7 +8989,7 @@
       <c r="F182" s="53"/>
       <c r="G182" s="68">
         <f>G179-G181</f>
-        <v>3937.5197999999991</v>
+        <v>3598.2698</v>
       </c>
       <c r="H182" s="7"/>
       <c r="I182" s="56"/>
@@ -9093,18 +9051,18 @@
     </row>
     <row r="184" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4"/>
-      <c r="B184" s="171" t="s">
+      <c r="B184" s="166" t="s">
         <v>219</v>
       </c>
-      <c r="C184" s="152"/>
-      <c r="D184" s="153"/>
-      <c r="E184" s="154"/>
-      <c r="F184" s="155"/>
-      <c r="G184" s="155"/>
-      <c r="H184" s="154"/>
-      <c r="I184" s="154"/>
-      <c r="J184" s="154"/>
-      <c r="K184" s="155"/>
+      <c r="C184" s="167"/>
+      <c r="D184" s="163"/>
+      <c r="E184" s="164"/>
+      <c r="F184" s="165"/>
+      <c r="G184" s="165"/>
+      <c r="H184" s="164"/>
+      <c r="I184" s="164"/>
+      <c r="J184" s="164"/>
+      <c r="K184" s="165"/>
       <c r="L184" s="4"/>
       <c r="M184" s="5"/>
       <c r="N184" s="7"/>
@@ -9678,22 +9636,22 @@
       <c r="N200" s="130" t="s">
         <v>229</v>
       </c>
-      <c r="O200" s="161" t="s">
+      <c r="O200" s="151" t="s">
         <v>230</v>
       </c>
-      <c r="P200" s="157"/>
-      <c r="Q200" s="161" t="s">
+      <c r="P200" s="152"/>
+      <c r="Q200" s="151" t="s">
         <v>231</v>
       </c>
-      <c r="R200" s="157"/>
-      <c r="S200" s="162" t="s">
+      <c r="R200" s="152"/>
+      <c r="S200" s="153" t="s">
         <v>232</v>
       </c>
-      <c r="T200" s="163"/>
-      <c r="U200" s="164" t="s">
+      <c r="T200" s="154"/>
+      <c r="U200" s="155" t="s">
         <v>233</v>
       </c>
-      <c r="V200" s="165"/>
+      <c r="V200" s="156"/>
       <c r="W200" s="4"/>
       <c r="X200" s="4"/>
       <c r="Y200" s="4"/>
@@ -9737,8 +9695,8 @@
       <c r="T201" s="136" t="s">
         <v>235</v>
       </c>
-      <c r="U201" s="166"/>
-      <c r="V201" s="167"/>
+      <c r="U201" s="157"/>
+      <c r="V201" s="158"/>
       <c r="W201" s="4"/>
       <c r="X201" s="4"/>
       <c r="Y201" s="4"/>
@@ -9769,27 +9727,27 @@
       <c r="M202" s="137"/>
       <c r="N202" s="43">
         <f>G136+H136</f>
-        <v>3242.11</v>
+        <v>2703.11</v>
       </c>
       <c r="O202" s="137">
         <v>14</v>
       </c>
       <c r="P202" s="138">
         <f>14*N202/100</f>
-        <v>453.8954</v>
+        <v>378.43540000000002</v>
       </c>
       <c r="Q202" s="139">
         <v>14</v>
       </c>
       <c r="R202" s="138">
         <f>P202</f>
-        <v>453.8954</v>
+        <v>378.43540000000002</v>
       </c>
       <c r="S202" s="70"/>
       <c r="T202" s="85"/>
       <c r="U202" s="56">
         <f>P202+R202</f>
-        <v>907.79079999999999</v>
+        <v>756.87080000000003</v>
       </c>
       <c r="V202" s="85"/>
       <c r="W202" s="4"/>
@@ -9818,27 +9776,27 @@
       <c r="M203" s="137"/>
       <c r="N203" s="43">
         <f>I136</f>
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="O203" s="137">
         <v>9</v>
       </c>
       <c r="P203" s="138">
         <f>9*N203/100</f>
-        <v>92.07</v>
+        <v>90.45</v>
       </c>
       <c r="Q203" s="139">
         <v>9</v>
       </c>
       <c r="R203" s="138">
         <f>P203</f>
-        <v>92.07</v>
+        <v>90.45</v>
       </c>
       <c r="S203" s="74"/>
       <c r="T203" s="85"/>
       <c r="U203" s="56">
         <f>P203+R203</f>
-        <v>184.14</v>
+        <v>180.9</v>
       </c>
       <c r="V203" s="85"/>
       <c r="W203" s="4"/>
@@ -9980,7 +9938,7 @@
       <c r="T206" s="101"/>
       <c r="U206" s="99">
         <f>SUM(U202:U205)</f>
-        <v>5013.4431999999997</v>
+        <v>4859.2831999999999</v>
       </c>
       <c r="V206" s="147"/>
       <c r="W206" s="4"/>
@@ -12836,6 +12794,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
     <mergeCell ref="O200:P200"/>
     <mergeCell ref="Q200:R200"/>
     <mergeCell ref="S200:T200"/>
@@ -12845,11 +12808,6 @@
     <mergeCell ref="C79:K79"/>
     <mergeCell ref="C82:K82"/>
     <mergeCell ref="B184:K184"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/OIC DOCS/dummy.xlsx
+++ b/OIC DOCS/dummy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jadav\Coding\Automation\UIIC\uiic_automation\OIC DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C5E2C4-DE6A-47E9-90AE-955D89370F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824372D2-DF4E-4856-BE3B-F16C9FF2C614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="253">
   <si>
     <t>Er. SUNIL KUMAR</t>
   </si>
@@ -464,9 +464,6 @@
   </si>
   <si>
     <t xml:space="preserve">expiry date </t>
-  </si>
-  <si>
-    <t>30/05/2026</t>
   </si>
   <si>
     <t>OBERVATIONS/COMMENTS</t>
@@ -1634,12 +1631,39 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1658,9 +1682,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1670,32 +1691,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2010,17 +2007,17 @@
     <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="13.5546875" bestFit="1" customWidth="1"/>
@@ -2385,18 +2382,18 @@
     </row>
     <row r="12" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="168" t="s">
+      <c r="B12" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="167"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="165"/>
-      <c r="G12" s="165"/>
-      <c r="H12" s="164"/>
-      <c r="I12" s="164"/>
-      <c r="J12" s="164"/>
-      <c r="K12" s="165"/>
+      <c r="C12" s="152"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="154"/>
+      <c r="F12" s="155"/>
+      <c r="G12" s="155"/>
+      <c r="H12" s="154"/>
+      <c r="I12" s="154"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="155"/>
       <c r="L12" s="4"/>
       <c r="M12" s="5"/>
       <c r="N12" s="7"/>
@@ -3051,14 +3048,14 @@
       <c r="D29" s="28"/>
       <c r="E29" s="29"/>
       <c r="F29" s="30"/>
-      <c r="G29" s="159" t="s">
+      <c r="G29" s="156" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="152"/>
-      <c r="I29" s="169" t="s">
+      <c r="H29" s="157"/>
+      <c r="I29" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="152"/>
+      <c r="J29" s="157"/>
       <c r="K29" s="31" t="s">
         <v>43</v>
       </c>
@@ -3096,15 +3093,15 @@
       <c r="F30" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="170" t="s">
+      <c r="G30" s="159" t="s">
         <v>45</v>
       </c>
-      <c r="H30" s="171"/>
-      <c r="I30" s="169" t="str">
+      <c r="H30" s="160"/>
+      <c r="I30" s="158" t="str">
         <f>G30</f>
         <v>MEXC19606KT080595</v>
       </c>
-      <c r="J30" s="152"/>
+      <c r="J30" s="157"/>
       <c r="K30" s="31" t="str">
         <f>G30</f>
         <v>MEXC19606KT080595</v>
@@ -3143,15 +3140,15 @@
       <c r="F31" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="159" t="s">
+      <c r="G31" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="152"/>
-      <c r="I31" s="160" t="str">
+      <c r="H31" s="157"/>
+      <c r="I31" s="168" t="str">
         <f>G31</f>
         <v>CBZL12533</v>
       </c>
-      <c r="J31" s="161"/>
+      <c r="J31" s="169"/>
       <c r="K31" s="37" t="str">
         <f>G31</f>
         <v>CBZL12533</v>
@@ -3200,7 +3197,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="5"/>
       <c r="N32" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O32" s="5">
         <v>1000</v>
@@ -3240,7 +3237,7 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="5" t="s">
@@ -3285,10 +3282,10 @@
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J34" s="150" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="4"/>
@@ -3335,10 +3332,10 @@
       <c r="L35" s="4"/>
       <c r="M35" s="5"/>
       <c r="N35" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O35" s="150" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P35" s="7"/>
       <c r="Q35" s="5"/>
@@ -3380,10 +3377,10 @@
       <c r="L36" s="4"/>
       <c r="M36" s="5"/>
       <c r="N36" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O36" s="150" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P36" s="7"/>
       <c r="Q36" s="5"/>
@@ -3425,7 +3422,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="5"/>
       <c r="N37" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O37" s="5">
         <v>5454</v>
@@ -3470,7 +3467,7 @@
       <c r="L38" s="4"/>
       <c r="M38" s="5"/>
       <c r="N38" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O38" s="5">
         <v>1515</v>
@@ -3547,7 +3544,7 @@
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J40" s="7"/>
       <c r="K40" s="5">
@@ -3556,10 +3553,10 @@
       <c r="L40" s="4"/>
       <c r="M40" s="5"/>
       <c r="N40" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O40" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P40" s="7"/>
       <c r="Q40" s="5"/>
@@ -3599,10 +3596,10 @@
       <c r="L41" s="4"/>
       <c r="M41" s="5"/>
       <c r="N41" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="5"/>
@@ -5099,17 +5096,17 @@
     <row r="79" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="19"/>
-      <c r="C79" s="162" t="s">
+      <c r="C79" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="D79" s="163"/>
-      <c r="E79" s="164"/>
-      <c r="F79" s="165"/>
-      <c r="G79" s="165"/>
-      <c r="H79" s="164"/>
-      <c r="I79" s="164"/>
-      <c r="J79" s="164"/>
-      <c r="K79" s="165"/>
+      <c r="D79" s="153"/>
+      <c r="E79" s="154"/>
+      <c r="F79" s="155"/>
+      <c r="G79" s="155"/>
+      <c r="H79" s="154"/>
+      <c r="I79" s="154"/>
+      <c r="J79" s="154"/>
+      <c r="K79" s="155"/>
       <c r="L79" s="4"/>
       <c r="M79" s="5"/>
       <c r="N79" s="7"/>
@@ -5142,8 +5139,8 @@
       <c r="H80" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I80" s="6" t="s">
-        <v>143</v>
+      <c r="I80" s="6">
+        <v>46203</v>
       </c>
       <c r="J80" s="7"/>
       <c r="K80" s="5"/>
@@ -5174,17 +5171,17 @@
         <v>10</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="7"/>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
       <c r="H81" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I81" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="J81" s="7"/>
       <c r="K81" s="5"/>
@@ -5212,17 +5209,17 @@
     <row r="82" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="19"/>
-      <c r="C82" s="162" t="s">
-        <v>147</v>
-      </c>
-      <c r="D82" s="163"/>
-      <c r="E82" s="164"/>
-      <c r="F82" s="165"/>
-      <c r="G82" s="165"/>
-      <c r="H82" s="164"/>
-      <c r="I82" s="164"/>
-      <c r="J82" s="164"/>
-      <c r="K82" s="165"/>
+      <c r="C82" s="170" t="s">
+        <v>146</v>
+      </c>
+      <c r="D82" s="153"/>
+      <c r="E82" s="154"/>
+      <c r="F82" s="155"/>
+      <c r="G82" s="155"/>
+      <c r="H82" s="154"/>
+      <c r="I82" s="154"/>
+      <c r="J82" s="154"/>
+      <c r="K82" s="155"/>
       <c r="L82" s="4"/>
       <c r="M82" s="5"/>
       <c r="N82" s="7"/>
@@ -5283,7 +5280,7 @@
         <v>11</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="7"/>
@@ -5318,7 +5315,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="19"/>
       <c r="C85" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="7"/>
@@ -5388,7 +5385,7 @@
         <v>12</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="7"/>
@@ -5462,7 +5459,7 @@
         <v>2</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="7"/>
@@ -5473,7 +5470,7 @@
       <c r="J89" s="7"/>
       <c r="K89" s="5"/>
       <c r="L89" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M89" s="5">
         <v>180</v>
@@ -5503,7 +5500,7 @@
         <v>3</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="7"/>
@@ -5514,7 +5511,7 @@
       <c r="J90" s="7"/>
       <c r="K90" s="5"/>
       <c r="L90" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M90" s="5">
         <v>1000</v>
@@ -5544,7 +5541,7 @@
         <v>4</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="7"/>
@@ -5555,7 +5552,7 @@
       <c r="J91" s="7"/>
       <c r="K91" s="5"/>
       <c r="L91" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M91" s="5">
         <v>1000</v>
@@ -5618,7 +5615,7 @@
         <v>13</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="7"/>
@@ -5687,7 +5684,7 @@
       <c r="B95" s="49"/>
       <c r="C95" s="50"/>
       <c r="D95" s="28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E95" s="51"/>
       <c r="F95" s="52"/>
@@ -5722,7 +5719,7 @@
     <row r="96" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="6"/>
@@ -5732,7 +5729,7 @@
         <v>-119.88888888888889</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
@@ -5765,7 +5762,7 @@
     <row r="97" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="49" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C97" s="50"/>
       <c r="D97" s="28"/>
@@ -5774,7 +5771,7 @@
         <v>18</v>
       </c>
       <c r="G97" s="53" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H97" s="51"/>
       <c r="I97" s="51"/>
@@ -5844,13 +5841,13 @@
       <c r="E99" s="14"/>
       <c r="F99" s="11"/>
       <c r="G99" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H99" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J99" s="7"/>
       <c r="K99" s="5"/>
@@ -5878,30 +5875,30 @@
     <row r="100" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C100" s="64" t="s">
         <v>164</v>
-      </c>
-      <c r="C100" s="64" t="s">
-        <v>165</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="65"/>
       <c r="F100" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="G100" s="66" t="s">
         <v>166</v>
       </c>
-      <c r="G100" s="66" t="s">
+      <c r="H100" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="H100" s="67" t="s">
+      <c r="I100" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="I100" s="68" t="s">
+      <c r="J100" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="J100" s="20" t="s">
+      <c r="K100" s="69" t="s">
         <v>170</v>
-      </c>
-      <c r="K100" s="69" t="s">
-        <v>171</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="5"/>
@@ -5930,7 +5927,7 @@
         <v>1</v>
       </c>
       <c r="C101" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="71"/>
@@ -5973,7 +5970,7 @@
         <v>2</v>
       </c>
       <c r="C102" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="71"/>
@@ -6016,7 +6013,7 @@
         <v>3</v>
       </c>
       <c r="C103" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="71"/>
@@ -6024,7 +6021,7 @@
         <v>8570</v>
       </c>
       <c r="G103" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H103" s="72">
         <v>500</v>
@@ -6059,7 +6056,7 @@
         <v>4</v>
       </c>
       <c r="C104" s="74" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D104" s="6"/>
       <c r="E104" s="71"/>
@@ -6098,7 +6095,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="74" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="71"/>
@@ -6134,7 +6131,7 @@
         <v>6</v>
       </c>
       <c r="C106" s="74" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="71"/>
@@ -6170,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="C107" s="74" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="71"/>
@@ -6182,7 +6179,7 @@
       <c r="L107" s="4"/>
       <c r="M107" s="5"/>
       <c r="N107" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O107" s="72">
         <v>5</v>
@@ -6210,7 +6207,7 @@
         <v>8</v>
       </c>
       <c r="C108" s="74" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="71"/>
@@ -6222,7 +6219,7 @@
       <c r="L108" s="4"/>
       <c r="M108" s="5"/>
       <c r="N108" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O108" s="72">
         <v>5</v>
@@ -6250,7 +6247,7 @@
         <v>9</v>
       </c>
       <c r="C109" s="74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="71"/>
@@ -6262,7 +6259,7 @@
       <c r="L109" s="4"/>
       <c r="M109" s="5"/>
       <c r="N109" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O109" s="72">
         <v>4</v>
@@ -6290,7 +6287,7 @@
         <v>10</v>
       </c>
       <c r="C110" s="74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="71"/>
@@ -6302,7 +6299,7 @@
       <c r="L110" s="4"/>
       <c r="M110" s="5"/>
       <c r="N110" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O110" s="72"/>
       <c r="P110" s="72">
@@ -6330,7 +6327,7 @@
         <v>11</v>
       </c>
       <c r="C111" s="74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="71"/>
@@ -6342,7 +6339,7 @@
       <c r="L111" s="4"/>
       <c r="M111" s="5"/>
       <c r="N111" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O111" s="72">
         <v>4</v>
@@ -6370,7 +6367,7 @@
         <v>12</v>
       </c>
       <c r="C112" s="74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="71"/>
@@ -6382,7 +6379,7 @@
       <c r="L112" s="4"/>
       <c r="M112" s="5"/>
       <c r="N112" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O112" s="72">
         <v>4</v>
@@ -6410,7 +6407,7 @@
         <v>13</v>
       </c>
       <c r="C113" s="74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="71"/>
@@ -6422,7 +6419,7 @@
       <c r="L113" s="4"/>
       <c r="M113" s="5"/>
       <c r="N113" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O113" s="72"/>
       <c r="P113" s="72">
@@ -6450,7 +6447,7 @@
         <v>14</v>
       </c>
       <c r="C114" s="74" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="71"/>
@@ -6462,7 +6459,7 @@
       <c r="L114" s="4"/>
       <c r="M114" s="5"/>
       <c r="N114" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O114" s="72"/>
       <c r="P114" s="72">
@@ -6490,7 +6487,7 @@
         <v>15</v>
       </c>
       <c r="C115" s="74" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="71"/>
@@ -6502,7 +6499,7 @@
       <c r="L115" s="4"/>
       <c r="M115" s="5"/>
       <c r="N115" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O115" s="72">
         <v>5</v>
@@ -6530,7 +6527,7 @@
         <v>16</v>
       </c>
       <c r="C116" s="74" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="71"/>
@@ -6546,7 +6543,7 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O116" s="72">
         <v>4</v>
@@ -6574,13 +6571,16 @@
         <v>17</v>
       </c>
       <c r="C117" s="74" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="71"/>
       <c r="F117" s="72">
         <v>12</v>
       </c>
+      <c r="H117" s="3">
+        <v>544</v>
+      </c>
       <c r="J117" s="69">
         <v>20000</v>
       </c>
@@ -6590,7 +6590,7 @@
       <c r="L117" s="4"/>
       <c r="M117" s="5"/>
       <c r="N117" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O117" s="72"/>
       <c r="P117" s="72">
@@ -6618,7 +6618,7 @@
         <v>18</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="71"/>
@@ -6630,7 +6630,7 @@
       <c r="L118" s="4"/>
       <c r="M118" s="5"/>
       <c r="N118" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O118" s="72">
         <v>4</v>
@@ -7224,7 +7224,7 @@
     <row r="136" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4"/>
       <c r="B136" s="55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C136" s="4"/>
       <c r="D136" s="6"/>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H136" s="84">
         <f>SUM(H101:H135)</f>
-        <v>500</v>
+        <v>1044</v>
       </c>
       <c r="I136" s="84">
         <f>SUM(I101:I135)</f>
@@ -7277,7 +7277,7 @@
         <v>18</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D137" s="13"/>
       <c r="E137" s="65"/>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="H137" s="87">
         <f>B137*H136/100</f>
-        <v>90</v>
+        <v>187.92</v>
       </c>
       <c r="I137" s="87">
         <f>18*I136/100</f>
@@ -7323,7 +7323,7 @@
     <row r="138" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
       <c r="B138" s="55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="6"/>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="H138" s="83">
         <f>SUM(H136:H137)</f>
-        <v>590</v>
+        <v>1231.92</v>
       </c>
       <c r="I138" s="84">
         <f>SUM(I136:I137)</f>
@@ -7370,7 +7370,7 @@
     <row r="139" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
       <c r="B139" s="88" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="6"/>
@@ -7409,7 +7409,7 @@
         <v>0</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D140" s="13"/>
       <c r="E140" s="65"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="H140" s="90">
         <f>H138/2</f>
-        <v>295</v>
+        <v>615.96</v>
       </c>
       <c r="I140" s="84">
         <v>0</v>
@@ -7451,7 +7451,7 @@
     <row r="141" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
       <c r="B141" s="49" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C141" s="50"/>
       <c r="D141" s="28"/>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="H141" s="92">
         <f>H138-H140</f>
-        <v>295</v>
+        <v>615.96</v>
       </c>
       <c r="I141" s="93">
         <f>I138-I140</f>
@@ -7498,7 +7498,7 @@
     <row r="142" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4"/>
       <c r="B142" s="63" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C142" s="12"/>
       <c r="D142" s="28"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="G142" s="96">
         <f>G141+H141+I141+J141</f>
-        <v>4080.5698000000002</v>
+        <v>4401.5298000000003</v>
       </c>
       <c r="H142" s="97"/>
       <c r="I142" s="91"/>
@@ -7572,7 +7572,7 @@
     <row r="144" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4"/>
       <c r="B144" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C144" s="4"/>
       <c r="D144" s="6"/>
@@ -7580,7 +7580,7 @@
       <c r="F144" s="5"/>
       <c r="G144" s="20">
         <f>G140+H140+J140+I140</f>
-        <v>295</v>
+        <v>615.96</v>
       </c>
       <c r="H144" s="7"/>
       <c r="I144" s="7"/>
@@ -7874,7 +7874,7 @@
     <row r="153" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4"/>
       <c r="B153" s="22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="6"/>
@@ -7942,7 +7942,7 @@
     <row r="155" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4"/>
       <c r="B155" s="98" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C155" s="50"/>
       <c r="D155" s="28"/>
@@ -7977,24 +7977,24 @@
     <row r="156" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4"/>
       <c r="B156" s="100" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C156" s="101" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D156" s="28"/>
       <c r="E156" s="91"/>
       <c r="F156" s="102" t="s">
+        <v>199</v>
+      </c>
+      <c r="G156" s="103" t="s">
         <v>200</v>
       </c>
-      <c r="G156" s="103" t="s">
+      <c r="H156" s="104" t="s">
         <v>201</v>
       </c>
-      <c r="H156" s="104" t="s">
+      <c r="I156" s="105" t="s">
         <v>202</v>
-      </c>
-      <c r="I156" s="105" t="s">
-        <v>203</v>
       </c>
       <c r="J156" s="7"/>
       <c r="K156" s="5"/>
@@ -8025,7 +8025,7 @@
         <v>1</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="7"/>
@@ -8064,7 +8064,7 @@
         <v>2</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D158" s="6"/>
       <c r="E158" s="7"/>
@@ -8103,7 +8103,7 @@
         <v>3</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="7"/>
@@ -8205,7 +8205,7 @@
     <row r="162" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4"/>
       <c r="B162" s="107" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C162" s="60"/>
       <c r="D162" s="61"/>
@@ -8285,7 +8285,7 @@
     <row r="164" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="85"/>
       <c r="B164" s="98" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C164" s="50"/>
       <c r="D164" s="28"/>
@@ -8334,7 +8334,7 @@
       <c r="B165" s="63"/>
       <c r="C165" s="12"/>
       <c r="D165" s="79" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E165" s="14"/>
       <c r="F165" s="110"/>
@@ -8403,7 +8403,7 @@
     <row r="167" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4"/>
       <c r="B167" s="98" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C167" s="50"/>
       <c r="D167" s="28"/>
@@ -8411,10 +8411,10 @@
       <c r="F167" s="116"/>
       <c r="G167" s="116"/>
       <c r="H167" s="117" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I167" s="117" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J167" s="7"/>
       <c r="K167" s="5"/>
@@ -8485,7 +8485,7 @@
         <v>18</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="7"/>
@@ -8525,7 +8525,7 @@
     <row r="170" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4"/>
       <c r="B170" s="98" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C170" s="50"/>
       <c r="D170" s="28"/>
@@ -8599,7 +8599,7 @@
     <row r="172" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4"/>
       <c r="B172" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C172" s="4"/>
       <c r="D172" s="6"/>
@@ -8670,16 +8670,16 @@
     <row r="174" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4"/>
       <c r="B174" s="63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C174" s="12"/>
       <c r="D174" s="13"/>
       <c r="E174" s="65"/>
       <c r="F174" s="66" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G174" s="66" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H174" s="7"/>
       <c r="I174" s="7"/>
@@ -8709,7 +8709,7 @@
     <row r="175" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4"/>
       <c r="B175" s="120" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C175" s="60"/>
       <c r="D175" s="61"/>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="G175" s="112">
         <f>G142</f>
-        <v>4080.5698000000002</v>
+        <v>4401.5298000000003</v>
       </c>
       <c r="H175" s="7"/>
       <c r="I175" s="7"/>
@@ -8750,7 +8750,7 @@
     <row r="176" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4"/>
       <c r="B176" s="109" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C176" s="12"/>
       <c r="D176" s="13"/>
@@ -8791,7 +8791,7 @@
     <row r="177" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4"/>
       <c r="B177" s="55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="6"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="G177" s="72">
         <f>G175+G176</f>
-        <v>4098.2698</v>
+        <v>4419.2298000000001</v>
       </c>
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
@@ -8832,7 +8832,7 @@
     <row r="178" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4"/>
       <c r="B178" s="109" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C178" s="12"/>
       <c r="D178" s="13"/>
@@ -8870,7 +8870,7 @@
     <row r="179" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4"/>
       <c r="B179" s="63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C179" s="12"/>
       <c r="D179" s="28"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G179" s="121">
         <f>G177-G178</f>
-        <v>3598.2698</v>
+        <v>3919.2298000000001</v>
       </c>
       <c r="H179" s="7"/>
       <c r="I179" s="7"/>
@@ -8944,7 +8944,7 @@
     <row r="181" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
       <c r="B181" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C181" s="4"/>
       <c r="D181" s="6"/>
@@ -8981,7 +8981,7 @@
     <row r="182" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4"/>
       <c r="B182" s="98" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C182" s="50"/>
       <c r="D182" s="28"/>
@@ -8989,7 +8989,7 @@
       <c r="F182" s="53"/>
       <c r="G182" s="68">
         <f>G179-G181</f>
-        <v>3598.2698</v>
+        <v>3919.2298000000001</v>
       </c>
       <c r="H182" s="7"/>
       <c r="I182" s="56"/>
@@ -9051,18 +9051,18 @@
     </row>
     <row r="184" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4"/>
-      <c r="B184" s="166" t="s">
-        <v>219</v>
-      </c>
-      <c r="C184" s="167"/>
-      <c r="D184" s="163"/>
-      <c r="E184" s="164"/>
-      <c r="F184" s="165"/>
-      <c r="G184" s="165"/>
-      <c r="H184" s="164"/>
-      <c r="I184" s="164"/>
-      <c r="J184" s="164"/>
-      <c r="K184" s="165"/>
+      <c r="B184" s="171" t="s">
+        <v>218</v>
+      </c>
+      <c r="C184" s="152"/>
+      <c r="D184" s="153"/>
+      <c r="E184" s="154"/>
+      <c r="F184" s="155"/>
+      <c r="G184" s="155"/>
+      <c r="H184" s="154"/>
+      <c r="I184" s="154"/>
+      <c r="J184" s="154"/>
+      <c r="K184" s="155"/>
       <c r="L184" s="4"/>
       <c r="M184" s="5"/>
       <c r="N184" s="7"/>
@@ -9120,7 +9120,7 @@
     <row r="186" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4"/>
       <c r="B186" s="124" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C186" s="4"/>
       <c r="D186" s="6"/>
@@ -9191,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D188" s="6"/>
       <c r="E188" s="10" t="s">
@@ -9266,7 +9266,7 @@
         <v>2</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D190" s="6"/>
       <c r="E190" s="10" t="s">
@@ -9339,7 +9339,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="19"/>
       <c r="C192" s="125" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D192" s="61"/>
       <c r="E192" s="62"/>
@@ -9348,7 +9348,7 @@
       <c r="H192" s="7"/>
       <c r="I192" s="7"/>
       <c r="J192" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K192" s="5"/>
       <c r="L192" s="4"/>
@@ -9409,7 +9409,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="19"/>
       <c r="C194" s="126" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D194" s="13"/>
       <c r="E194" s="14"/>
@@ -9543,7 +9543,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D198" s="6" t="s">
         <v>15</v>
@@ -9563,7 +9563,7 @@
       <c r="K198" s="5"/>
       <c r="L198" s="4"/>
       <c r="M198" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N198" s="7"/>
       <c r="O198" s="5"/>
@@ -9631,27 +9631,27 @@
       <c r="K200" s="5"/>
       <c r="L200" s="4"/>
       <c r="M200" s="129" t="s">
+        <v>227</v>
+      </c>
+      <c r="N200" s="130" t="s">
         <v>228</v>
       </c>
-      <c r="N200" s="130" t="s">
+      <c r="O200" s="161" t="s">
         <v>229</v>
       </c>
-      <c r="O200" s="151" t="s">
+      <c r="P200" s="157"/>
+      <c r="Q200" s="161" t="s">
         <v>230</v>
       </c>
-      <c r="P200" s="152"/>
-      <c r="Q200" s="151" t="s">
+      <c r="R200" s="157"/>
+      <c r="S200" s="162" t="s">
         <v>231</v>
       </c>
-      <c r="R200" s="152"/>
-      <c r="S200" s="153" t="s">
+      <c r="T200" s="163"/>
+      <c r="U200" s="164" t="s">
         <v>232</v>
       </c>
-      <c r="T200" s="154"/>
-      <c r="U200" s="155" t="s">
-        <v>233</v>
-      </c>
-      <c r="V200" s="156"/>
+      <c r="V200" s="165"/>
       <c r="W200" s="4"/>
       <c r="X200" s="4"/>
       <c r="Y200" s="4"/>
@@ -9678,25 +9678,25 @@
       <c r="M201" s="132"/>
       <c r="N201" s="65"/>
       <c r="O201" s="131" t="s">
+        <v>233</v>
+      </c>
+      <c r="P201" s="133" t="s">
         <v>234</v>
       </c>
-      <c r="P201" s="133" t="s">
-        <v>235</v>
-      </c>
       <c r="Q201" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="R201" s="133" t="s">
         <v>234</v>
       </c>
-      <c r="R201" s="133" t="s">
-        <v>235</v>
-      </c>
       <c r="S201" s="135" t="s">
+        <v>233</v>
+      </c>
+      <c r="T201" s="136" t="s">
         <v>234</v>
       </c>
-      <c r="T201" s="136" t="s">
-        <v>235</v>
-      </c>
-      <c r="U201" s="157"/>
-      <c r="V201" s="158"/>
+      <c r="U201" s="166"/>
+      <c r="V201" s="167"/>
       <c r="W201" s="4"/>
       <c r="X201" s="4"/>
       <c r="Y201" s="4"/>
@@ -9711,10 +9711,10 @@
       <c r="A202" s="4"/>
       <c r="B202" s="19"/>
       <c r="C202" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D202" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="D202" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="5"/>
@@ -9727,27 +9727,27 @@
       <c r="M202" s="137"/>
       <c r="N202" s="43">
         <f>G136+H136</f>
-        <v>2703.11</v>
+        <v>3247.11</v>
       </c>
       <c r="O202" s="137">
         <v>14</v>
       </c>
       <c r="P202" s="138">
         <f>14*N202/100</f>
-        <v>378.43540000000002</v>
+        <v>454.59539999999998</v>
       </c>
       <c r="Q202" s="139">
         <v>14</v>
       </c>
       <c r="R202" s="138">
         <f>P202</f>
-        <v>378.43540000000002</v>
+        <v>454.59539999999998</v>
       </c>
       <c r="S202" s="70"/>
       <c r="T202" s="85"/>
       <c r="U202" s="56">
         <f>P202+R202</f>
-        <v>756.87080000000003</v>
+        <v>909.19079999999997</v>
       </c>
       <c r="V202" s="85"/>
       <c r="W202" s="4"/>
@@ -9914,7 +9914,7 @@
       <c r="B206" s="5"/>
       <c r="C206" s="4"/>
       <c r="D206" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E206" s="38">
         <v>2500</v>
@@ -9927,7 +9927,7 @@
       <c r="K206" s="5"/>
       <c r="L206" s="4"/>
       <c r="M206" s="98" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N206" s="145"/>
       <c r="O206" s="30"/>
@@ -9938,7 +9938,7 @@
       <c r="T206" s="101"/>
       <c r="U206" s="99">
         <f>SUM(U202:U205)</f>
-        <v>4859.2831999999999</v>
+        <v>5011.6031999999996</v>
       </c>
       <c r="V206" s="147"/>
       <c r="W206" s="4"/>
@@ -11671,7 +11671,7 @@
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D259" s="6"/>
       <c r="E259" s="148">
@@ -12794,11 +12794,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
     <mergeCell ref="O200:P200"/>
     <mergeCell ref="Q200:R200"/>
     <mergeCell ref="S200:T200"/>
@@ -12808,6 +12803,11 @@
     <mergeCell ref="C79:K79"/>
     <mergeCell ref="C82:K82"/>
     <mergeCell ref="B184:K184"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
